--- a/PATXOT 512/Agosto/PATXOT 521 Agosto.xlsx
+++ b/PATXOT 512/Agosto/PATXOT 521 Agosto.xlsx
@@ -1,34 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PATXOT 512\Junio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\PATXOT 512\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C34E795-CC59-4E9D-ABB6-2BBF9959560E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEEDAFE4-10BB-4BCE-AA7E-11DE057360DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
     <sheet name="prorrateo " sheetId="1" r:id="rId2"/>
     <sheet name="edesur" sheetId="5" r:id="rId3"/>
     <sheet name="eXTR" sheetId="4" r:id="rId4"/>
+    <sheet name="PRORRATEO EXPRESS" sheetId="6" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$45</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">edesur!$A$1:$H$15</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$L$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'PRORRATEO EXPRESS'!$A$1:$L$16</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="136">
   <si>
     <t>UF</t>
   </si>
@@ -414,23 +416,42 @@
     <t>Prevision ordinaria</t>
   </si>
   <si>
-    <t>LIQUIDACIÓN EXPENSAS MAYO 2025</t>
-  </si>
-  <si>
     <t>Honorarios MAYO 2025</t>
+  </si>
+  <si>
+    <t>Deuda</t>
+  </si>
+  <si>
+    <t>MATERIALES</t>
+  </si>
+  <si>
+    <t>Mano de</t>
+  </si>
+  <si>
+    <t>Materiales</t>
+  </si>
+  <si>
+    <t>Obra</t>
+  </si>
+  <si>
+    <t>MANO DE OBRA (1/2)</t>
+  </si>
+  <si>
+    <t>LIQUIDACIÓN EXPENSAS AGOSTO 2025</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
-    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="167" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="168" formatCode="d/m"/>
-    <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
+  <numFmts count="7">
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="d/m"/>
+    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="169" formatCode="_ &quot;$&quot;\ * #,##0.0_ ;_ &quot;$&quot;\ * \-#,##0.0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24" x14ac:knownFonts="1">
     <font>
@@ -670,7 +691,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="63">
+  <borders count="65">
     <border>
       <left/>
       <right/>
@@ -1394,15 +1415,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="205">
+  <cellXfs count="214">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1413,7 +1460,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1436,14 +1483,14 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1460,7 +1507,7 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1468,10 +1515,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="3" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="3" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="1" fillId="3" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="3" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1480,7 +1527,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="1" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1493,7 +1540,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1506,7 +1553,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1533,8 +1580,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1542,8 +1589,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1554,11 +1601,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="17" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="15" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1569,7 +1616,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1603,12 +1650,12 @@
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="8" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="8" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1638,16 +1685,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="11" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1657,7 +1704,7 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="22" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="22" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
@@ -1671,6 +1718,12 @@
     <xf numFmtId="4" fontId="15" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="15" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1734,7 +1787,7 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="22" fillId="11" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="22" fillId="11" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1749,9 +1802,26 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -2122,16 +2192,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:F56"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.28515625" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.33203125" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>21</v>
       </c>
@@ -2139,66 +2209,66 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="25"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="170" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B7" s="26"/>
       <c r="C7" s="26"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="23" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="87" t="s">
         <v>13</v>
       </c>
       <c r="B16" s="76"/>
       <c r="C16" s="11"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="76" t="s">
         <v>35</v>
       </c>
@@ -2206,43 +2276,43 @@
         <v>63</v>
       </c>
       <c r="C17" s="172">
-        <v>74186.03</v>
+        <v>79724.34</v>
       </c>
       <c r="D17" s="48"/>
       <c r="F17" s="14"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="76"/>
       <c r="B18" s="88"/>
       <c r="C18" s="85"/>
       <c r="D18" s="48"/>
       <c r="F18" s="14"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="76"/>
       <c r="B19" s="88"/>
       <c r="C19" s="85"/>
       <c r="D19" s="5"/>
       <c r="E19" s="14"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="89"/>
       <c r="B20" s="90"/>
       <c r="C20" s="61">
         <f>SUM(C17:C19)</f>
-        <v>74186.03</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+        <v>79724.34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="87" t="s">
         <v>36</v>
       </c>
       <c r="B21" s="88"/>
       <c r="C21" s="91"/>
     </row>
-    <row r="22" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="76" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B22" s="92"/>
       <c r="C22" s="85">
@@ -2250,7 +2320,7 @@
       </c>
       <c r="F22" s="22"/>
     </row>
-    <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="76" t="s">
         <v>126</v>
       </c>
@@ -2260,19 +2330,19 @@
       </c>
       <c r="F23" s="22"/>
     </row>
-    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="76"/>
       <c r="B24" s="92"/>
       <c r="C24" s="85"/>
       <c r="F24" s="22"/>
     </row>
-    <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="76"/>
       <c r="B25" s="92"/>
       <c r="C25" s="85"/>
       <c r="F25" s="22"/>
     </row>
-    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="76" t="s">
         <v>127</v>
       </c>
@@ -2284,7 +2354,7 @@
       <c r="E26" s="14"/>
       <c r="F26" s="22"/>
     </row>
-    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="89"/>
       <c r="B27" s="90"/>
       <c r="C27" s="61">
@@ -2293,51 +2363,51 @@
       </c>
       <c r="F27" s="22"/>
     </row>
-    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="80" t="s">
         <v>79</v>
       </c>
       <c r="B28" s="80"/>
       <c r="C28" s="93">
         <f>+C27+C20</f>
-        <v>290720.63</v>
+        <v>296258.94</v>
       </c>
       <c r="F28" s="22"/>
     </row>
-    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C29" s="62"/>
       <c r="F29" s="22"/>
     </row>
-    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="23" t="s">
         <v>44</v>
       </c>
       <c r="C30" s="62"/>
       <c r="F30" s="22"/>
     </row>
-    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="76"/>
       <c r="B31" s="76"/>
       <c r="C31" s="85"/>
       <c r="F31" s="22"/>
     </row>
-    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="76"/>
       <c r="B32" s="76"/>
       <c r="C32" s="86"/>
       <c r="F32" s="22"/>
     </row>
-    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="76"/>
       <c r="B33" s="76"/>
       <c r="C33" s="86"/>
       <c r="F33" s="22"/>
     </row>
-    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C34" s="64"/>
       <c r="F34" s="22"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="23" t="s">
         <v>41</v>
       </c>
@@ -2348,25 +2418,25 @@
       </c>
       <c r="E35" s="14"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="34" t="s">
         <v>15</v>
       </c>
       <c r="B37" s="34"/>
       <c r="C37" s="35">
         <f>+C35+C28</f>
-        <v>290720.63</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="39" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>296258.94</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="39" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="147" t="s">
         <v>37</v>
       </c>
       <c r="B39" s="148"/>
       <c r="C39" s="149"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="145" t="s">
         <v>10</v>
       </c>
@@ -2377,7 +2447,7 @@
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>9</v>
       </c>
@@ -2388,7 +2458,7 @@
       <c r="D41" s="14"/>
       <c r="E41" s="14"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>80</v>
       </c>
@@ -2399,43 +2469,43 @@
       <c r="D42" s="14"/>
       <c r="E42" s="14"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>65</v>
       </c>
       <c r="C43" s="94">
         <f>-(C28-C26)</f>
-        <v>-140720.63</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+        <v>-146258.94</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="36" t="s">
         <v>16</v>
       </c>
       <c r="B44" s="33"/>
       <c r="C44" s="40">
         <f>SUM(C40:C43)</f>
-        <v>-141943.09625966029</v>
+        <v>-147481.40625966029</v>
       </c>
       <c r="D44" s="6"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="19"/>
       <c r="B45" s="18"/>
       <c r="C45" s="20"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="19"/>
       <c r="B46" s="18"/>
       <c r="C46" s="20"/>
       <c r="F46" s="95"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="19"/>
       <c r="B47" s="18"/>
       <c r="C47" s="20"/>
     </row>
-    <row r="48" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="74" t="s">
         <v>58</v>
       </c>
@@ -2444,7 +2514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="76" t="s">
         <v>64</v>
       </c>
@@ -2454,17 +2524,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="76"/>
       <c r="B50" s="76"/>
       <c r="C50" s="83"/>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="76"/>
       <c r="B51" s="76"/>
       <c r="C51" s="84"/>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="80" t="s">
         <v>4</v>
       </c>
@@ -2474,22 +2544,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="18"/>
       <c r="B53" s="18"/>
       <c r="C53" s="18"/>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="18"/>
       <c r="B54" s="18"/>
       <c r="C54" s="18"/>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="18"/>
       <c r="B55" s="18"/>
       <c r="C55" s="18"/>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="18"/>
       <c r="B56" s="18"/>
       <c r="C56" s="18"/>
@@ -2511,24 +2581,24 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N128"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="4" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" customWidth="1"/>
-    <col min="7" max="7" width="9.5703125" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" customWidth="1"/>
-    <col min="9" max="9" width="8.28515625" customWidth="1"/>
-    <col min="10" max="10" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.42578125" style="21"/>
+    <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" customWidth="1"/>
+    <col min="7" max="7" width="9.5546875" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" customWidth="1"/>
+    <col min="9" max="9" width="8.33203125" customWidth="1"/>
+    <col min="10" max="10" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.44140625" customWidth="1"/>
+    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.44140625" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="53" t="s">
         <v>49</v>
       </c>
@@ -2536,7 +2606,7 @@
         <v>291359.89</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="98">
         <f>'detalle y gastos'!B7</f>
         <v>0</v>
@@ -2553,15 +2623,15 @@
       <c r="K2" s="102"/>
       <c r="L2" s="103"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="181" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="183" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="182"/>
-      <c r="C3" s="177" t="s">
+      <c r="B3" s="184"/>
+      <c r="C3" s="179" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="179" t="s">
+      <c r="D3" s="181" t="s">
         <v>56</v>
       </c>
       <c r="E3" s="7" t="s">
@@ -2570,52 +2640,52 @@
       <c r="F3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="177" t="s">
+      <c r="G3" s="179" t="s">
         <v>54</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="I3" s="175" t="s">
+      <c r="I3" s="177" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="185" t="s">
+      <c r="J3" s="187" t="s">
         <v>112</v>
       </c>
-      <c r="K3" s="177" t="s">
+      <c r="K3" s="179" t="s">
         <v>43</v>
       </c>
       <c r="L3" s="45" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="183"/>
-      <c r="B4" s="184"/>
-      <c r="C4" s="178"/>
-      <c r="D4" s="180"/>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="185"/>
+      <c r="B4" s="186"/>
+      <c r="C4" s="180"/>
+      <c r="D4" s="182"/>
       <c r="E4" s="58" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G4" s="178"/>
+      <c r="G4" s="180"/>
       <c r="H4" s="37">
         <v>0.04</v>
       </c>
-      <c r="I4" s="176"/>
-      <c r="J4" s="186"/>
-      <c r="K4" s="178"/>
+      <c r="I4" s="178"/>
+      <c r="J4" s="188"/>
+      <c r="K4" s="180"/>
       <c r="L4" s="38" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="173">
+    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="175">
         <v>1</v>
       </c>
-      <c r="B5" s="174"/>
+      <c r="B5" s="176"/>
       <c r="C5" s="111" t="s">
         <v>66</v>
       </c>
@@ -2651,11 +2721,11 @@
         <v>41619.622545752514</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A6" s="173">
+    <row r="6" spans="1:12" ht="27" x14ac:dyDescent="0.3">
+      <c r="A6" s="175">
         <v>2</v>
       </c>
-      <c r="B6" s="174"/>
+      <c r="B6" s="176"/>
       <c r="C6" s="111" t="s">
         <v>67</v>
       </c>
@@ -2693,11 +2763,11 @@
         <v>36242.744626240805</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A7" s="173">
+    <row r="7" spans="1:12" ht="27" x14ac:dyDescent="0.3">
+      <c r="A7" s="175">
         <v>3</v>
       </c>
-      <c r="B7" s="174"/>
+      <c r="B7" s="176"/>
       <c r="C7" s="111" t="s">
         <v>67</v>
       </c>
@@ -2735,11 +2805,11 @@
         <v>37973.684969585294</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A8" s="173">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="175">
         <v>4</v>
       </c>
-      <c r="B8" s="174"/>
+      <c r="B8" s="176"/>
       <c r="C8" s="111" t="s">
         <v>68</v>
       </c>
@@ -2777,11 +2847,11 @@
         <v>44818.016417140476</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="173">
+    <row r="9" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="175">
         <v>5</v>
       </c>
-      <c r="B9" s="174"/>
+      <c r="B9" s="176"/>
       <c r="C9" s="111" t="s">
         <v>69</v>
       </c>
@@ -2819,11 +2889,11 @@
         <v>37190.902148331101</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="173">
+    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="175">
         <v>6</v>
       </c>
-      <c r="B10" s="174"/>
+      <c r="B10" s="176"/>
       <c r="C10" s="111" t="s">
         <v>70</v>
       </c>
@@ -2859,11 +2929,11 @@
         <v>37412.073067986625</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="173">
+    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="175">
         <v>7</v>
       </c>
-      <c r="B11" s="174"/>
+      <c r="B11" s="176"/>
       <c r="C11" s="111" t="s">
         <v>71</v>
       </c>
@@ -2899,11 +2969,11 @@
         <v>54803.682602963214</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="173" t="s">
+    <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="175" t="s">
         <v>76</v>
       </c>
-      <c r="B12" s="174"/>
+      <c r="B12" s="176"/>
       <c r="C12" s="111" t="str">
         <f>C9</f>
         <v>Grand Jorge</v>
@@ -2939,11 +3009,11 @@
         <v>3904.2225260000005</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="173" t="s">
+    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="175" t="s">
         <v>77</v>
       </c>
-      <c r="B13" s="174"/>
+      <c r="B13" s="176"/>
       <c r="C13" s="111" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
@@ -2979,11 +3049,11 @@
         <v>3845.9505480000003</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="173" t="s">
+    <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="175" t="s">
         <v>78</v>
       </c>
-      <c r="B14" s="174"/>
+      <c r="B14" s="176"/>
       <c r="C14" s="59" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
@@ -3019,7 +3089,7 @@
         <v>3845.9505480000003</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="105" t="s">
         <v>11</v>
       </c>
@@ -3056,7 +3126,7 @@
         <v>301656.85000000003</v>
       </c>
     </row>
-    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="53" t="s">
         <v>50</v>
       </c>
@@ -3064,7 +3134,7 @@
         <v>7454</v>
       </c>
     </row>
-    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="27" t="s">
         <v>52</v>
       </c>
@@ -3082,7 +3152,7 @@
       <c r="K19" s="54"/>
       <c r="L19" s="31"/>
     </row>
-    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>0</v>
       </c>
@@ -3114,7 +3184,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -3140,7 +3210,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="11">
         <v>1</v>
       </c>
@@ -3174,7 +3244,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11">
         <v>2</v>
       </c>
@@ -3208,7 +3278,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="11">
         <v>3</v>
       </c>
@@ -3243,7 +3313,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11">
         <v>4</v>
       </c>
@@ -3274,7 +3344,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="11">
         <v>5</v>
       </c>
@@ -3305,7 +3375,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11">
         <v>6</v>
       </c>
@@ -3336,7 +3406,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="11">
         <v>7</v>
       </c>
@@ -3370,7 +3440,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="11">
         <v>8</v>
       </c>
@@ -3404,7 +3474,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="8" t="s">
         <v>11</v>
       </c>
@@ -3437,44 +3507,44 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="N31"/>
     </row>
-    <row r="32" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="187" t="s">
+      <c r="E32" s="189" t="s">
         <v>113</v>
       </c>
-      <c r="F32" s="188"/>
-      <c r="G32" s="188"/>
-      <c r="H32" s="188"/>
-      <c r="I32" s="188"/>
-      <c r="J32" s="188"/>
-      <c r="K32" s="189"/>
+      <c r="F32" s="190"/>
+      <c r="G32" s="190"/>
+      <c r="H32" s="190"/>
+      <c r="I32" s="190"/>
+      <c r="J32" s="190"/>
+      <c r="K32" s="191"/>
       <c r="L32" s="153"/>
       <c r="M32" s="154"/>
       <c r="N32"/>
     </row>
-    <row r="33" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
-      <c r="E33" s="190" t="s">
+      <c r="E33" s="192" t="s">
         <v>114</v>
       </c>
-      <c r="F33" s="188"/>
-      <c r="G33" s="188"/>
-      <c r="H33" s="188"/>
-      <c r="I33" s="188"/>
-      <c r="J33" s="188"/>
-      <c r="K33" s="189"/>
+      <c r="F33" s="190"/>
+      <c r="G33" s="190"/>
+      <c r="H33" s="190"/>
+      <c r="I33" s="190"/>
+      <c r="J33" s="190"/>
+      <c r="K33" s="191"/>
       <c r="L33" s="155"/>
       <c r="M33" s="156"/>
       <c r="N33"/>
     </row>
-    <row r="34" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="153"/>
@@ -3491,7 +3561,7 @@
       <c r="M34" s="156"/>
       <c r="N34"/>
     </row>
-    <row r="35" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="155" t="s">
@@ -3507,7 +3577,7 @@
       <c r="M35" s="156"/>
       <c r="N35"/>
     </row>
-    <row r="36" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="159"/>
@@ -3521,23 +3591,23 @@
       <c r="M36" s="156"/>
       <c r="N36"/>
     </row>
-    <row r="37" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="191" t="s">
+      <c r="E37" s="193" t="s">
         <v>50</v>
       </c>
-      <c r="F37" s="192"/>
-      <c r="G37" s="192"/>
-      <c r="H37" s="192"/>
-      <c r="I37" s="192"/>
-      <c r="J37" s="192"/>
-      <c r="K37" s="193"/>
+      <c r="F37" s="194"/>
+      <c r="G37" s="194"/>
+      <c r="H37" s="194"/>
+      <c r="I37" s="194"/>
+      <c r="J37" s="194"/>
+      <c r="K37" s="195"/>
       <c r="L37" s="155"/>
       <c r="M37" s="156"/>
       <c r="N37"/>
     </row>
-    <row r="38" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="155"/>
@@ -3551,7 +3621,7 @@
       <c r="M38" s="156"/>
       <c r="N38"/>
     </row>
-    <row r="39" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="155" t="s">
@@ -3570,13 +3640,13 @@
         <v>45674</v>
       </c>
       <c r="K39" s="156"/>
-      <c r="L39" s="194" t="s">
+      <c r="L39" s="196" t="s">
         <v>118</v>
       </c>
-      <c r="M39" s="195"/>
+      <c r="M39" s="197"/>
       <c r="N39"/>
     </row>
-    <row r="40" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="155" t="s">
@@ -3594,7 +3664,7 @@
       <c r="M40" s="156"/>
       <c r="N40"/>
     </row>
-    <row r="41" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="155"/>
@@ -3604,11 +3674,11 @@
       <c r="I41" s="158"/>
       <c r="J41" s="158"/>
       <c r="K41" s="156"/>
-      <c r="L41" s="196"/>
-      <c r="M41" s="195"/>
+      <c r="L41" s="198"/>
+      <c r="M41" s="197"/>
       <c r="N41"/>
     </row>
-    <row r="42" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="155" t="s">
@@ -3627,7 +3697,7 @@
       <c r="M42" s="156"/>
       <c r="N42"/>
     </row>
-    <row r="43" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="165" t="s">
@@ -3646,7 +3716,7 @@
       <c r="M43" s="156"/>
       <c r="N43"/>
     </row>
-    <row r="44" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="165" t="s">
@@ -3665,7 +3735,7 @@
       <c r="M44" s="156"/>
       <c r="N44"/>
     </row>
-    <row r="45" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="165"/>
@@ -3679,7 +3749,7 @@
       <c r="M45" s="156"/>
       <c r="N45"/>
     </row>
-    <row r="46" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="165"/>
@@ -3693,7 +3763,7 @@
       <c r="M46" s="156"/>
       <c r="N46"/>
     </row>
-    <row r="47" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="F47" s="158"/>
@@ -3706,7 +3776,7 @@
       <c r="M47" s="156"/>
       <c r="N47"/>
     </row>
-    <row r="48" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="165"/>
@@ -3720,7 +3790,7 @@
       <c r="M48" s="156"/>
       <c r="N48"/>
     </row>
-    <row r="49" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="155"/>
@@ -3734,7 +3804,7 @@
       <c r="M49" s="156"/>
       <c r="N49"/>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="155" t="s">
@@ -3753,7 +3823,7 @@
       <c r="M50" s="156"/>
       <c r="N50"/>
     </row>
-    <row r="51" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="155"/>
@@ -3767,58 +3837,58 @@
       <c r="M51" s="167"/>
       <c r="N51"/>
     </row>
-    <row r="52" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
-      <c r="E52" s="197" t="s">
+      <c r="E52" s="199" t="s">
         <v>121</v>
       </c>
-      <c r="F52" s="198"/>
-      <c r="G52" s="198"/>
-      <c r="H52" s="198"/>
-      <c r="I52" s="198"/>
-      <c r="J52" s="199">
+      <c r="F52" s="200"/>
+      <c r="G52" s="200"/>
+      <c r="H52" s="200"/>
+      <c r="I52" s="200"/>
+      <c r="J52" s="201">
         <f>SUM(J42:J51)</f>
         <v>38049.484969585297</v>
       </c>
-      <c r="K52" s="189"/>
+      <c r="K52" s="191"/>
       <c r="L52" s="168"/>
       <c r="M52" s="169"/>
       <c r="N52"/>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="N53"/>
     </row>
-    <row r="55" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="56" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E56" s="187" t="s">
+    <row r="55" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="56" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E56" s="189" t="s">
         <v>113</v>
       </c>
-      <c r="F56" s="188"/>
-      <c r="G56" s="188"/>
-      <c r="H56" s="188"/>
-      <c r="I56" s="188"/>
-      <c r="J56" s="188"/>
-      <c r="K56" s="189"/>
+      <c r="F56" s="190"/>
+      <c r="G56" s="190"/>
+      <c r="H56" s="190"/>
+      <c r="I56" s="190"/>
+      <c r="J56" s="190"/>
+      <c r="K56" s="191"/>
       <c r="L56" s="153"/>
       <c r="M56" s="154"/>
     </row>
-    <row r="57" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E57" s="190" t="s">
+    <row r="57" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E57" s="192" t="s">
         <v>114</v>
       </c>
-      <c r="F57" s="188"/>
-      <c r="G57" s="188"/>
-      <c r="H57" s="188"/>
-      <c r="I57" s="188"/>
-      <c r="J57" s="188"/>
-      <c r="K57" s="189"/>
+      <c r="F57" s="190"/>
+      <c r="G57" s="190"/>
+      <c r="H57" s="190"/>
+      <c r="I57" s="190"/>
+      <c r="J57" s="190"/>
+      <c r="K57" s="191"/>
       <c r="L57" s="155"/>
       <c r="M57" s="156"/>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E58" s="153"/>
       <c r="F58" s="157"/>
       <c r="G58" s="157"/>
@@ -3832,7 +3902,7 @@
       <c r="L58" s="155"/>
       <c r="M58" s="156"/>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E59" s="155" t="s">
         <v>115</v>
       </c>
@@ -3845,7 +3915,7 @@
       <c r="L59" s="155"/>
       <c r="M59" s="156"/>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E60" s="159"/>
       <c r="F60" s="160"/>
       <c r="G60" s="160"/>
@@ -3856,20 +3926,20 @@
       <c r="L60" s="155"/>
       <c r="M60" s="156"/>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="E61" s="191" t="s">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="E61" s="193" t="s">
         <v>50</v>
       </c>
-      <c r="F61" s="192"/>
-      <c r="G61" s="192"/>
-      <c r="H61" s="192"/>
-      <c r="I61" s="192"/>
-      <c r="J61" s="192"/>
-      <c r="K61" s="193"/>
+      <c r="F61" s="194"/>
+      <c r="G61" s="194"/>
+      <c r="H61" s="194"/>
+      <c r="I61" s="194"/>
+      <c r="J61" s="194"/>
+      <c r="K61" s="195"/>
       <c r="L61" s="155"/>
       <c r="M61" s="156"/>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E62" s="155"/>
       <c r="F62" s="158"/>
       <c r="G62" s="158"/>
@@ -3880,7 +3950,7 @@
       <c r="L62" s="155"/>
       <c r="M62" s="156"/>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E63" s="155" t="s">
         <v>116</v>
       </c>
@@ -3897,12 +3967,12 @@
         <v>45674</v>
       </c>
       <c r="K63" s="156"/>
-      <c r="L63" s="194" t="s">
+      <c r="L63" s="196" t="s">
         <v>118</v>
       </c>
-      <c r="M63" s="195"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="M63" s="197"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E64" s="155" t="s">
         <v>119</v>
       </c>
@@ -3917,7 +3987,7 @@
       <c r="L64" s="155"/>
       <c r="M64" s="156"/>
     </row>
-    <row r="65" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E65" s="155"/>
       <c r="F65" s="158"/>
       <c r="G65" s="158"/>
@@ -3925,10 +3995,10 @@
       <c r="I65" s="158"/>
       <c r="J65" s="158"/>
       <c r="K65" s="156"/>
-      <c r="L65" s="196"/>
-      <c r="M65" s="195"/>
-    </row>
-    <row r="66" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="L65" s="198"/>
+      <c r="M65" s="197"/>
+    </row>
+    <row r="66" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E66" s="155" t="s">
         <v>49</v>
       </c>
@@ -3944,7 +4014,7 @@
       <c r="L66" s="155"/>
       <c r="M66" s="156"/>
     </row>
-    <row r="67" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E67" s="165" t="s">
         <v>120</v>
       </c>
@@ -3960,7 +4030,7 @@
       <c r="L67" s="155"/>
       <c r="M67" s="156"/>
     </row>
-    <row r="68" spans="5:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="5:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E68" s="165" t="s">
         <v>122</v>
       </c>
@@ -3976,7 +4046,7 @@
       <c r="L68" s="155"/>
       <c r="M68" s="156"/>
     </row>
-    <row r="69" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="E69" s="165"/>
       <c r="F69" s="158"/>
       <c r="G69" s="158"/>
@@ -3987,7 +4057,7 @@
       <c r="L69" s="155"/>
       <c r="M69" s="156"/>
     </row>
-    <row r="70" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="E70" s="165"/>
       <c r="F70" s="158"/>
       <c r="G70" s="158"/>
@@ -3998,7 +4068,7 @@
       <c r="L70" s="155"/>
       <c r="M70" s="156"/>
     </row>
-    <row r="71" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="F71" s="158"/>
       <c r="G71" s="158"/>
       <c r="H71" s="158"/>
@@ -4008,7 +4078,7 @@
       <c r="L71" s="155"/>
       <c r="M71" s="156"/>
     </row>
-    <row r="72" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="E72" s="165"/>
       <c r="F72" s="158"/>
       <c r="G72" s="158"/>
@@ -4019,7 +4089,7 @@
       <c r="L72" s="155"/>
       <c r="M72" s="156"/>
     </row>
-    <row r="73" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="E73" s="155"/>
       <c r="F73" s="158"/>
       <c r="G73" s="158"/>
@@ -4030,7 +4100,7 @@
       <c r="L73" s="155"/>
       <c r="M73" s="156"/>
     </row>
-    <row r="74" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="E74" s="155"/>
       <c r="F74" s="158"/>
       <c r="G74" s="158"/>
@@ -4041,7 +4111,7 @@
       <c r="L74" s="155"/>
       <c r="M74" s="156"/>
     </row>
-    <row r="75" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E75" s="155"/>
       <c r="F75" s="158"/>
       <c r="G75" s="158"/>
@@ -4052,50 +4122,50 @@
       <c r="L75" s="166"/>
       <c r="M75" s="167"/>
     </row>
-    <row r="76" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E76" s="197" t="s">
+    <row r="76" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E76" s="199" t="s">
         <v>121</v>
       </c>
-      <c r="F76" s="198"/>
-      <c r="G76" s="198"/>
-      <c r="H76" s="198"/>
-      <c r="I76" s="198"/>
-      <c r="J76" s="199">
+      <c r="F76" s="200"/>
+      <c r="G76" s="200"/>
+      <c r="H76" s="200"/>
+      <c r="I76" s="200"/>
+      <c r="J76" s="201">
         <f>SUM(J66:J75)</f>
         <v>44818.016417140476</v>
       </c>
-      <c r="K76" s="189"/>
+      <c r="K76" s="191"/>
       <c r="L76" s="168"/>
       <c r="M76" s="169"/>
     </row>
-    <row r="82" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="83" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E83" s="187" t="s">
+    <row r="82" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="83" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E83" s="189" t="s">
         <v>113</v>
       </c>
-      <c r="F83" s="188"/>
-      <c r="G83" s="188"/>
-      <c r="H83" s="188"/>
-      <c r="I83" s="188"/>
-      <c r="J83" s="188"/>
-      <c r="K83" s="189"/>
+      <c r="F83" s="190"/>
+      <c r="G83" s="190"/>
+      <c r="H83" s="190"/>
+      <c r="I83" s="190"/>
+      <c r="J83" s="190"/>
+      <c r="K83" s="191"/>
       <c r="L83" s="153"/>
       <c r="M83" s="154"/>
     </row>
-    <row r="84" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E84" s="190" t="s">
+    <row r="84" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E84" s="192" t="s">
         <v>114</v>
       </c>
-      <c r="F84" s="188"/>
-      <c r="G84" s="188"/>
-      <c r="H84" s="188"/>
-      <c r="I84" s="188"/>
-      <c r="J84" s="188"/>
-      <c r="K84" s="189"/>
+      <c r="F84" s="190"/>
+      <c r="G84" s="190"/>
+      <c r="H84" s="190"/>
+      <c r="I84" s="190"/>
+      <c r="J84" s="190"/>
+      <c r="K84" s="191"/>
       <c r="L84" s="155"/>
       <c r="M84" s="156"/>
     </row>
-    <row r="85" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E85" s="153"/>
       <c r="F85" s="157"/>
       <c r="G85" s="157"/>
@@ -4109,7 +4179,7 @@
       <c r="L85" s="155"/>
       <c r="M85" s="156"/>
     </row>
-    <row r="86" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E86" s="155" t="s">
         <v>115</v>
       </c>
@@ -4122,7 +4192,7 @@
       <c r="L86" s="155"/>
       <c r="M86" s="156"/>
     </row>
-    <row r="87" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="87" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E87" s="159"/>
       <c r="F87" s="160"/>
       <c r="G87" s="160"/>
@@ -4133,20 +4203,20 @@
       <c r="L87" s="155"/>
       <c r="M87" s="156"/>
     </row>
-    <row r="88" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E88" s="191" t="s">
+    <row r="88" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E88" s="193" t="s">
         <v>50</v>
       </c>
-      <c r="F88" s="192"/>
-      <c r="G88" s="192"/>
-      <c r="H88" s="192"/>
-      <c r="I88" s="192"/>
-      <c r="J88" s="192"/>
-      <c r="K88" s="193"/>
+      <c r="F88" s="194"/>
+      <c r="G88" s="194"/>
+      <c r="H88" s="194"/>
+      <c r="I88" s="194"/>
+      <c r="J88" s="194"/>
+      <c r="K88" s="195"/>
       <c r="L88" s="155"/>
       <c r="M88" s="156"/>
     </row>
-    <row r="89" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="89" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E89" s="155"/>
       <c r="F89" s="158"/>
       <c r="G89" s="158"/>
@@ -4157,7 +4227,7 @@
       <c r="L89" s="155"/>
       <c r="M89" s="156"/>
     </row>
-    <row r="90" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="90" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E90" s="155" t="s">
         <v>116</v>
       </c>
@@ -4174,12 +4244,12 @@
         <v>45674</v>
       </c>
       <c r="K90" s="156"/>
-      <c r="L90" s="194" t="s">
+      <c r="L90" s="196" t="s">
         <v>118</v>
       </c>
-      <c r="M90" s="195"/>
-    </row>
-    <row r="91" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="M90" s="197"/>
+    </row>
+    <row r="91" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E91" s="155" t="s">
         <v>119</v>
       </c>
@@ -4194,7 +4264,7 @@
       <c r="L91" s="155"/>
       <c r="M91" s="156"/>
     </row>
-    <row r="92" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="92" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E92" s="155"/>
       <c r="F92" s="158"/>
       <c r="G92" s="158"/>
@@ -4202,10 +4272,10 @@
       <c r="I92" s="158"/>
       <c r="J92" s="158"/>
       <c r="K92" s="156"/>
-      <c r="L92" s="196"/>
-      <c r="M92" s="195"/>
-    </row>
-    <row r="93" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="L92" s="198"/>
+      <c r="M92" s="197"/>
+    </row>
+    <row r="93" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E93" s="155" t="s">
         <v>49</v>
       </c>
@@ -4221,7 +4291,7 @@
       <c r="L93" s="155"/>
       <c r="M93" s="156"/>
     </row>
-    <row r="94" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="94" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E94" s="165" t="s">
         <v>120</v>
       </c>
@@ -4237,7 +4307,7 @@
       <c r="L94" s="155"/>
       <c r="M94" s="156"/>
     </row>
-    <row r="95" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="95" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E95" s="165" t="s">
         <v>123</v>
       </c>
@@ -4252,7 +4322,7 @@
       <c r="L95" s="155"/>
       <c r="M95" s="156"/>
     </row>
-    <row r="96" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E96" s="165"/>
       <c r="F96" s="158"/>
       <c r="G96" s="158"/>
@@ -4263,7 +4333,7 @@
       <c r="L96" s="155"/>
       <c r="M96" s="156"/>
     </row>
-    <row r="97" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E97" s="165"/>
       <c r="F97" s="158"/>
       <c r="G97" s="158"/>
@@ -4274,7 +4344,7 @@
       <c r="L97" s="155"/>
       <c r="M97" s="156"/>
     </row>
-    <row r="98" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F98" s="158"/>
       <c r="G98" s="158"/>
       <c r="H98" s="158"/>
@@ -4284,7 +4354,7 @@
       <c r="L98" s="155"/>
       <c r="M98" s="156"/>
     </row>
-    <row r="99" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E99" s="165"/>
       <c r="F99" s="158"/>
       <c r="G99" s="158"/>
@@ -4295,7 +4365,7 @@
       <c r="L99" s="155"/>
       <c r="M99" s="156"/>
     </row>
-    <row r="100" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E100" s="155"/>
       <c r="F100" s="158"/>
       <c r="G100" s="158"/>
@@ -4306,7 +4376,7 @@
       <c r="L100" s="155"/>
       <c r="M100" s="156"/>
     </row>
-    <row r="101" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E101" s="155"/>
       <c r="F101" s="158"/>
       <c r="G101" s="158"/>
@@ -4317,7 +4387,7 @@
       <c r="L101" s="155"/>
       <c r="M101" s="156"/>
     </row>
-    <row r="102" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E102" s="155"/>
       <c r="F102" s="158"/>
       <c r="G102" s="158"/>
@@ -4328,50 +4398,50 @@
       <c r="L102" s="166"/>
       <c r="M102" s="167"/>
     </row>
-    <row r="103" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E103" s="197" t="s">
+    <row r="103" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E103" s="199" t="s">
         <v>121</v>
       </c>
-      <c r="F103" s="198"/>
-      <c r="G103" s="198"/>
-      <c r="H103" s="198"/>
-      <c r="I103" s="198"/>
-      <c r="J103" s="199">
+      <c r="F103" s="200"/>
+      <c r="G103" s="200"/>
+      <c r="H103" s="200"/>
+      <c r="I103" s="200"/>
+      <c r="J103" s="201">
         <f>SUM(J93:J102)</f>
         <v>37435.963067986624</v>
       </c>
-      <c r="K103" s="189"/>
+      <c r="K103" s="191"/>
       <c r="L103" s="168"/>
       <c r="M103" s="169"/>
     </row>
-    <row r="107" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="108" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E108" s="187" t="s">
+    <row r="107" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="108" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E108" s="189" t="s">
         <v>113</v>
       </c>
-      <c r="F108" s="188"/>
-      <c r="G108" s="188"/>
-      <c r="H108" s="188"/>
-      <c r="I108" s="188"/>
-      <c r="J108" s="188"/>
-      <c r="K108" s="189"/>
+      <c r="F108" s="190"/>
+      <c r="G108" s="190"/>
+      <c r="H108" s="190"/>
+      <c r="I108" s="190"/>
+      <c r="J108" s="190"/>
+      <c r="K108" s="191"/>
       <c r="L108" s="153"/>
       <c r="M108" s="154"/>
     </row>
-    <row r="109" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E109" s="190" t="s">
+    <row r="109" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E109" s="192" t="s">
         <v>114</v>
       </c>
-      <c r="F109" s="188"/>
-      <c r="G109" s="188"/>
-      <c r="H109" s="188"/>
-      <c r="I109" s="188"/>
-      <c r="J109" s="188"/>
-      <c r="K109" s="189"/>
+      <c r="F109" s="190"/>
+      <c r="G109" s="190"/>
+      <c r="H109" s="190"/>
+      <c r="I109" s="190"/>
+      <c r="J109" s="190"/>
+      <c r="K109" s="191"/>
       <c r="L109" s="155"/>
       <c r="M109" s="156"/>
     </row>
-    <row r="110" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="110" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E110" s="153"/>
       <c r="F110" s="157"/>
       <c r="G110" s="157"/>
@@ -4385,7 +4455,7 @@
       <c r="L110" s="155"/>
       <c r="M110" s="156"/>
     </row>
-    <row r="111" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="111" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E111" s="155" t="s">
         <v>115</v>
       </c>
@@ -4398,7 +4468,7 @@
       <c r="L111" s="155"/>
       <c r="M111" s="156"/>
     </row>
-    <row r="112" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="112" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E112" s="159"/>
       <c r="F112" s="160"/>
       <c r="G112" s="160"/>
@@ -4409,20 +4479,20 @@
       <c r="L112" s="155"/>
       <c r="M112" s="156"/>
     </row>
-    <row r="113" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E113" s="191" t="s">
+    <row r="113" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E113" s="193" t="s">
         <v>50</v>
       </c>
-      <c r="F113" s="192"/>
-      <c r="G113" s="192"/>
-      <c r="H113" s="192"/>
-      <c r="I113" s="192"/>
-      <c r="J113" s="192"/>
-      <c r="K113" s="193"/>
+      <c r="F113" s="194"/>
+      <c r="G113" s="194"/>
+      <c r="H113" s="194"/>
+      <c r="I113" s="194"/>
+      <c r="J113" s="194"/>
+      <c r="K113" s="195"/>
       <c r="L113" s="155"/>
       <c r="M113" s="156"/>
     </row>
-    <row r="114" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E114" s="155"/>
       <c r="F114" s="158"/>
       <c r="G114" s="158"/>
@@ -4433,7 +4503,7 @@
       <c r="L114" s="155"/>
       <c r="M114" s="156"/>
     </row>
-    <row r="115" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E115" s="155" t="s">
         <v>116</v>
       </c>
@@ -4450,12 +4520,12 @@
         <v>45674</v>
       </c>
       <c r="K115" s="156"/>
-      <c r="L115" s="194" t="s">
+      <c r="L115" s="196" t="s">
         <v>118</v>
       </c>
-      <c r="M115" s="195"/>
-    </row>
-    <row r="116" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="M115" s="197"/>
+    </row>
+    <row r="116" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E116" s="155" t="s">
         <v>119</v>
       </c>
@@ -4470,7 +4540,7 @@
       <c r="L116" s="155"/>
       <c r="M116" s="156"/>
     </row>
-    <row r="117" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E117" s="155"/>
       <c r="F117" s="158"/>
       <c r="G117" s="158"/>
@@ -4478,10 +4548,10 @@
       <c r="I117" s="158"/>
       <c r="J117" s="158"/>
       <c r="K117" s="156"/>
-      <c r="L117" s="196"/>
-      <c r="M117" s="195"/>
-    </row>
-    <row r="118" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="L117" s="198"/>
+      <c r="M117" s="197"/>
+    </row>
+    <row r="118" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E118" s="155" t="s">
         <v>49</v>
       </c>
@@ -4497,7 +4567,7 @@
       <c r="L118" s="155"/>
       <c r="M118" s="156"/>
     </row>
-    <row r="119" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="119" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E119" s="165" t="s">
         <v>120</v>
       </c>
@@ -4513,7 +4583,7 @@
       <c r="L119" s="155"/>
       <c r="M119" s="156"/>
     </row>
-    <row r="120" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="120" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E120" s="165" t="s">
         <v>124</v>
       </c>
@@ -4529,7 +4599,7 @@
       <c r="L120" s="155"/>
       <c r="M120" s="156"/>
     </row>
-    <row r="121" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E121" s="165"/>
       <c r="F121" s="158"/>
       <c r="G121" s="158"/>
@@ -4540,7 +4610,7 @@
       <c r="L121" s="155"/>
       <c r="M121" s="156"/>
     </row>
-    <row r="122" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E122" s="165"/>
       <c r="F122" s="158"/>
       <c r="G122" s="158"/>
@@ -4551,7 +4621,7 @@
       <c r="L122" s="155"/>
       <c r="M122" s="156"/>
     </row>
-    <row r="123" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F123" s="158"/>
       <c r="G123" s="158"/>
       <c r="H123" s="158"/>
@@ -4561,7 +4631,7 @@
       <c r="L123" s="155"/>
       <c r="M123" s="156"/>
     </row>
-    <row r="124" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E124" s="165"/>
       <c r="F124" s="158"/>
       <c r="G124" s="158"/>
@@ -4572,7 +4642,7 @@
       <c r="L124" s="155"/>
       <c r="M124" s="156"/>
     </row>
-    <row r="125" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E125" s="155"/>
       <c r="F125" s="158"/>
       <c r="G125" s="158"/>
@@ -4583,7 +4653,7 @@
       <c r="L125" s="155"/>
       <c r="M125" s="156"/>
     </row>
-    <row r="126" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E126" s="155"/>
       <c r="F126" s="158"/>
       <c r="G126" s="158"/>
@@ -4594,7 +4664,7 @@
       <c r="L126" s="155"/>
       <c r="M126" s="156"/>
     </row>
-    <row r="127" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E127" s="155"/>
       <c r="F127" s="158"/>
       <c r="G127" s="158"/>
@@ -4605,19 +4675,19 @@
       <c r="L127" s="166"/>
       <c r="M127" s="167"/>
     </row>
-    <row r="128" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E128" s="197" t="s">
+    <row r="128" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E128" s="199" t="s">
         <v>121</v>
       </c>
-      <c r="F128" s="198"/>
-      <c r="G128" s="198"/>
-      <c r="H128" s="198"/>
-      <c r="I128" s="198"/>
-      <c r="J128" s="199">
+      <c r="F128" s="200"/>
+      <c r="G128" s="200"/>
+      <c r="H128" s="200"/>
+      <c r="I128" s="200"/>
+      <c r="J128" s="201">
         <f>SUM(J118:J127)</f>
         <v>41567.282545752518</v>
       </c>
-      <c r="K128" s="189"/>
+      <c r="K128" s="191"/>
       <c r="L128" s="168"/>
       <c r="M128" s="169"/>
     </row>
@@ -4678,16 +4748,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="6" max="7" width="15.42578125" customWidth="1"/>
-    <col min="8" max="8" width="18.28515625" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" customWidth="1"/>
-    <col min="10" max="10" width="22.5703125" customWidth="1"/>
-    <col min="11" max="11" width="13.85546875" customWidth="1"/>
+    <col min="6" max="7" width="15.44140625" customWidth="1"/>
+    <col min="8" max="8" width="18.33203125" customWidth="1"/>
+    <col min="9" max="9" width="13.5546875" customWidth="1"/>
+    <col min="10" max="10" width="22.5546875" customWidth="1"/>
+    <col min="11" max="11" width="13.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="B1" s="112" t="s">
         <v>81</v>
       </c>
@@ -4707,12 +4777,12 @@
       <c r="K1" s="115"/>
       <c r="L1" s="116"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="H2" s="117"/>
       <c r="I2" s="117"/>
       <c r="J2" s="117"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B3" s="118" t="s">
         <v>84</v>
       </c>
@@ -4739,7 +4809,7 @@
       <c r="K3" s="5"/>
       <c r="M3" s="120"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B4" s="118"/>
       <c r="C4" s="112" t="s">
         <v>90</v>
@@ -4756,7 +4826,7 @@
       <c r="I4" s="121"/>
       <c r="J4" s="121"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>92</v>
       </c>
@@ -4789,7 +4859,7 @@
       <c r="L5" s="123"/>
       <c r="M5" s="124"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>93</v>
       </c>
@@ -4822,7 +4892,7 @@
       <c r="L6" s="123"/>
       <c r="M6" s="124"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>94</v>
       </c>
@@ -4854,7 +4924,7 @@
       <c r="L7" s="123"/>
       <c r="M7" s="124"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>95</v>
       </c>
@@ -4887,7 +4957,7 @@
       <c r="L8" s="123"/>
       <c r="M8" s="124"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>96</v>
       </c>
@@ -4920,7 +4990,7 @@
       <c r="L9" s="123"/>
       <c r="M9" s="124"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>97</v>
       </c>
@@ -4953,7 +5023,7 @@
       <c r="L10" s="123"/>
       <c r="M10" s="124"/>
     </row>
-    <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>98</v>
       </c>
@@ -4986,7 +5056,7 @@
       <c r="L11" s="123"/>
       <c r="M11" s="124"/>
     </row>
-    <row r="12" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="126"/>
       <c r="C12" s="127">
         <f>SUM(C5:C11)</f>
@@ -5014,13 +5084,13 @@
       <c r="K12" s="126"/>
       <c r="L12" s="129"/>
     </row>
-    <row r="13" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C13" s="130"/>
       <c r="H13" s="118"/>
       <c r="I13" s="118"/>
       <c r="J13" s="118"/>
     </row>
-    <row r="14" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>99</v>
       </c>
@@ -5032,7 +5102,7 @@
       <c r="I14" s="118"/>
       <c r="J14" s="118"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>100</v>
       </c>
@@ -5040,7 +5110,7 @@
       <c r="I15" s="118"/>
       <c r="J15" s="118"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B16" s="118"/>
       <c r="C16" s="112"/>
       <c r="D16" s="112"/>
@@ -5051,7 +5121,7 @@
       <c r="J16" s="112"/>
       <c r="K16" s="5"/>
     </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B17" s="118"/>
       <c r="C17" s="112"/>
       <c r="D17" s="112"/>
@@ -5061,12 +5131,12 @@
       <c r="I17" s="121"/>
       <c r="J17" s="121"/>
     </row>
-    <row r="18" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H18" s="118"/>
       <c r="I18" s="118"/>
       <c r="J18" s="118"/>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C19" s="132"/>
       <c r="D19" s="133"/>
       <c r="E19" s="133"/>
@@ -5079,7 +5149,7 @@
       <c r="L19" s="133"/>
       <c r="M19" s="135"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C20" s="136"/>
       <c r="E20" t="s">
         <v>101</v>
@@ -5095,7 +5165,7 @@
       </c>
       <c r="M20" s="138"/>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C21" s="136"/>
       <c r="D21" t="s">
         <v>103</v>
@@ -5117,7 +5187,7 @@
       </c>
       <c r="M21" s="138"/>
     </row>
-    <row r="22" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C22" s="139"/>
       <c r="D22" s="140"/>
       <c r="E22" s="140"/>
@@ -5130,16 +5200,16 @@
       <c r="L22" s="140"/>
       <c r="M22" s="141"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K25" s="142" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:13" x14ac:dyDescent="0.3">
       <c r="G26" s="5"/>
       <c r="K26" s="120"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.3">
       <c r="I27" t="s">
         <v>107</v>
       </c>
@@ -5150,7 +5220,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:13" x14ac:dyDescent="0.3">
       <c r="G28" s="5"/>
       <c r="H28" s="5" t="s">
         <v>97</v>
@@ -5166,7 +5236,7 @@
         <v>45829</v>
       </c>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:13" x14ac:dyDescent="0.3">
       <c r="J31" t="s">
         <v>109</v>
       </c>
@@ -5174,7 +5244,7 @@
         <v>117067</v>
       </c>
     </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:13" x14ac:dyDescent="0.3">
       <c r="J32" t="s">
         <v>110</v>
       </c>
@@ -5182,7 +5252,7 @@
         <v>-55000</v>
       </c>
     </row>
-    <row r="33" spans="10:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J33" s="120" t="s">
         <v>111</v>
       </c>
@@ -5190,7 +5260,7 @@
         <v>43965</v>
       </c>
     </row>
-    <row r="34" spans="10:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K34" s="114">
         <f>SUM(K31:K33)</f>
         <v>106032</v>
@@ -5205,39 +5275,39 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:P14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.109375" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="12" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="10.28515625" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" customWidth="1"/>
-    <col min="9" max="9" width="0.140625" customWidth="1"/>
+    <col min="6" max="6" width="10.33203125" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="11.109375" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" customWidth="1"/>
+    <col min="9" max="9" width="0.109375" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="0.140625" customWidth="1"/>
+    <col min="11" max="11" width="0.109375" customWidth="1"/>
     <col min="12" max="13" width="12" customWidth="1"/>
     <col min="14" max="14" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="D1" s="56">
         <v>50000</v>
       </c>
-      <c r="H1" s="204">
+      <c r="H1" s="206">
         <v>250000</v>
       </c>
-      <c r="I1" s="204"/>
-      <c r="J1" s="204"/>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I1" s="206"/>
+      <c r="J1" s="206"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="53" t="s">
         <v>50</v>
       </c>
       <c r="B2" s="1"/>
       <c r="P2" s="21"/>
     </row>
-    <row r="3" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="27" t="s">
         <v>57</v>
       </c>
@@ -5260,7 +5330,7 @@
       <c r="N3" s="31"/>
       <c r="P3" s="21"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
@@ -5292,18 +5362,18 @@
         <v>54</v>
       </c>
       <c r="K4" s="68"/>
-      <c r="L4" s="202" t="s">
+      <c r="L4" s="204" t="s">
         <v>61</v>
       </c>
       <c r="M4" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="N4" s="200" t="s">
+      <c r="N4" s="202" t="s">
         <v>55</v>
       </c>
       <c r="P4" s="21"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -5327,14 +5397,14 @@
         <v>60</v>
       </c>
       <c r="K5" s="58"/>
-      <c r="L5" s="203"/>
+      <c r="L5" s="205"/>
       <c r="M5" s="82" t="s">
         <v>62</v>
       </c>
-      <c r="N5" s="201"/>
+      <c r="N5" s="203"/>
       <c r="P5" s="21"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
         <v>1</v>
       </c>
@@ -5382,7 +5452,7 @@
       </c>
       <c r="P6" s="21"/>
     </row>
-    <row r="7" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11">
         <v>2</v>
       </c>
@@ -5430,7 +5500,7 @@
       </c>
       <c r="P7" s="21"/>
     </row>
-    <row r="8" spans="1:16" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" ht="27" x14ac:dyDescent="0.3">
       <c r="A8" s="11">
         <v>3</v>
       </c>
@@ -5478,7 +5548,7 @@
       </c>
       <c r="P8" s="21"/>
     </row>
-    <row r="9" spans="1:16" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" ht="27" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
         <v>4</v>
       </c>
@@ -5526,7 +5596,7 @@
       </c>
       <c r="P9" s="21"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
         <v>5</v>
       </c>
@@ -5574,7 +5644,7 @@
       </c>
       <c r="P10" s="21"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="11">
         <v>6</v>
       </c>
@@ -5622,7 +5692,7 @@
       </c>
       <c r="P11" s="21"/>
     </row>
-    <row r="12" spans="1:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11">
         <v>7</v>
       </c>
@@ -5670,7 +5740,7 @@
       </c>
       <c r="P12" s="21"/>
     </row>
-    <row r="13" spans="1:16" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" ht="27" x14ac:dyDescent="0.3">
       <c r="A13" s="11">
         <v>8</v>
       </c>
@@ -5718,7 +5788,7 @@
       </c>
       <c r="P13" s="21"/>
     </row>
-    <row r="14" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
         <v>11</v>
       </c>
@@ -5776,4 +5846,2193 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="85" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{434C3368-DE46-4844-AE9C-0C1B6FC5250E}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:N128"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="1.77734375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" customWidth="1"/>
+    <col min="7" max="7" width="9.5546875" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" customWidth="1"/>
+    <col min="9" max="9" width="8.33203125" customWidth="1"/>
+    <col min="10" max="10" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.44140625" customWidth="1"/>
+    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.5546875" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="211" t="s">
+        <v>130</v>
+      </c>
+      <c r="B1" s="211"/>
+      <c r="C1" s="211"/>
+      <c r="D1" s="210">
+        <f>350535.51+12600</f>
+        <v>363135.51</v>
+      </c>
+      <c r="E1" s="210"/>
+      <c r="F1" s="211" t="s">
+        <v>134</v>
+      </c>
+      <c r="G1" s="211"/>
+      <c r="H1" s="211"/>
+      <c r="I1" s="207">
+        <v>800000</v>
+      </c>
+      <c r="J1" s="207"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="98"/>
+      <c r="B2" s="99"/>
+      <c r="C2" s="100"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="102"/>
+      <c r="K2" s="102"/>
+      <c r="L2" s="103"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="183" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="184"/>
+      <c r="C3" s="179" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="181" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="179" t="s">
+        <v>129</v>
+      </c>
+      <c r="H3" s="179" t="s">
+        <v>45</v>
+      </c>
+      <c r="I3" s="177" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="181" t="s">
+        <v>132</v>
+      </c>
+      <c r="K3" s="173" t="s">
+        <v>131</v>
+      </c>
+      <c r="L3" s="208" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="185"/>
+      <c r="B4" s="186"/>
+      <c r="C4" s="180"/>
+      <c r="D4" s="182"/>
+      <c r="E4" s="58" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="G4" s="180"/>
+      <c r="H4" s="180"/>
+      <c r="I4" s="178"/>
+      <c r="J4" s="182"/>
+      <c r="K4" s="174" t="s">
+        <v>133</v>
+      </c>
+      <c r="L4" s="209"/>
+    </row>
+    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="175">
+        <v>1</v>
+      </c>
+      <c r="B5" s="176"/>
+      <c r="C5" s="111" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="59"/>
+      <c r="E5" s="150">
+        <v>0</v>
+      </c>
+      <c r="F5" s="151">
+        <f>E5</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="152">
+        <f>E5-F5</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="152">
+        <f>IF(G5&gt;0,G5*4%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="96">
+        <v>13.8</v>
+      </c>
+      <c r="J5" s="212">
+        <f>D$1*I5/100</f>
+        <v>50112.700380000009</v>
+      </c>
+      <c r="K5" s="213">
+        <f>I$1*I5/100</f>
+        <v>110400</v>
+      </c>
+      <c r="L5" s="104">
+        <f>G5+H5+J5+K5</f>
+        <v>160512.70037999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="27" x14ac:dyDescent="0.3">
+      <c r="A6" s="175">
+        <v>2</v>
+      </c>
+      <c r="B6" s="176"/>
+      <c r="C6" s="111" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" s="73" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" s="150">
+        <v>0</v>
+      </c>
+      <c r="F6" s="151">
+        <f t="shared" ref="F6:F9" si="0">E6</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="152">
+        <f t="shared" ref="G6:G14" si="1">E6-F6</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="152">
+        <f t="shared" ref="H6:H14" si="2">IF(G6&gt;0,G6*4%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="96">
+        <v>11.86</v>
+      </c>
+      <c r="J6" s="212">
+        <f>D$1*I6/100</f>
+        <v>43067.871485999996</v>
+      </c>
+      <c r="K6" s="213">
+        <f t="shared" ref="K6:K14" si="3">I$1*I6/100</f>
+        <v>94880</v>
+      </c>
+      <c r="L6" s="104">
+        <f t="shared" ref="L6:L14" si="4">G6+H6+J6+K6</f>
+        <v>137947.87148599999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="27" x14ac:dyDescent="0.3">
+      <c r="A7" s="175">
+        <v>3</v>
+      </c>
+      <c r="B7" s="176"/>
+      <c r="C7" s="111" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="E7" s="150">
+        <v>0</v>
+      </c>
+      <c r="F7" s="151">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G7" s="152">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H7" s="152">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I7" s="96">
+        <v>12.46</v>
+      </c>
+      <c r="J7" s="212">
+        <f>D$1*I7/100</f>
+        <v>45246.684546000004</v>
+      </c>
+      <c r="K7" s="213">
+        <f t="shared" si="3"/>
+        <v>99680</v>
+      </c>
+      <c r="L7" s="104">
+        <f t="shared" si="4"/>
+        <v>144926.684546</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="175">
+        <v>4</v>
+      </c>
+      <c r="B8" s="176"/>
+      <c r="C8" s="111" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" s="73" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" s="150">
+        <v>0</v>
+      </c>
+      <c r="F8" s="151">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="152">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="152">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I8" s="96">
+        <v>14.75</v>
+      </c>
+      <c r="J8" s="212">
+        <f>D$1*I8/100</f>
+        <v>53562.487724999999</v>
+      </c>
+      <c r="K8" s="213">
+        <f t="shared" si="3"/>
+        <v>118000</v>
+      </c>
+      <c r="L8" s="104">
+        <f t="shared" si="4"/>
+        <v>171562.48772500001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="175">
+        <v>5</v>
+      </c>
+      <c r="B9" s="176"/>
+      <c r="C9" s="111" t="s">
+        <v>69</v>
+      </c>
+      <c r="D9" s="73" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" s="150">
+        <v>0</v>
+      </c>
+      <c r="F9" s="151">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G9" s="152">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H9" s="152">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I9" s="96">
+        <v>12.41</v>
+      </c>
+      <c r="J9" s="212">
+        <f>D$1*I9/100</f>
+        <v>45065.116791</v>
+      </c>
+      <c r="K9" s="213">
+        <f t="shared" si="3"/>
+        <v>99280</v>
+      </c>
+      <c r="L9" s="104">
+        <f>G9+H9+J9+K9</f>
+        <v>144345.11679100001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="175">
+        <v>6</v>
+      </c>
+      <c r="B10" s="176"/>
+      <c r="C10" s="111" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" s="73"/>
+      <c r="E10" s="150">
+        <v>0</v>
+      </c>
+      <c r="F10" s="151">
+        <f>E10</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="152">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H10" s="152">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I10" s="96">
+        <v>12.48</v>
+      </c>
+      <c r="J10" s="212">
+        <f>D$1*I10/100</f>
+        <v>45319.311648000003</v>
+      </c>
+      <c r="K10" s="213">
+        <f t="shared" si="3"/>
+        <v>99840</v>
+      </c>
+      <c r="L10" s="104">
+        <f t="shared" si="4"/>
+        <v>145159.311648</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="175">
+        <v>7</v>
+      </c>
+      <c r="B11" s="176"/>
+      <c r="C11" s="111" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" s="73"/>
+      <c r="E11" s="150">
+        <v>0</v>
+      </c>
+      <c r="F11" s="151">
+        <f>E11</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="152">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H11" s="152">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I11" s="96">
+        <v>18.260000000000002</v>
+      </c>
+      <c r="J11" s="212">
+        <f>D$1*I11/100</f>
+        <v>66308.544126000008</v>
+      </c>
+      <c r="K11" s="213">
+        <f t="shared" si="3"/>
+        <v>146080.00000000003</v>
+      </c>
+      <c r="L11" s="104">
+        <f t="shared" si="4"/>
+        <v>212388.54412600002</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="175" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="176"/>
+      <c r="C12" s="111" t="str">
+        <f>C9</f>
+        <v>Grand Jorge</v>
+      </c>
+      <c r="D12" s="73"/>
+      <c r="E12" s="150">
+        <v>0</v>
+      </c>
+      <c r="F12" s="151">
+        <f t="shared" ref="F12:F14" si="5">E12</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="152">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="152">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I12" s="96">
+        <v>1.34</v>
+      </c>
+      <c r="J12" s="212">
+        <f>D$1*I12/100</f>
+        <v>4866.0158340000007</v>
+      </c>
+      <c r="K12" s="213">
+        <f t="shared" si="3"/>
+        <v>10720</v>
+      </c>
+      <c r="L12" s="104">
+        <f t="shared" si="4"/>
+        <v>15586.015834000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="175" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" s="176"/>
+      <c r="C13" s="111" t="str">
+        <f>C6</f>
+        <v>Maceyle Gabriela</v>
+      </c>
+      <c r="D13" s="73"/>
+      <c r="E13" s="150">
+        <v>0</v>
+      </c>
+      <c r="F13" s="151">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G13" s="152">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="152">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I13" s="96">
+        <v>1.32</v>
+      </c>
+      <c r="J13" s="212">
+        <f>D$1*I13/100</f>
+        <v>4793.3887320000003</v>
+      </c>
+      <c r="K13" s="213">
+        <f t="shared" si="3"/>
+        <v>10560</v>
+      </c>
+      <c r="L13" s="104">
+        <f t="shared" si="4"/>
+        <v>15353.388731999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="175" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" s="176"/>
+      <c r="C14" s="59" t="str">
+        <f>C6</f>
+        <v>Maceyle Gabriela</v>
+      </c>
+      <c r="D14" s="73"/>
+      <c r="E14" s="150">
+        <v>0</v>
+      </c>
+      <c r="F14" s="151">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="152">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="152">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I14" s="96">
+        <v>1.32</v>
+      </c>
+      <c r="J14" s="212">
+        <f>D$1*I14/100</f>
+        <v>4793.3887320000003</v>
+      </c>
+      <c r="K14" s="213">
+        <f t="shared" si="3"/>
+        <v>10560</v>
+      </c>
+      <c r="L14" s="104">
+        <f t="shared" si="4"/>
+        <v>15353.388731999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="105" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="106"/>
+      <c r="C15" s="107"/>
+      <c r="D15" s="107"/>
+      <c r="E15" s="42">
+        <f>SUM(E5:E14)</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="42">
+        <f t="shared" ref="F15:H15" si="6">SUM(F5:F14)</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="42">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="42">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I15" s="110">
+        <f t="shared" ref="I15" si="7">SUM(I5:I14)</f>
+        <v>100</v>
+      </c>
+      <c r="J15" s="39">
+        <f>SUM(J5:J14)</f>
+        <v>363135.51000000007</v>
+      </c>
+      <c r="K15" s="42">
+        <f>SUM(K5:K14)</f>
+        <v>800000</v>
+      </c>
+      <c r="L15" s="42">
+        <f>SUM(L5:L14)</f>
+        <v>1163135.51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="53" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18">
+        <v>7454</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="28"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="71"/>
+      <c r="E19">
+        <v>14805</v>
+      </c>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="54"/>
+      <c r="K19" s="54"/>
+      <c r="L19" s="31"/>
+    </row>
+    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="1"/>
+      <c r="E20">
+        <v>3297</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J20" s="55" t="s">
+        <v>17</v>
+      </c>
+      <c r="K20" s="45"/>
+      <c r="L20" s="45" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="1"/>
+      <c r="E21">
+        <v>3177</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="37">
+        <v>0.02</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J21" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="K21" s="38"/>
+      <c r="L21" s="38" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="11">
+        <v>1</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="72"/>
+      <c r="E22">
+        <v>3056</v>
+      </c>
+      <c r="F22" s="46">
+        <v>37971</v>
+      </c>
+      <c r="G22" s="51"/>
+      <c r="H22" s="51">
+        <v>0</v>
+      </c>
+      <c r="I22" s="17">
+        <v>0.121</v>
+      </c>
+      <c r="J22" s="44">
+        <f>0*I22</f>
+        <v>0</v>
+      </c>
+      <c r="K22" s="41"/>
+      <c r="L22" s="41" t="e">
+        <f>+#REF!+H22+J22</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="11">
+        <v>2</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="72"/>
+      <c r="E23">
+        <v>3056</v>
+      </c>
+      <c r="F23" s="46">
+        <v>66612</v>
+      </c>
+      <c r="G23" s="51"/>
+      <c r="H23" s="51">
+        <v>0</v>
+      </c>
+      <c r="I23" s="17">
+        <v>0.122</v>
+      </c>
+      <c r="J23" s="44">
+        <f t="shared" ref="J23:J29" si="8">0*I23</f>
+        <v>0</v>
+      </c>
+      <c r="K23" s="41"/>
+      <c r="L23" s="41" t="e">
+        <f>+#REF!+H23+J23</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="11">
+        <v>3</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" s="72"/>
+      <c r="E24">
+        <f>SUM(E16:E23)</f>
+        <v>34845</v>
+      </c>
+      <c r="F24" s="46">
+        <v>0</v>
+      </c>
+      <c r="G24" s="51"/>
+      <c r="H24" s="51">
+        <v>0</v>
+      </c>
+      <c r="I24" s="17">
+        <v>0.11700000000000001</v>
+      </c>
+      <c r="J24" s="44">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="41"/>
+      <c r="L24" s="41" t="e">
+        <f>+#REF!+H24+J24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="11">
+        <v>4</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" s="72"/>
+      <c r="F25" s="46">
+        <v>0</v>
+      </c>
+      <c r="G25" s="51"/>
+      <c r="H25" s="51">
+        <v>0</v>
+      </c>
+      <c r="I25" s="17">
+        <v>0.11700000000000001</v>
+      </c>
+      <c r="J25" s="44">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="41"/>
+      <c r="L25" s="41" t="e">
+        <f>+#REF!+H25+J25</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="11">
+        <v>5</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" s="72"/>
+      <c r="F26" s="46">
+        <v>80517</v>
+      </c>
+      <c r="G26" s="51"/>
+      <c r="H26" s="51">
+        <v>0</v>
+      </c>
+      <c r="I26" s="17">
+        <v>0.13700000000000001</v>
+      </c>
+      <c r="J26" s="44">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="41"/>
+      <c r="L26" s="41" t="e">
+        <f>+#REF!+H26+J26</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="11">
+        <v>6</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" s="72"/>
+      <c r="F27" s="46">
+        <v>0</v>
+      </c>
+      <c r="G27" s="51"/>
+      <c r="H27" s="51">
+        <v>0</v>
+      </c>
+      <c r="I27" s="17">
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="J27" s="44">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="41"/>
+      <c r="L27" s="41" t="e">
+        <f>+#REF!+H27+J27</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="11">
+        <v>7</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" s="72"/>
+      <c r="E28" t="s">
+        <v>38</v>
+      </c>
+      <c r="F28" s="46">
+        <v>18542</v>
+      </c>
+      <c r="G28" s="51"/>
+      <c r="H28" s="51">
+        <v>0</v>
+      </c>
+      <c r="I28" s="17">
+        <v>0.127</v>
+      </c>
+      <c r="J28" s="44">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="41"/>
+      <c r="L28" s="41" t="e">
+        <f>+#REF!+H28+J28</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="11">
+        <v>8</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D29" s="72"/>
+      <c r="E29" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29" s="46">
+        <v>0</v>
+      </c>
+      <c r="G29" s="51"/>
+      <c r="H29" s="51">
+        <v>0</v>
+      </c>
+      <c r="I29" s="17">
+        <v>0.127</v>
+      </c>
+      <c r="J29" s="44">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="41"/>
+      <c r="L29" s="41" t="e">
+        <f>+#REF!+H29+J29</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30" s="9"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="70"/>
+      <c r="E30" t="s">
+        <v>20</v>
+      </c>
+      <c r="F30" s="49">
+        <f>SUM(F22:F29)</f>
+        <v>203642</v>
+      </c>
+      <c r="G30" s="49"/>
+      <c r="H30" s="52">
+        <f>SUM(H22:H29)</f>
+        <v>0</v>
+      </c>
+      <c r="I30" s="15">
+        <f t="shared" ref="I30:J30" si="9">SUM(I22:I29)</f>
+        <v>1</v>
+      </c>
+      <c r="J30" s="39">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="K30" s="42"/>
+      <c r="L30" s="42" t="e">
+        <f>SUM(L22:L29)</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="N31"/>
+    </row>
+    <row r="32" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="189" t="s">
+        <v>113</v>
+      </c>
+      <c r="F32" s="190"/>
+      <c r="G32" s="190"/>
+      <c r="H32" s="190"/>
+      <c r="I32" s="190"/>
+      <c r="J32" s="190"/>
+      <c r="K32" s="191"/>
+      <c r="L32" s="153"/>
+      <c r="M32" s="154"/>
+      <c r="N32"/>
+    </row>
+    <row r="33" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="192" t="s">
+        <v>114</v>
+      </c>
+      <c r="F33" s="190"/>
+      <c r="G33" s="190"/>
+      <c r="H33" s="190"/>
+      <c r="I33" s="190"/>
+      <c r="J33" s="190"/>
+      <c r="K33" s="191"/>
+      <c r="L33" s="155"/>
+      <c r="M33" s="156"/>
+      <c r="N33"/>
+    </row>
+    <row r="34" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="153"/>
+      <c r="F34" s="157"/>
+      <c r="G34" s="157"/>
+      <c r="H34" s="157"/>
+      <c r="I34" s="158"/>
+      <c r="J34" s="158">
+        <f>'detalle y gastos'!B7</f>
+        <v>0</v>
+      </c>
+      <c r="K34" s="156"/>
+      <c r="L34" s="155"/>
+      <c r="M34" s="156"/>
+      <c r="N34"/>
+    </row>
+    <row r="35" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="155" t="s">
+        <v>115</v>
+      </c>
+      <c r="F35" s="158"/>
+      <c r="G35" s="158"/>
+      <c r="H35" s="158"/>
+      <c r="I35" s="158"/>
+      <c r="J35" s="158"/>
+      <c r="K35" s="156"/>
+      <c r="L35" s="155"/>
+      <c r="M35" s="156"/>
+      <c r="N35"/>
+    </row>
+    <row r="36" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="159"/>
+      <c r="F36" s="160"/>
+      <c r="G36" s="160"/>
+      <c r="H36" s="160"/>
+      <c r="I36" s="160"/>
+      <c r="J36" s="160"/>
+      <c r="K36" s="161"/>
+      <c r="L36" s="155"/>
+      <c r="M36" s="156"/>
+      <c r="N36"/>
+    </row>
+    <row r="37" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="193" t="s">
+        <v>50</v>
+      </c>
+      <c r="F37" s="194"/>
+      <c r="G37" s="194"/>
+      <c r="H37" s="194"/>
+      <c r="I37" s="194"/>
+      <c r="J37" s="194"/>
+      <c r="K37" s="195"/>
+      <c r="L37" s="155"/>
+      <c r="M37" s="156"/>
+      <c r="N37"/>
+    </row>
+    <row r="38" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="155"/>
+      <c r="F38" s="158"/>
+      <c r="G38" s="158"/>
+      <c r="H38" s="158"/>
+      <c r="I38" s="158"/>
+      <c r="J38" s="158"/>
+      <c r="K38" s="156"/>
+      <c r="L38" s="155"/>
+      <c r="M38" s="156"/>
+      <c r="N38"/>
+    </row>
+    <row r="39" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="155" t="s">
+        <v>116</v>
+      </c>
+      <c r="F39" s="158"/>
+      <c r="G39" s="158" t="str">
+        <f>C7</f>
+        <v>Maceyle Gabriela</v>
+      </c>
+      <c r="H39" s="158"/>
+      <c r="I39" s="158" t="s">
+        <v>117</v>
+      </c>
+      <c r="J39" s="162">
+        <v>45674</v>
+      </c>
+      <c r="K39" s="156"/>
+      <c r="L39" s="196" t="s">
+        <v>118</v>
+      </c>
+      <c r="M39" s="197"/>
+      <c r="N39"/>
+    </row>
+    <row r="40" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="155" t="s">
+        <v>119</v>
+      </c>
+      <c r="F40" s="163">
+        <v>3</v>
+      </c>
+      <c r="G40" s="158"/>
+      <c r="H40" s="158"/>
+      <c r="I40" s="158"/>
+      <c r="J40" s="158"/>
+      <c r="K40" s="156"/>
+      <c r="L40" s="155"/>
+      <c r="M40" s="156"/>
+      <c r="N40"/>
+    </row>
+    <row r="41" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="155"/>
+      <c r="F41" s="158"/>
+      <c r="G41" s="158"/>
+      <c r="H41" s="158"/>
+      <c r="I41" s="158"/>
+      <c r="J41" s="158"/>
+      <c r="K41" s="156"/>
+      <c r="L41" s="198"/>
+      <c r="M41" s="197"/>
+      <c r="N41"/>
+    </row>
+    <row r="42" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="155" t="s">
+        <v>49</v>
+      </c>
+      <c r="F42" s="158"/>
+      <c r="G42" s="158"/>
+      <c r="H42" s="158"/>
+      <c r="I42" s="158"/>
+      <c r="J42" s="164">
+        <f>J7</f>
+        <v>45246.684546000004</v>
+      </c>
+      <c r="K42" s="156"/>
+      <c r="L42" s="155"/>
+      <c r="M42" s="156"/>
+      <c r="N42"/>
+    </row>
+    <row r="43" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="165" t="s">
+        <v>120</v>
+      </c>
+      <c r="F43" s="158"/>
+      <c r="G43" s="158"/>
+      <c r="H43" s="158"/>
+      <c r="I43" s="158"/>
+      <c r="J43" s="164">
+        <f>K7</f>
+        <v>99680</v>
+      </c>
+      <c r="K43" s="156"/>
+      <c r="L43" s="155"/>
+      <c r="M43" s="156"/>
+      <c r="N43"/>
+    </row>
+    <row r="44" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="165" t="s">
+        <v>122</v>
+      </c>
+      <c r="F44" s="158"/>
+      <c r="G44" s="158"/>
+      <c r="H44" s="158"/>
+      <c r="I44" s="158"/>
+      <c r="J44" s="164">
+        <f>G7+H7</f>
+        <v>0</v>
+      </c>
+      <c r="K44" s="156"/>
+      <c r="L44" s="155"/>
+      <c r="M44" s="156"/>
+      <c r="N44"/>
+    </row>
+    <row r="45" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="165"/>
+      <c r="F45" s="158"/>
+      <c r="G45" s="158"/>
+      <c r="H45" s="158"/>
+      <c r="I45" s="158"/>
+      <c r="J45" s="164"/>
+      <c r="K45" s="156"/>
+      <c r="L45" s="155"/>
+      <c r="M45" s="156"/>
+      <c r="N45"/>
+    </row>
+    <row r="46" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="165"/>
+      <c r="F46" s="158"/>
+      <c r="G46" s="158"/>
+      <c r="H46" s="158"/>
+      <c r="I46" s="158"/>
+      <c r="J46" s="164"/>
+      <c r="K46" s="156"/>
+      <c r="L46" s="155"/>
+      <c r="M46" s="156"/>
+      <c r="N46"/>
+    </row>
+    <row r="47" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="F47" s="158"/>
+      <c r="G47" s="158"/>
+      <c r="H47" s="158"/>
+      <c r="I47" s="158"/>
+      <c r="J47" s="164"/>
+      <c r="K47" s="156"/>
+      <c r="L47" s="155"/>
+      <c r="M47" s="156"/>
+      <c r="N47"/>
+    </row>
+    <row r="48" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="165"/>
+      <c r="F48" s="158"/>
+      <c r="G48" s="158"/>
+      <c r="H48" s="158"/>
+      <c r="I48" s="158"/>
+      <c r="J48" s="164"/>
+      <c r="K48" s="156"/>
+      <c r="L48" s="155"/>
+      <c r="M48" s="156"/>
+      <c r="N48"/>
+    </row>
+    <row r="49" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="155"/>
+      <c r="F49" s="158"/>
+      <c r="G49" s="158"/>
+      <c r="H49" s="158"/>
+      <c r="I49" s="158"/>
+      <c r="J49" s="158"/>
+      <c r="K49" s="156"/>
+      <c r="L49" s="155"/>
+      <c r="M49" s="156"/>
+      <c r="N49"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="155" t="s">
+        <v>123</v>
+      </c>
+      <c r="F50" s="158"/>
+      <c r="G50" s="158"/>
+      <c r="H50" s="158"/>
+      <c r="I50" s="158"/>
+      <c r="J50" s="158">
+        <f>77200-77124.2</f>
+        <v>75.80000000000291</v>
+      </c>
+      <c r="K50" s="156"/>
+      <c r="L50" s="155"/>
+      <c r="M50" s="156"/>
+      <c r="N50"/>
+    </row>
+    <row r="51" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="155"/>
+      <c r="F51" s="158"/>
+      <c r="G51" s="158"/>
+      <c r="H51" s="158"/>
+      <c r="I51" s="158"/>
+      <c r="J51" s="158"/>
+      <c r="K51" s="156"/>
+      <c r="L51" s="166"/>
+      <c r="M51" s="167"/>
+      <c r="N51"/>
+    </row>
+    <row r="52" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="199" t="s">
+        <v>121</v>
+      </c>
+      <c r="F52" s="200"/>
+      <c r="G52" s="200"/>
+      <c r="H52" s="200"/>
+      <c r="I52" s="200"/>
+      <c r="J52" s="201">
+        <f>SUM(J42:J51)</f>
+        <v>145002.48454600002</v>
+      </c>
+      <c r="K52" s="191"/>
+      <c r="L52" s="168"/>
+      <c r="M52" s="169"/>
+      <c r="N52"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="N53"/>
+    </row>
+    <row r="55" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="56" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E56" s="189" t="s">
+        <v>113</v>
+      </c>
+      <c r="F56" s="190"/>
+      <c r="G56" s="190"/>
+      <c r="H56" s="190"/>
+      <c r="I56" s="190"/>
+      <c r="J56" s="190"/>
+      <c r="K56" s="191"/>
+      <c r="L56" s="153"/>
+      <c r="M56" s="154"/>
+    </row>
+    <row r="57" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E57" s="192" t="s">
+        <v>114</v>
+      </c>
+      <c r="F57" s="190"/>
+      <c r="G57" s="190"/>
+      <c r="H57" s="190"/>
+      <c r="I57" s="190"/>
+      <c r="J57" s="190"/>
+      <c r="K57" s="191"/>
+      <c r="L57" s="155"/>
+      <c r="M57" s="156"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="E58" s="153"/>
+      <c r="F58" s="157"/>
+      <c r="G58" s="157"/>
+      <c r="H58" s="157"/>
+      <c r="I58" s="158"/>
+      <c r="J58" s="158">
+        <f>J34</f>
+        <v>0</v>
+      </c>
+      <c r="K58" s="156"/>
+      <c r="L58" s="155"/>
+      <c r="M58" s="156"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="E59" s="155" t="s">
+        <v>115</v>
+      </c>
+      <c r="F59" s="158"/>
+      <c r="G59" s="158"/>
+      <c r="H59" s="158"/>
+      <c r="I59" s="158"/>
+      <c r="J59" s="158"/>
+      <c r="K59" s="156"/>
+      <c r="L59" s="155"/>
+      <c r="M59" s="156"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="E60" s="159"/>
+      <c r="F60" s="160"/>
+      <c r="G60" s="160"/>
+      <c r="H60" s="160"/>
+      <c r="I60" s="160"/>
+      <c r="J60" s="160"/>
+      <c r="K60" s="161"/>
+      <c r="L60" s="155"/>
+      <c r="M60" s="156"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="E61" s="193" t="s">
+        <v>50</v>
+      </c>
+      <c r="F61" s="194"/>
+      <c r="G61" s="194"/>
+      <c r="H61" s="194"/>
+      <c r="I61" s="194"/>
+      <c r="J61" s="194"/>
+      <c r="K61" s="195"/>
+      <c r="L61" s="155"/>
+      <c r="M61" s="156"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="E62" s="155"/>
+      <c r="F62" s="158"/>
+      <c r="G62" s="158"/>
+      <c r="H62" s="158"/>
+      <c r="I62" s="158"/>
+      <c r="J62" s="158"/>
+      <c r="K62" s="156"/>
+      <c r="L62" s="155"/>
+      <c r="M62" s="156"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="E63" s="155" t="s">
+        <v>116</v>
+      </c>
+      <c r="F63" s="158"/>
+      <c r="G63" s="163" t="str">
+        <f>C8</f>
+        <v>Castelao Lorena</v>
+      </c>
+      <c r="H63" s="158"/>
+      <c r="I63" s="158" t="s">
+        <v>117</v>
+      </c>
+      <c r="J63" s="162">
+        <v>45674</v>
+      </c>
+      <c r="K63" s="156"/>
+      <c r="L63" s="196" t="s">
+        <v>118</v>
+      </c>
+      <c r="M63" s="197"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="E64" s="155" t="s">
+        <v>119</v>
+      </c>
+      <c r="F64" s="163">
+        <v>4</v>
+      </c>
+      <c r="G64" s="158"/>
+      <c r="H64" s="158"/>
+      <c r="I64" s="158"/>
+      <c r="J64" s="158"/>
+      <c r="K64" s="156"/>
+      <c r="L64" s="155"/>
+      <c r="M64" s="156"/>
+    </row>
+    <row r="65" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E65" s="155"/>
+      <c r="F65" s="158"/>
+      <c r="G65" s="158"/>
+      <c r="H65" s="158"/>
+      <c r="I65" s="158"/>
+      <c r="J65" s="158"/>
+      <c r="K65" s="156"/>
+      <c r="L65" s="198"/>
+      <c r="M65" s="197"/>
+    </row>
+    <row r="66" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E66" s="155" t="s">
+        <v>49</v>
+      </c>
+      <c r="F66" s="158"/>
+      <c r="G66" s="158"/>
+      <c r="H66" s="158"/>
+      <c r="I66" s="158"/>
+      <c r="J66" s="164">
+        <f>J8</f>
+        <v>53562.487724999999</v>
+      </c>
+      <c r="K66" s="156"/>
+      <c r="L66" s="155"/>
+      <c r="M66" s="156"/>
+    </row>
+    <row r="67" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E67" s="165" t="s">
+        <v>120</v>
+      </c>
+      <c r="F67" s="158"/>
+      <c r="G67" s="158"/>
+      <c r="H67" s="158"/>
+      <c r="I67" s="158"/>
+      <c r="J67" s="164">
+        <f>K8</f>
+        <v>118000</v>
+      </c>
+      <c r="K67" s="156"/>
+      <c r="L67" s="155"/>
+      <c r="M67" s="156"/>
+    </row>
+    <row r="68" spans="5:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E68" s="165" t="s">
+        <v>122</v>
+      </c>
+      <c r="F68" s="158"/>
+      <c r="G68" s="158"/>
+      <c r="H68" s="158"/>
+      <c r="I68" s="158"/>
+      <c r="J68" s="164">
+        <f>G29+H29</f>
+        <v>0</v>
+      </c>
+      <c r="K68" s="156"/>
+      <c r="L68" s="155"/>
+      <c r="M68" s="156"/>
+    </row>
+    <row r="69" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E69" s="165"/>
+      <c r="F69" s="158"/>
+      <c r="G69" s="158"/>
+      <c r="H69" s="158"/>
+      <c r="I69" s="158"/>
+      <c r="J69" s="164"/>
+      <c r="K69" s="156"/>
+      <c r="L69" s="155"/>
+      <c r="M69" s="156"/>
+    </row>
+    <row r="70" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E70" s="165"/>
+      <c r="F70" s="158"/>
+      <c r="G70" s="158"/>
+      <c r="H70" s="158"/>
+      <c r="I70" s="158"/>
+      <c r="J70" s="164"/>
+      <c r="K70" s="156"/>
+      <c r="L70" s="155"/>
+      <c r="M70" s="156"/>
+    </row>
+    <row r="71" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="F71" s="158"/>
+      <c r="G71" s="158"/>
+      <c r="H71" s="158"/>
+      <c r="I71" s="158"/>
+      <c r="J71" s="164"/>
+      <c r="K71" s="156"/>
+      <c r="L71" s="155"/>
+      <c r="M71" s="156"/>
+    </row>
+    <row r="72" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E72" s="165"/>
+      <c r="F72" s="158"/>
+      <c r="G72" s="158"/>
+      <c r="H72" s="158"/>
+      <c r="I72" s="158"/>
+      <c r="J72" s="164"/>
+      <c r="K72" s="156"/>
+      <c r="L72" s="155"/>
+      <c r="M72" s="156"/>
+    </row>
+    <row r="73" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E73" s="155"/>
+      <c r="F73" s="158"/>
+      <c r="G73" s="158"/>
+      <c r="H73" s="158"/>
+      <c r="I73" s="158"/>
+      <c r="J73" s="158"/>
+      <c r="K73" s="156"/>
+      <c r="L73" s="155"/>
+      <c r="M73" s="156"/>
+    </row>
+    <row r="74" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E74" s="155"/>
+      <c r="F74" s="158"/>
+      <c r="G74" s="158"/>
+      <c r="H74" s="158"/>
+      <c r="I74" s="158"/>
+      <c r="J74" s="158"/>
+      <c r="K74" s="156"/>
+      <c r="L74" s="155"/>
+      <c r="M74" s="156"/>
+    </row>
+    <row r="75" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E75" s="155"/>
+      <c r="F75" s="158"/>
+      <c r="G75" s="158"/>
+      <c r="H75" s="158"/>
+      <c r="I75" s="158"/>
+      <c r="J75" s="158"/>
+      <c r="K75" s="156"/>
+      <c r="L75" s="166"/>
+      <c r="M75" s="167"/>
+    </row>
+    <row r="76" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E76" s="199" t="s">
+        <v>121</v>
+      </c>
+      <c r="F76" s="200"/>
+      <c r="G76" s="200"/>
+      <c r="H76" s="200"/>
+      <c r="I76" s="200"/>
+      <c r="J76" s="201">
+        <f>SUM(J66:J75)</f>
+        <v>171562.48772500001</v>
+      </c>
+      <c r="K76" s="191"/>
+      <c r="L76" s="168"/>
+      <c r="M76" s="169"/>
+    </row>
+    <row r="82" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="83" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E83" s="189" t="s">
+        <v>113</v>
+      </c>
+      <c r="F83" s="190"/>
+      <c r="G83" s="190"/>
+      <c r="H83" s="190"/>
+      <c r="I83" s="190"/>
+      <c r="J83" s="190"/>
+      <c r="K83" s="191"/>
+      <c r="L83" s="153"/>
+      <c r="M83" s="154"/>
+    </row>
+    <row r="84" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E84" s="192" t="s">
+        <v>114</v>
+      </c>
+      <c r="F84" s="190"/>
+      <c r="G84" s="190"/>
+      <c r="H84" s="190"/>
+      <c r="I84" s="190"/>
+      <c r="J84" s="190"/>
+      <c r="K84" s="191"/>
+      <c r="L84" s="155"/>
+      <c r="M84" s="156"/>
+    </row>
+    <row r="85" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E85" s="153"/>
+      <c r="F85" s="157"/>
+      <c r="G85" s="157"/>
+      <c r="H85" s="157"/>
+      <c r="I85" s="158"/>
+      <c r="J85" s="158">
+        <f>'detalle y gastos'!B7</f>
+        <v>0</v>
+      </c>
+      <c r="K85" s="156"/>
+      <c r="L85" s="155"/>
+      <c r="M85" s="156"/>
+    </row>
+    <row r="86" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E86" s="155" t="s">
+        <v>115</v>
+      </c>
+      <c r="F86" s="158"/>
+      <c r="G86" s="158"/>
+      <c r="H86" s="158"/>
+      <c r="I86" s="158"/>
+      <c r="J86" s="158"/>
+      <c r="K86" s="156"/>
+      <c r="L86" s="155"/>
+      <c r="M86" s="156"/>
+    </row>
+    <row r="87" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E87" s="159"/>
+      <c r="F87" s="160"/>
+      <c r="G87" s="160"/>
+      <c r="H87" s="160"/>
+      <c r="I87" s="160"/>
+      <c r="J87" s="160"/>
+      <c r="K87" s="161"/>
+      <c r="L87" s="155"/>
+      <c r="M87" s="156"/>
+    </row>
+    <row r="88" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E88" s="193" t="s">
+        <v>50</v>
+      </c>
+      <c r="F88" s="194"/>
+      <c r="G88" s="194"/>
+      <c r="H88" s="194"/>
+      <c r="I88" s="194"/>
+      <c r="J88" s="194"/>
+      <c r="K88" s="195"/>
+      <c r="L88" s="155"/>
+      <c r="M88" s="156"/>
+    </row>
+    <row r="89" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E89" s="155"/>
+      <c r="F89" s="158"/>
+      <c r="G89" s="158"/>
+      <c r="H89" s="158"/>
+      <c r="I89" s="158"/>
+      <c r="J89" s="158"/>
+      <c r="K89" s="156"/>
+      <c r="L89" s="155"/>
+      <c r="M89" s="156"/>
+    </row>
+    <row r="90" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E90" s="155" t="s">
+        <v>116</v>
+      </c>
+      <c r="F90" s="158"/>
+      <c r="G90" s="163" t="str">
+        <f>C10</f>
+        <v>Valdez Norberto</v>
+      </c>
+      <c r="H90" s="158"/>
+      <c r="I90" s="158" t="s">
+        <v>117</v>
+      </c>
+      <c r="J90" s="162">
+        <v>45674</v>
+      </c>
+      <c r="K90" s="156"/>
+      <c r="L90" s="196" t="s">
+        <v>118</v>
+      </c>
+      <c r="M90" s="197"/>
+    </row>
+    <row r="91" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E91" s="155" t="s">
+        <v>119</v>
+      </c>
+      <c r="F91" s="163">
+        <v>6</v>
+      </c>
+      <c r="G91" s="158"/>
+      <c r="H91" s="158"/>
+      <c r="I91" s="158"/>
+      <c r="J91" s="158"/>
+      <c r="K91" s="156"/>
+      <c r="L91" s="155"/>
+      <c r="M91" s="156"/>
+    </row>
+    <row r="92" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E92" s="155"/>
+      <c r="F92" s="158"/>
+      <c r="G92" s="158"/>
+      <c r="H92" s="158"/>
+      <c r="I92" s="158"/>
+      <c r="J92" s="158"/>
+      <c r="K92" s="156"/>
+      <c r="L92" s="198"/>
+      <c r="M92" s="197"/>
+    </row>
+    <row r="93" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E93" s="155" t="s">
+        <v>49</v>
+      </c>
+      <c r="F93" s="158"/>
+      <c r="G93" s="158"/>
+      <c r="H93" s="158"/>
+      <c r="I93" s="158"/>
+      <c r="J93" s="164">
+        <f>J10</f>
+        <v>45319.311648000003</v>
+      </c>
+      <c r="K93" s="156"/>
+      <c r="L93" s="155"/>
+      <c r="M93" s="156"/>
+    </row>
+    <row r="94" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E94" s="165" t="s">
+        <v>120</v>
+      </c>
+      <c r="F94" s="158"/>
+      <c r="G94" s="158"/>
+      <c r="H94" s="158"/>
+      <c r="I94" s="158"/>
+      <c r="J94" s="164">
+        <f>K10</f>
+        <v>99840</v>
+      </c>
+      <c r="K94" s="156"/>
+      <c r="L94" s="155"/>
+      <c r="M94" s="156"/>
+    </row>
+    <row r="95" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E95" s="165" t="s">
+        <v>123</v>
+      </c>
+      <c r="F95" s="158"/>
+      <c r="G95" s="158"/>
+      <c r="H95" s="158"/>
+      <c r="I95" s="158"/>
+      <c r="J95" s="164">
+        <v>23.89</v>
+      </c>
+      <c r="K95" s="156"/>
+      <c r="L95" s="155"/>
+      <c r="M95" s="156"/>
+    </row>
+    <row r="96" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E96" s="165"/>
+      <c r="F96" s="158"/>
+      <c r="G96" s="158"/>
+      <c r="H96" s="158"/>
+      <c r="I96" s="158"/>
+      <c r="J96" s="164"/>
+      <c r="K96" s="156"/>
+      <c r="L96" s="155"/>
+      <c r="M96" s="156"/>
+    </row>
+    <row r="97" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E97" s="165"/>
+      <c r="F97" s="158"/>
+      <c r="G97" s="158"/>
+      <c r="H97" s="158"/>
+      <c r="I97" s="158"/>
+      <c r="J97" s="164"/>
+      <c r="K97" s="156"/>
+      <c r="L97" s="155"/>
+      <c r="M97" s="156"/>
+    </row>
+    <row r="98" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F98" s="158"/>
+      <c r="G98" s="158"/>
+      <c r="H98" s="158"/>
+      <c r="I98" s="158"/>
+      <c r="J98" s="164"/>
+      <c r="K98" s="156"/>
+      <c r="L98" s="155"/>
+      <c r="M98" s="156"/>
+    </row>
+    <row r="99" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E99" s="165"/>
+      <c r="F99" s="158"/>
+      <c r="G99" s="158"/>
+      <c r="H99" s="158"/>
+      <c r="I99" s="158"/>
+      <c r="J99" s="164"/>
+      <c r="K99" s="156"/>
+      <c r="L99" s="155"/>
+      <c r="M99" s="156"/>
+    </row>
+    <row r="100" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E100" s="155"/>
+      <c r="F100" s="158"/>
+      <c r="G100" s="158"/>
+      <c r="H100" s="158"/>
+      <c r="I100" s="158"/>
+      <c r="J100" s="158"/>
+      <c r="K100" s="156"/>
+      <c r="L100" s="155"/>
+      <c r="M100" s="156"/>
+    </row>
+    <row r="101" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E101" s="155"/>
+      <c r="F101" s="158"/>
+      <c r="G101" s="158"/>
+      <c r="H101" s="158"/>
+      <c r="I101" s="158"/>
+      <c r="J101" s="158"/>
+      <c r="K101" s="156"/>
+      <c r="L101" s="155"/>
+      <c r="M101" s="156"/>
+    </row>
+    <row r="102" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E102" s="155"/>
+      <c r="F102" s="158"/>
+      <c r="G102" s="158"/>
+      <c r="H102" s="158"/>
+      <c r="I102" s="158"/>
+      <c r="J102" s="158"/>
+      <c r="K102" s="156"/>
+      <c r="L102" s="166"/>
+      <c r="M102" s="167"/>
+    </row>
+    <row r="103" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E103" s="199" t="s">
+        <v>121</v>
+      </c>
+      <c r="F103" s="200"/>
+      <c r="G103" s="200"/>
+      <c r="H103" s="200"/>
+      <c r="I103" s="200"/>
+      <c r="J103" s="201">
+        <f>SUM(J93:J102)</f>
+        <v>145183.20164800002</v>
+      </c>
+      <c r="K103" s="191"/>
+      <c r="L103" s="168"/>
+      <c r="M103" s="169"/>
+    </row>
+    <row r="107" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="108" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E108" s="189" t="s">
+        <v>113</v>
+      </c>
+      <c r="F108" s="190"/>
+      <c r="G108" s="190"/>
+      <c r="H108" s="190"/>
+      <c r="I108" s="190"/>
+      <c r="J108" s="190"/>
+      <c r="K108" s="191"/>
+      <c r="L108" s="153"/>
+      <c r="M108" s="154"/>
+    </row>
+    <row r="109" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E109" s="192" t="s">
+        <v>114</v>
+      </c>
+      <c r="F109" s="190"/>
+      <c r="G109" s="190"/>
+      <c r="H109" s="190"/>
+      <c r="I109" s="190"/>
+      <c r="J109" s="190"/>
+      <c r="K109" s="191"/>
+      <c r="L109" s="155"/>
+      <c r="M109" s="156"/>
+    </row>
+    <row r="110" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E110" s="153"/>
+      <c r="F110" s="157"/>
+      <c r="G110" s="157"/>
+      <c r="H110" s="157"/>
+      <c r="I110" s="158"/>
+      <c r="J110" s="158">
+        <f>'detalle y gastos'!B7</f>
+        <v>0</v>
+      </c>
+      <c r="K110" s="156"/>
+      <c r="L110" s="155"/>
+      <c r="M110" s="156"/>
+    </row>
+    <row r="111" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E111" s="155" t="s">
+        <v>115</v>
+      </c>
+      <c r="F111" s="158"/>
+      <c r="G111" s="158"/>
+      <c r="H111" s="158"/>
+      <c r="I111" s="158"/>
+      <c r="J111" s="158"/>
+      <c r="K111" s="156"/>
+      <c r="L111" s="155"/>
+      <c r="M111" s="156"/>
+    </row>
+    <row r="112" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E112" s="159"/>
+      <c r="F112" s="160"/>
+      <c r="G112" s="160"/>
+      <c r="H112" s="160"/>
+      <c r="I112" s="160"/>
+      <c r="J112" s="160"/>
+      <c r="K112" s="161"/>
+      <c r="L112" s="155"/>
+      <c r="M112" s="156"/>
+    </row>
+    <row r="113" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E113" s="193" t="s">
+        <v>50</v>
+      </c>
+      <c r="F113" s="194"/>
+      <c r="G113" s="194"/>
+      <c r="H113" s="194"/>
+      <c r="I113" s="194"/>
+      <c r="J113" s="194"/>
+      <c r="K113" s="195"/>
+      <c r="L113" s="155"/>
+      <c r="M113" s="156"/>
+    </row>
+    <row r="114" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E114" s="155"/>
+      <c r="F114" s="158"/>
+      <c r="G114" s="158"/>
+      <c r="H114" s="158"/>
+      <c r="I114" s="158"/>
+      <c r="J114" s="158"/>
+      <c r="K114" s="156"/>
+      <c r="L114" s="155"/>
+      <c r="M114" s="156"/>
+    </row>
+    <row r="115" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E115" s="155" t="s">
+        <v>116</v>
+      </c>
+      <c r="F115" s="158"/>
+      <c r="G115" s="163" t="str">
+        <f>C5</f>
+        <v>Gomez Elizabeth</v>
+      </c>
+      <c r="H115" s="158"/>
+      <c r="I115" s="158" t="s">
+        <v>117</v>
+      </c>
+      <c r="J115" s="162">
+        <v>45674</v>
+      </c>
+      <c r="K115" s="156"/>
+      <c r="L115" s="196" t="s">
+        <v>118</v>
+      </c>
+      <c r="M115" s="197"/>
+    </row>
+    <row r="116" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E116" s="155" t="s">
+        <v>119</v>
+      </c>
+      <c r="F116" s="163">
+        <v>1</v>
+      </c>
+      <c r="G116" s="158"/>
+      <c r="H116" s="158"/>
+      <c r="I116" s="158"/>
+      <c r="J116" s="158"/>
+      <c r="K116" s="156"/>
+      <c r="L116" s="155"/>
+      <c r="M116" s="156"/>
+    </row>
+    <row r="117" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E117" s="155"/>
+      <c r="F117" s="158"/>
+      <c r="G117" s="158"/>
+      <c r="H117" s="158"/>
+      <c r="I117" s="158"/>
+      <c r="J117" s="158"/>
+      <c r="K117" s="156"/>
+      <c r="L117" s="198"/>
+      <c r="M117" s="197"/>
+    </row>
+    <row r="118" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E118" s="155" t="s">
+        <v>49</v>
+      </c>
+      <c r="F118" s="158"/>
+      <c r="G118" s="158"/>
+      <c r="H118" s="158"/>
+      <c r="I118" s="158"/>
+      <c r="J118" s="164">
+        <f>J5</f>
+        <v>50112.700380000009</v>
+      </c>
+      <c r="K118" s="156"/>
+      <c r="L118" s="155"/>
+      <c r="M118" s="156"/>
+    </row>
+    <row r="119" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E119" s="165" t="s">
+        <v>120</v>
+      </c>
+      <c r="F119" s="158"/>
+      <c r="G119" s="158"/>
+      <c r="H119" s="158"/>
+      <c r="I119" s="158"/>
+      <c r="J119" s="164">
+        <f>K5</f>
+        <v>110400</v>
+      </c>
+      <c r="K119" s="156"/>
+      <c r="L119" s="155"/>
+      <c r="M119" s="156"/>
+    </row>
+    <row r="120" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E120" s="165" t="s">
+        <v>124</v>
+      </c>
+      <c r="F120" s="158"/>
+      <c r="G120" s="158"/>
+      <c r="H120" s="158"/>
+      <c r="I120" s="158"/>
+      <c r="J120" s="164">
+        <f>-20862.34+20810</f>
+        <v>-52.340000000000146</v>
+      </c>
+      <c r="K120" s="156"/>
+      <c r="L120" s="155"/>
+      <c r="M120" s="156"/>
+    </row>
+    <row r="121" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E121" s="165"/>
+      <c r="F121" s="158"/>
+      <c r="G121" s="158"/>
+      <c r="H121" s="158"/>
+      <c r="I121" s="158"/>
+      <c r="J121" s="164"/>
+      <c r="K121" s="156"/>
+      <c r="L121" s="155"/>
+      <c r="M121" s="156"/>
+    </row>
+    <row r="122" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E122" s="165"/>
+      <c r="F122" s="158"/>
+      <c r="G122" s="158"/>
+      <c r="H122" s="158"/>
+      <c r="I122" s="158"/>
+      <c r="J122" s="164"/>
+      <c r="K122" s="156"/>
+      <c r="L122" s="155"/>
+      <c r="M122" s="156"/>
+    </row>
+    <row r="123" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F123" s="158"/>
+      <c r="G123" s="158"/>
+      <c r="H123" s="158"/>
+      <c r="I123" s="158"/>
+      <c r="J123" s="164"/>
+      <c r="K123" s="156"/>
+      <c r="L123" s="155"/>
+      <c r="M123" s="156"/>
+    </row>
+    <row r="124" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E124" s="165"/>
+      <c r="F124" s="158"/>
+      <c r="G124" s="158"/>
+      <c r="H124" s="158"/>
+      <c r="I124" s="158"/>
+      <c r="J124" s="164"/>
+      <c r="K124" s="156"/>
+      <c r="L124" s="155"/>
+      <c r="M124" s="156"/>
+    </row>
+    <row r="125" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E125" s="155"/>
+      <c r="F125" s="158"/>
+      <c r="G125" s="158"/>
+      <c r="H125" s="158"/>
+      <c r="I125" s="158"/>
+      <c r="J125" s="158"/>
+      <c r="K125" s="156"/>
+      <c r="L125" s="155"/>
+      <c r="M125" s="156"/>
+    </row>
+    <row r="126" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E126" s="155"/>
+      <c r="F126" s="158"/>
+      <c r="G126" s="158"/>
+      <c r="H126" s="158"/>
+      <c r="I126" s="158"/>
+      <c r="J126" s="158"/>
+      <c r="K126" s="156"/>
+      <c r="L126" s="155"/>
+      <c r="M126" s="156"/>
+    </row>
+    <row r="127" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E127" s="155"/>
+      <c r="F127" s="158"/>
+      <c r="G127" s="158"/>
+      <c r="H127" s="158"/>
+      <c r="I127" s="158"/>
+      <c r="J127" s="158"/>
+      <c r="K127" s="156"/>
+      <c r="L127" s="166"/>
+      <c r="M127" s="167"/>
+    </row>
+    <row r="128" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E128" s="199" t="s">
+        <v>121</v>
+      </c>
+      <c r="F128" s="200"/>
+      <c r="G128" s="200"/>
+      <c r="H128" s="200"/>
+      <c r="I128" s="200"/>
+      <c r="J128" s="201">
+        <f>SUM(J118:J127)</f>
+        <v>160460.36038</v>
+      </c>
+      <c r="K128" s="191"/>
+      <c r="L128" s="168"/>
+      <c r="M128" s="169"/>
+    </row>
+  </sheetData>
+  <mergeCells count="50">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="E52:I52"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="E32:K32"/>
+    <mergeCell ref="L115:M115"/>
+    <mergeCell ref="L117:M117"/>
+    <mergeCell ref="E128:I128"/>
+    <mergeCell ref="J128:K128"/>
+    <mergeCell ref="E83:K83"/>
+    <mergeCell ref="E84:K84"/>
+    <mergeCell ref="E88:K88"/>
+    <mergeCell ref="L90:M90"/>
+    <mergeCell ref="L92:M92"/>
+    <mergeCell ref="E103:I103"/>
+    <mergeCell ref="J103:K103"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="E108:K108"/>
+    <mergeCell ref="E109:K109"/>
+    <mergeCell ref="E113:K113"/>
+    <mergeCell ref="E56:K56"/>
+    <mergeCell ref="E57:K57"/>
+    <mergeCell ref="E61:K61"/>
+    <mergeCell ref="L63:M63"/>
+    <mergeCell ref="L65:M65"/>
+    <mergeCell ref="E76:I76"/>
+    <mergeCell ref="J76:K76"/>
+    <mergeCell ref="E33:K33"/>
+    <mergeCell ref="E37:K37"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="L41:M41"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+</worksheet>
 </file>
--- a/PATXOT 512/Agosto/PATXOT 521 Agosto.xlsx
+++ b/PATXOT 512/Agosto/PATXOT 521 Agosto.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\PATXOT 512\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PATXOT 512\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEEDAFE4-10BB-4BCE-AA7E-11DE057360DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56E022D1-3448-4832-81C8-A58423EF4291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="PRORRATEO EXPRESS" sheetId="6" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$45</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$49</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">edesur!$A$1:$H$15</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$L$16</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'PRORRATEO EXPRESS'!$A$1:$L$16</definedName>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="145">
   <si>
     <t>UF</t>
   </si>
@@ -137,9 +137,6 @@
     <t>MANTEIGA LUCAS</t>
   </si>
   <si>
-    <t>AYSA</t>
-  </si>
-  <si>
     <t>LIMPIEZA / MANTENIMIENTO / GASTOS GENERALES</t>
   </si>
   <si>
@@ -272,9 +269,6 @@
     <t>TOTAL GASTOS ORDINARIOS (A) - SIN CONTAR EDESUR</t>
   </si>
   <si>
-    <t>Edesur</t>
-  </si>
-  <si>
     <t>PATXOT</t>
   </si>
   <si>
@@ -410,15 +404,9 @@
     <t>ENERO 2025</t>
   </si>
   <si>
-    <t>Poliza de Seguro Obligatoria Mercantil andina N. 1181593</t>
-  </si>
-  <si>
     <t>Prevision ordinaria</t>
   </si>
   <si>
-    <t>Honorarios MAYO 2025</t>
-  </si>
-  <si>
     <t>Deuda</t>
   </si>
   <si>
@@ -434,10 +422,49 @@
     <t>Obra</t>
   </si>
   <si>
-    <t>MANO DE OBRA (1/2)</t>
-  </si>
-  <si>
     <t>LIQUIDACIÓN EXPENSAS AGOSTO 2025</t>
+  </si>
+  <si>
+    <t>MANO DE OBRA (2/2)</t>
+  </si>
+  <si>
+    <t>AYSA - Agosto</t>
+  </si>
+  <si>
+    <t>AYSA - Julio</t>
+  </si>
+  <si>
+    <t>Edesur - Julio</t>
+  </si>
+  <si>
+    <t>Edesur - Agosto</t>
+  </si>
+  <si>
+    <t>Poliza de Seguro Obligatoria Mercantil andina N. 1181593 - Agosto</t>
+  </si>
+  <si>
+    <t>Poliza de Seguro Obligatoria Mercantil andina N. 1181593 - Julio</t>
+  </si>
+  <si>
+    <t>Honorarios Administracion - Julio</t>
+  </si>
+  <si>
+    <t>Honorarios Administracion - Agosto</t>
+  </si>
+  <si>
+    <t>Honorarios Administracion - Junio</t>
+  </si>
+  <si>
+    <t>Poliza de Seguro Obligatoria Mercantil andina N. 1181593 - Junio</t>
+  </si>
+  <si>
+    <t>AYSA - Junio</t>
+  </si>
+  <si>
+    <t>Edesur - Junio</t>
+  </si>
+  <si>
+    <t>EDESUR:</t>
   </si>
 </sst>
 </file>
@@ -1449,7 +1476,7 @@
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="214">
+  <cellXfs count="213">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1530,7 +1557,6 @@
     <xf numFmtId="166" fontId="1" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1715,16 +1741,14 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="15" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="15" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1805,9 +1829,6 @@
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1820,8 +1841,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -2191,378 +2219,435 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F56"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:F60"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="25"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="170" t="s">
-        <v>135</v>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="169" t="s">
+        <v>130</v>
       </c>
       <c r="B7" s="26"/>
       <c r="C7" s="26"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="23" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="87" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="86" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="76"/>
+      <c r="B16" s="75"/>
       <c r="C16" s="11"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="76" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" s="88" t="s">
-        <v>63</v>
-      </c>
-      <c r="C17" s="172">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="75" t="s">
+        <v>132</v>
+      </c>
+      <c r="B17" s="87" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" s="211">
         <v>79724.34</v>
       </c>
       <c r="D17" s="48"/>
       <c r="F17" s="14"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="76"/>
-      <c r="B18" s="88"/>
-      <c r="C18" s="85"/>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="75" t="s">
+        <v>133</v>
+      </c>
+      <c r="B18" s="87" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="84">
+        <v>84579.51</v>
+      </c>
       <c r="D18" s="48"/>
       <c r="F18" s="14"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="76"/>
-      <c r="B19" s="88"/>
-      <c r="C19" s="85"/>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="75" t="s">
+        <v>142</v>
+      </c>
+      <c r="B19" s="87" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="84">
+        <v>74186.03</v>
+      </c>
       <c r="D19" s="5"/>
       <c r="E19" s="14"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="89"/>
-      <c r="B20" s="90"/>
-      <c r="C20" s="61">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="88"/>
+      <c r="B20" s="89"/>
+      <c r="C20" s="60">
         <f>SUM(C17:C19)</f>
-        <v>79724.34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="87" t="s">
+        <v>238489.87999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="86" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="87"/>
+      <c r="C21" s="90"/>
+    </row>
+    <row r="22" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="75" t="s">
+        <v>139</v>
+      </c>
+      <c r="B22" s="91"/>
+      <c r="C22" s="84">
+        <v>30000</v>
+      </c>
+      <c r="F22" s="22"/>
+    </row>
+    <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="75" t="s">
+        <v>138</v>
+      </c>
+      <c r="B23" s="91"/>
+      <c r="C23" s="84">
+        <v>30000</v>
+      </c>
+      <c r="F23" s="22"/>
+    </row>
+    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="75" t="s">
+        <v>140</v>
+      </c>
+      <c r="B24" s="91"/>
+      <c r="C24" s="84">
+        <v>30000</v>
+      </c>
+      <c r="F24" s="22"/>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="75" t="s">
+        <v>136</v>
+      </c>
+      <c r="B25" s="91"/>
+      <c r="C25" s="84">
+        <v>36534.6</v>
+      </c>
+      <c r="F25" s="22"/>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="75" t="s">
+        <v>137</v>
+      </c>
+      <c r="B26" s="91"/>
+      <c r="C26" s="84">
+        <v>36534.6</v>
+      </c>
+      <c r="F26" s="22"/>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="75" t="s">
+        <v>141</v>
+      </c>
+      <c r="B27" s="91"/>
+      <c r="C27" s="84">
+        <v>36534.6</v>
+      </c>
+      <c r="F27" s="22"/>
+    </row>
+    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="75" t="s">
+        <v>124</v>
+      </c>
+      <c r="B28" s="87"/>
+      <c r="C28" s="85"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="22"/>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="88"/>
+      <c r="B29" s="89"/>
+      <c r="C29" s="60">
+        <f>SUM(C21:C28)</f>
+        <v>199603.80000000002</v>
+      </c>
+      <c r="F29" s="22"/>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="79" t="s">
+        <v>78</v>
+      </c>
+      <c r="B30" s="79"/>
+      <c r="C30" s="92">
+        <f>+C29+C20</f>
+        <v>438093.68</v>
+      </c>
+      <c r="F30" s="22"/>
+    </row>
+    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C31" s="61"/>
+      <c r="F31" s="22"/>
+    </row>
+    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" s="61"/>
+      <c r="F32" s="22"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="75"/>
+      <c r="B33" s="75"/>
+      <c r="C33" s="84"/>
+      <c r="F33" s="22"/>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="75"/>
+      <c r="B34" s="75"/>
+      <c r="C34" s="85"/>
+      <c r="F34" s="22"/>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="75"/>
+      <c r="B35" s="75"/>
+      <c r="C35" s="85"/>
+      <c r="F35" s="22"/>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C36" s="63"/>
+      <c r="F36" s="22"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="23"/>
+      <c r="C37" s="24">
+        <f>+C33+C34+C35+C36</f>
+        <v>0</v>
+      </c>
+      <c r="E37" s="14"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" s="34"/>
+      <c r="C39" s="35">
+        <f>+C37+C30</f>
+        <v>438093.68</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="41" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="146" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="88"/>
-      <c r="C21" s="91"/>
-    </row>
-    <row r="22" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="76" t="s">
-        <v>128</v>
-      </c>
-      <c r="B22" s="92"/>
-      <c r="C22" s="85">
-        <v>30000</v>
-      </c>
-      <c r="F22" s="22"/>
-    </row>
-    <row r="23" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="76" t="s">
-        <v>126</v>
-      </c>
-      <c r="B23" s="92"/>
-      <c r="C23" s="171">
-        <v>36534.6</v>
-      </c>
-      <c r="F23" s="22"/>
-    </row>
-    <row r="24" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="76"/>
-      <c r="B24" s="92"/>
-      <c r="C24" s="85"/>
-      <c r="F24" s="22"/>
-    </row>
-    <row r="25" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="76"/>
-      <c r="B25" s="92"/>
-      <c r="C25" s="85"/>
-      <c r="F25" s="22"/>
-    </row>
-    <row r="26" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="76" t="s">
-        <v>127</v>
-      </c>
-      <c r="B26" s="88"/>
-      <c r="C26" s="86">
-        <v>150000</v>
-      </c>
-      <c r="D26" s="5"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="22"/>
-    </row>
-    <row r="27" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="89"/>
-      <c r="B27" s="90"/>
-      <c r="C27" s="61">
-        <f>SUM(C21:C26)</f>
-        <v>216534.6</v>
-      </c>
-      <c r="F27" s="22"/>
-    </row>
-    <row r="28" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="80" t="s">
-        <v>79</v>
-      </c>
-      <c r="B28" s="80"/>
-      <c r="C28" s="93">
-        <f>+C27+C20</f>
-        <v>296258.94</v>
-      </c>
-      <c r="F28" s="22"/>
-    </row>
-    <row r="29" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C29" s="62"/>
-      <c r="F29" s="22"/>
-    </row>
-    <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="C30" s="62"/>
-      <c r="F30" s="22"/>
-    </row>
-    <row r="31" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="76"/>
-      <c r="B31" s="76"/>
-      <c r="C31" s="85"/>
-      <c r="F31" s="22"/>
-    </row>
-    <row r="32" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="76"/>
-      <c r="B32" s="76"/>
-      <c r="C32" s="86"/>
-      <c r="F32" s="22"/>
-    </row>
-    <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="76"/>
-      <c r="B33" s="76"/>
-      <c r="C33" s="86"/>
-      <c r="F33" s="22"/>
-    </row>
-    <row r="34" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C34" s="64"/>
-      <c r="F34" s="22"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="23"/>
-      <c r="C35" s="24">
-        <f>+C31+C32+C33+C34</f>
-        <v>0</v>
-      </c>
-      <c r="E35" s="14"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" s="34"/>
-      <c r="C37" s="35">
-        <f>+C35+C28</f>
-        <v>296258.94</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="39" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="147" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="148"/>
-      <c r="C39" s="149"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="145" t="s">
+      <c r="B41" s="147"/>
+      <c r="C41" s="148"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="144" t="s">
         <v>10</v>
       </c>
-      <c r="B40" s="3"/>
-      <c r="C40" s="146">
-        <v>-225247.17452636751</v>
-      </c>
-      <c r="D40" s="6"/>
-      <c r="E40" s="6"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+      <c r="B42" s="3"/>
+      <c r="C42" s="145">
+        <v>8056.9037403397379</v>
+      </c>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>9</v>
       </c>
-      <c r="C41" s="32">
+      <c r="C43" s="32">
         <f>'prorrateo '!F15</f>
-        <v>234321.66826670722</v>
-      </c>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>80</v>
-      </c>
-      <c r="C42" s="94">
-        <f>-edesur!H1</f>
+        <v>114809.90303832441</v>
+      </c>
+      <c r="D43" s="14"/>
+      <c r="E43" s="14"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>135</v>
+      </c>
+      <c r="C44" s="93">
+        <v>-133418.04</v>
+      </c>
+      <c r="D44" s="14"/>
+      <c r="E44" s="14"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>134</v>
+      </c>
+      <c r="C45" s="93">
+        <v>-125968.51</v>
+      </c>
+      <c r="D45" s="14"/>
+      <c r="E45" s="14"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>143</v>
+      </c>
+      <c r="C46" s="93">
         <v>-10296.959999999999</v>
       </c>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>65</v>
-      </c>
-      <c r="C43" s="94">
-        <f>-(C28-C26)</f>
-        <v>-146258.94</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="36" t="s">
+      <c r="D46" s="14"/>
+      <c r="E46" s="14"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>64</v>
+      </c>
+      <c r="C47" s="93">
+        <f>-(C30-C28)</f>
+        <v>-438093.68</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="B44" s="33"/>
-      <c r="C44" s="40">
-        <f>SUM(C40:C43)</f>
-        <v>-147481.40625966029</v>
-      </c>
-      <c r="D44" s="6"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="19"/>
-      <c r="B45" s="18"/>
-      <c r="C45" s="20"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="19"/>
-      <c r="B46" s="18"/>
-      <c r="C46" s="20"/>
-      <c r="F46" s="95"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="19"/>
-      <c r="B47" s="18"/>
-      <c r="C47" s="20"/>
-    </row>
-    <row r="48" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="74" t="s">
-        <v>58</v>
-      </c>
-      <c r="B48" s="75"/>
-      <c r="C48" s="78">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="76" t="s">
-        <v>64</v>
-      </c>
-      <c r="B49" s="76"/>
-      <c r="C49" s="83">
-        <f>-C35</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="76"/>
-      <c r="B50" s="76"/>
-      <c r="C50" s="83"/>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="76"/>
-      <c r="B51" s="76"/>
-      <c r="C51" s="84"/>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="80" t="s">
+      <c r="B48" s="33"/>
+      <c r="C48" s="40">
+        <f>SUM(C42:C47)</f>
+        <v>-584910.38322133583</v>
+      </c>
+      <c r="D48" s="6"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="19"/>
+      <c r="B49" s="18"/>
+      <c r="C49" s="20"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="19"/>
+      <c r="B50" s="18"/>
+      <c r="C50" s="20"/>
+      <c r="F50" s="94"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="19"/>
+      <c r="B51" s="18"/>
+      <c r="C51" s="20"/>
+    </row>
+    <row r="52" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A52" s="73" t="s">
+        <v>57</v>
+      </c>
+      <c r="B52" s="74"/>
+      <c r="C52" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="75" t="s">
+        <v>63</v>
+      </c>
+      <c r="B53" s="75"/>
+      <c r="C53" s="82">
+        <f>-C37</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="75"/>
+      <c r="B54" s="75"/>
+      <c r="C54" s="82"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="75"/>
+      <c r="B55" s="75"/>
+      <c r="C55" s="83"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="B52" s="77"/>
-      <c r="C52" s="79">
-        <f>SUM(C48:C51)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="18"/>
-      <c r="B53" s="18"/>
-      <c r="C53" s="18"/>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="18"/>
-      <c r="B54" s="18"/>
-      <c r="C54" s="18"/>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" s="18"/>
-      <c r="B55" s="18"/>
-      <c r="C55" s="18"/>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="18"/>
-      <c r="B56" s="18"/>
-      <c r="C56" s="18"/>
+      <c r="B56" s="76"/>
+      <c r="C56" s="78">
+        <f>SUM(C52:C55)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="18"/>
+      <c r="B57" s="18"/>
+      <c r="C57" s="18"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="18"/>
+      <c r="B58" s="18"/>
+      <c r="C58" s="18"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="18"/>
+      <c r="B59" s="18"/>
+      <c r="C59" s="18"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="18"/>
+      <c r="B60" s="18"/>
+      <c r="C60" s="18"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2581,58 +2666,66 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N128"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
     <col min="2" max="2" width="4" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" customWidth="1"/>
-    <col min="6" max="6" width="10.6640625" customWidth="1"/>
-    <col min="7" max="7" width="9.5546875" customWidth="1"/>
-    <col min="8" max="8" width="10.33203125" customWidth="1"/>
-    <col min="9" max="9" width="8.33203125" customWidth="1"/>
-    <col min="10" max="10" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.44140625" customWidth="1"/>
-    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.44140625" style="21"/>
+    <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" customWidth="1"/>
+    <col min="7" max="7" width="9.5703125" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" customWidth="1"/>
+    <col min="9" max="9" width="8.28515625" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="53" t="s">
-        <v>49</v>
-      </c>
-      <c r="E1" s="50">
-        <v>291359.89</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="98">
+    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="52" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="14">
+        <v>438093.68</v>
+      </c>
+      <c r="H1" s="212" t="s">
+        <v>144</v>
+      </c>
+      <c r="I1" s="212"/>
+      <c r="J1" s="14">
+        <f>-('detalle y gastos'!C44+'detalle y gastos'!C45+'detalle y gastos'!C46)</f>
+        <v>269683.51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="97">
         <f>'detalle y gastos'!B7</f>
         <v>0</v>
       </c>
-      <c r="B2" s="99"/>
-      <c r="C2" s="100"/>
-      <c r="D2" s="100"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="102"/>
-      <c r="K2" s="102"/>
-      <c r="L2" s="103"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="183" t="s">
+      <c r="B2" s="98"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="98"/>
+      <c r="H2" s="98"/>
+      <c r="I2" s="98"/>
+      <c r="J2" s="101"/>
+      <c r="K2" s="101"/>
+      <c r="L2" s="102"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="182" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="184"/>
-      <c r="C3" s="179" t="s">
+      <c r="B3" s="183"/>
+      <c r="C3" s="178" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="181" t="s">
-        <v>56</v>
+      <c r="D3" s="180" t="s">
+        <v>55</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>19</v>
@@ -2640,507 +2733,489 @@
       <c r="F3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="179" t="s">
-        <v>54</v>
+      <c r="G3" s="178" t="s">
+        <v>53</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I3" s="177" t="s">
+        <v>44</v>
+      </c>
+      <c r="I3" s="176" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="187" t="s">
-        <v>112</v>
-      </c>
-      <c r="K3" s="179" t="s">
-        <v>43</v>
+      <c r="J3" s="186" t="s">
+        <v>110</v>
+      </c>
+      <c r="K3" s="178" t="s">
+        <v>42</v>
       </c>
       <c r="L3" s="45" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="185"/>
-      <c r="B4" s="186"/>
-      <c r="C4" s="180"/>
-      <c r="D4" s="182"/>
-      <c r="E4" s="58" t="s">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="184"/>
+      <c r="B4" s="185"/>
+      <c r="C4" s="179"/>
+      <c r="D4" s="181"/>
+      <c r="E4" s="57" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="G4" s="180"/>
+        <v>45</v>
+      </c>
+      <c r="G4" s="179"/>
       <c r="H4" s="37">
         <v>0.04</v>
       </c>
-      <c r="I4" s="178"/>
-      <c r="J4" s="188"/>
-      <c r="K4" s="180"/>
+      <c r="I4" s="177"/>
+      <c r="J4" s="187"/>
+      <c r="K4" s="179"/>
       <c r="L4" s="38" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="175">
+    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="174">
         <v>1</v>
       </c>
-      <c r="B5" s="176"/>
-      <c r="C5" s="111" t="s">
+      <c r="B5" s="175"/>
+      <c r="C5" s="110" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" s="58"/>
+      <c r="E5" s="149">
+        <v>41531.40466575251</v>
+      </c>
+      <c r="F5" s="150">
+        <f t="shared" ref="F5:F9" si="0">E5</f>
+        <v>41531.40466575251</v>
+      </c>
+      <c r="G5" s="151">
+        <f>E5-F5</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="151">
+        <f>IF(G5&gt;0,G5*4%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="95">
+        <v>13.8</v>
+      </c>
+      <c r="J5" s="96">
+        <f>E$1*I5/100</f>
+        <v>60456.927839999997</v>
+      </c>
+      <c r="K5" s="142">
+        <f>J$1*I5/100</f>
+        <v>37216.324380000005</v>
+      </c>
+      <c r="L5" s="103">
+        <f>G5+H5+J5+K5</f>
+        <v>97673.252219999995</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="174">
+        <v>2</v>
+      </c>
+      <c r="B6" s="175"/>
+      <c r="C6" s="110" t="s">
         <v>66</v>
       </c>
-      <c r="D5" s="59"/>
-      <c r="E5" s="150">
-        <v>31310.712786555188</v>
-      </c>
-      <c r="F5" s="151">
-        <f t="shared" ref="F5:F9" si="0">E5</f>
-        <v>31310.712786555188</v>
-      </c>
-      <c r="G5" s="152">
-        <f>E5-F5</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="152">
-        <f>IF(G5&gt;0,G5*4%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="I5" s="96">
-        <v>13.8</v>
-      </c>
-      <c r="J5" s="97">
-        <f>E$1*I5/100</f>
-        <v>40207.664820000005</v>
-      </c>
-      <c r="K5" s="143">
-        <f>edesur!H5</f>
-        <v>1411.9577257525084</v>
-      </c>
-      <c r="L5" s="104">
-        <f>G5+H5+J5+K5</f>
-        <v>41619.622545752514</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="27" x14ac:dyDescent="0.3">
-      <c r="A6" s="175">
-        <v>2</v>
-      </c>
-      <c r="B6" s="176"/>
-      <c r="C6" s="111" t="s">
+      <c r="D6" s="72" t="s">
+        <v>71</v>
+      </c>
+      <c r="E6" s="149">
+        <v>36166.928390240799</v>
+      </c>
+      <c r="F6" s="150">
+        <f t="shared" si="0"/>
+        <v>36166.928390240799</v>
+      </c>
+      <c r="G6" s="151">
+        <f t="shared" ref="G6:G14" si="1">E6-F6</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="151">
+        <f t="shared" ref="H6:H14" si="2">IF(G6&gt;0,G6*4%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="95">
+        <v>11.86</v>
+      </c>
+      <c r="J6" s="96">
+        <f t="shared" ref="J6:J14" si="3">E$1*I6/100</f>
+        <v>51957.910447999995</v>
+      </c>
+      <c r="K6" s="142">
+        <f t="shared" ref="K6:K14" si="4">J$1*I6/100</f>
+        <v>31984.464285999999</v>
+      </c>
+      <c r="L6" s="103">
+        <f t="shared" ref="L6:L14" si="5">G6+H6+J6+K6</f>
+        <v>83942.374733999997</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="174">
+        <v>3</v>
+      </c>
+      <c r="B7" s="175"/>
+      <c r="C7" s="110" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="72" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" s="149">
+        <v>37894.033173585289</v>
+      </c>
+      <c r="F7" s="150"/>
+      <c r="G7" s="151">
+        <f t="shared" si="1"/>
+        <v>37894.033173585289</v>
+      </c>
+      <c r="H7" s="151">
+        <f t="shared" si="2"/>
+        <v>1515.7613269434116</v>
+      </c>
+      <c r="I7" s="95">
+        <v>12.46</v>
+      </c>
+      <c r="J7" s="96">
+        <f t="shared" si="3"/>
+        <v>54586.472527999998</v>
+      </c>
+      <c r="K7" s="142">
+        <f t="shared" si="4"/>
+        <v>33602.565346000003</v>
+      </c>
+      <c r="L7" s="103">
+        <f t="shared" si="5"/>
+        <v>127598.83237452871</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A8" s="174">
+        <v>4</v>
+      </c>
+      <c r="B8" s="175"/>
+      <c r="C8" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="D6" s="73" t="s">
-        <v>72</v>
-      </c>
-      <c r="E6" s="150">
-        <v>30871.318343297658</v>
-      </c>
-      <c r="F6" s="151">
+      <c r="D8" s="72" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" s="149">
+        <v>44723.725567140471</v>
+      </c>
+      <c r="F8" s="150"/>
+      <c r="G8" s="151">
+        <f t="shared" si="1"/>
+        <v>44723.725567140471</v>
+      </c>
+      <c r="H8" s="151">
+        <f t="shared" si="2"/>
+        <v>1788.949022685619</v>
+      </c>
+      <c r="I8" s="95">
+        <v>14.75</v>
+      </c>
+      <c r="J8" s="96">
+        <f t="shared" si="3"/>
+        <v>64618.817800000004</v>
+      </c>
+      <c r="K8" s="142">
+        <f t="shared" si="4"/>
+        <v>39778.317725000001</v>
+      </c>
+      <c r="L8" s="103">
+        <f t="shared" si="5"/>
+        <v>150909.8101148261</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="174">
+        <v>5</v>
+      </c>
+      <c r="B9" s="175"/>
+      <c r="C9" s="110" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" s="72" t="s">
+        <v>74</v>
+      </c>
+      <c r="E9" s="149">
+        <v>37111.569982331108</v>
+      </c>
+      <c r="F9" s="150">
         <f t="shared" si="0"/>
-        <v>30871.318343297658</v>
-      </c>
-      <c r="G6" s="152">
-        <f t="shared" ref="G6:G14" si="1">E6-F6</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="152">
-        <f t="shared" ref="H6:H14" si="2">IF(G6&gt;0,G6*4%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="96">
-        <v>11.86</v>
-      </c>
-      <c r="J6" s="97">
-        <f t="shared" ref="J6:J14" si="3">E$1*I6/100</f>
-        <v>34555.282954000002</v>
-      </c>
-      <c r="K6" s="143">
-        <f>edesur!H6</f>
-        <v>1687.4616722408025</v>
-      </c>
-      <c r="L6" s="104">
-        <f t="shared" ref="L6:L14" si="4">G6+H6+J6+K6</f>
-        <v>36242.744626240805</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="27" x14ac:dyDescent="0.3">
-      <c r="A7" s="175">
-        <v>3</v>
-      </c>
-      <c r="B7" s="176"/>
-      <c r="C7" s="111" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" s="73" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" s="150">
-        <v>31575.545756876258</v>
-      </c>
-      <c r="F7" s="151">
-        <f t="shared" si="0"/>
-        <v>31575.545756876258</v>
-      </c>
-      <c r="G7" s="152">
+        <v>37111.569982331108</v>
+      </c>
+      <c r="G9" s="151">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H7" s="152">
+      <c r="H9" s="151">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I7" s="96">
-        <v>12.46</v>
-      </c>
-      <c r="J7" s="97">
+      <c r="I9" s="95">
+        <v>12.41</v>
+      </c>
+      <c r="J9" s="96">
         <f t="shared" si="3"/>
-        <v>36303.442294000008</v>
-      </c>
-      <c r="K7" s="143">
-        <f>edesur!H7</f>
-        <v>1670.2426755852841</v>
-      </c>
-      <c r="L7" s="104">
+        <v>54367.425687999996</v>
+      </c>
+      <c r="K9" s="142">
         <f t="shared" si="4"/>
-        <v>37973.684969585294</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="175">
-        <v>4</v>
-      </c>
-      <c r="B8" s="176"/>
-      <c r="C8" s="111" t="s">
-        <v>68</v>
-      </c>
-      <c r="D8" s="73" t="s">
-        <v>74</v>
-      </c>
-      <c r="E8" s="150">
-        <v>36252.089402090307</v>
-      </c>
-      <c r="F8" s="151">
-        <f t="shared" si="0"/>
-        <v>36252.089402090307</v>
-      </c>
-      <c r="G8" s="152">
+        <v>33467.723591000002</v>
+      </c>
+      <c r="L9" s="103">
+        <f>G9+H9+J9+K9</f>
+        <v>87835.149279000005</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="174">
+        <v>6</v>
+      </c>
+      <c r="B10" s="175"/>
+      <c r="C10" s="110" t="s">
+        <v>69</v>
+      </c>
+      <c r="D10" s="72"/>
+      <c r="E10" s="149">
+        <v>37332.293419986621</v>
+      </c>
+      <c r="F10" s="150"/>
+      <c r="G10" s="151">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H8" s="152">
+        <v>37332.293419986621</v>
+      </c>
+      <c r="H10" s="151">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I8" s="96">
-        <v>14.75</v>
-      </c>
-      <c r="J8" s="97">
+        <v>1493.2917367994648</v>
+      </c>
+      <c r="I10" s="95">
+        <v>12.48</v>
+      </c>
+      <c r="J10" s="96">
         <f t="shared" si="3"/>
-        <v>42975.583775000006</v>
-      </c>
-      <c r="K8" s="143">
-        <f>edesur!H8</f>
-        <v>1842.432642140468</v>
-      </c>
-      <c r="L8" s="104">
+        <v>54674.091264000002</v>
+      </c>
+      <c r="K10" s="142">
         <f t="shared" si="4"/>
-        <v>44818.016417140476</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="175">
-        <v>5</v>
-      </c>
-      <c r="B9" s="176"/>
-      <c r="C9" s="111" t="s">
-        <v>69</v>
-      </c>
-      <c r="D9" s="73" t="s">
+        <v>33656.502048000002</v>
+      </c>
+      <c r="L10" s="103">
+        <f t="shared" si="5"/>
+        <v>127156.17846878609</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="174">
+        <v>7</v>
+      </c>
+      <c r="B11" s="175"/>
+      <c r="C11" s="110" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="72"/>
+      <c r="E11" s="149">
+        <v>54686.953726963213</v>
+      </c>
+      <c r="F11" s="150"/>
+      <c r="G11" s="151">
+        <f t="shared" si="1"/>
+        <v>54686.953726963213</v>
+      </c>
+      <c r="H11" s="151">
+        <f t="shared" si="2"/>
+        <v>2187.4781490785285</v>
+      </c>
+      <c r="I11" s="95">
+        <v>18.260000000000002</v>
+      </c>
+      <c r="J11" s="96">
+        <f t="shared" si="3"/>
+        <v>79995.905968000006</v>
+      </c>
+      <c r="K11" s="142">
+        <f t="shared" si="4"/>
+        <v>49244.208926000007</v>
+      </c>
+      <c r="L11" s="103">
+        <f t="shared" si="5"/>
+        <v>186114.54677004175</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="174" t="s">
         <v>75</v>
       </c>
-      <c r="E9" s="150">
-        <v>26179.162034284283</v>
-      </c>
-      <c r="F9" s="151">
-        <f t="shared" si="0"/>
-        <v>26179.162034284283</v>
-      </c>
-      <c r="G9" s="152">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H9" s="152">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I9" s="96">
-        <v>12.41</v>
-      </c>
-      <c r="J9" s="97">
-        <f t="shared" si="3"/>
-        <v>36157.762348999997</v>
-      </c>
-      <c r="K9" s="143">
-        <f>edesur!H9</f>
-        <v>1033.1397993311036</v>
-      </c>
-      <c r="L9" s="104">
-        <f>G9+H9+J9+K9</f>
-        <v>37190.902148331101</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="175">
-        <v>6</v>
-      </c>
-      <c r="B10" s="176"/>
-      <c r="C10" s="111" t="s">
-        <v>70</v>
-      </c>
-      <c r="D10" s="73"/>
-      <c r="E10" s="150">
-        <v>26422.052583705688</v>
-      </c>
-      <c r="F10" s="151">
-        <f>E10</f>
-        <v>26422.052583705688</v>
-      </c>
-      <c r="G10" s="152">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="152">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I10" s="96">
-        <v>12.48</v>
-      </c>
-      <c r="J10" s="97">
-        <f t="shared" si="3"/>
-        <v>36361.714272000005</v>
-      </c>
-      <c r="K10" s="143">
-        <f>edesur!H10</f>
-        <v>1050.358795986622</v>
-      </c>
-      <c r="L10" s="104">
-        <f t="shared" si="4"/>
-        <v>37412.073067986625</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="175">
-        <v>7</v>
-      </c>
-      <c r="B11" s="176"/>
-      <c r="C11" s="111" t="s">
-        <v>71</v>
-      </c>
-      <c r="D11" s="73"/>
-      <c r="E11" s="150">
-        <v>39198.725671190645</v>
-      </c>
-      <c r="F11" s="151">
-        <f>E11</f>
-        <v>39198.725671190645</v>
-      </c>
-      <c r="G11" s="152">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H11" s="152">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I11" s="96">
-        <v>18.260000000000002</v>
-      </c>
-      <c r="J11" s="97">
-        <f t="shared" si="3"/>
-        <v>53202.315914000006</v>
-      </c>
-      <c r="K11" s="143">
-        <f>edesur!H11</f>
-        <v>1601.3666889632107</v>
-      </c>
-      <c r="L11" s="104">
-        <f t="shared" si="4"/>
-        <v>54803.682602963214</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="175" t="s">
-        <v>76</v>
-      </c>
-      <c r="B12" s="176"/>
-      <c r="C12" s="111" t="str">
+      <c r="B12" s="175"/>
+      <c r="C12" s="110" t="str">
         <f>C9</f>
         <v>Grand Jorge</v>
       </c>
-      <c r="D12" s="73"/>
-      <c r="E12" s="150">
-        <v>4212.6036841376008</v>
-      </c>
-      <c r="F12" s="151">
-        <f t="shared" ref="F12:F14" si="5">E12</f>
-        <v>4212.6036841376008</v>
-      </c>
-      <c r="G12" s="152">
+      <c r="D12" s="72"/>
+      <c r="E12" s="149">
+        <v>3895.6564420000004</v>
+      </c>
+      <c r="F12" s="150"/>
+      <c r="G12" s="151">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H12" s="152">
+        <v>3895.6564420000004</v>
+      </c>
+      <c r="H12" s="151">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I12" s="96">
+        <v>155.82625768000003</v>
+      </c>
+      <c r="I12" s="95">
         <v>1.34</v>
       </c>
-      <c r="J12" s="97">
+      <c r="J12" s="96">
         <f t="shared" si="3"/>
-        <v>3904.2225260000005</v>
-      </c>
-      <c r="K12" s="143">
-        <v>0</v>
-      </c>
-      <c r="L12" s="104">
+        <v>5870.455312</v>
+      </c>
+      <c r="K12" s="142">
         <f t="shared" si="4"/>
-        <v>3904.2225260000005</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="175" t="s">
-        <v>77</v>
-      </c>
-      <c r="B13" s="176"/>
-      <c r="C13" s="111" t="str">
+        <v>3613.7590340000002</v>
+      </c>
+      <c r="L12" s="103">
+        <f t="shared" si="5"/>
+        <v>13535.697045680001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="174" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" s="175"/>
+      <c r="C13" s="110" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
       </c>
-      <c r="D13" s="73"/>
-      <c r="E13" s="150">
-        <v>4149.7290022848001</v>
-      </c>
-      <c r="F13" s="151">
+      <c r="D13" s="72"/>
+      <c r="E13" s="149">
+        <v>3837.5123159999998</v>
+      </c>
+      <c r="F13" s="150"/>
+      <c r="G13" s="151">
+        <f t="shared" si="1"/>
+        <v>3837.5123159999998</v>
+      </c>
+      <c r="H13" s="151">
+        <f t="shared" si="2"/>
+        <v>153.50049264</v>
+      </c>
+      <c r="I13" s="95">
+        <v>1.32</v>
+      </c>
+      <c r="J13" s="96">
+        <f t="shared" si="3"/>
+        <v>5782.8365760000006</v>
+      </c>
+      <c r="K13" s="142">
+        <f t="shared" si="4"/>
+        <v>3559.8223320000002</v>
+      </c>
+      <c r="L13" s="103">
         <f t="shared" si="5"/>
-        <v>4149.7290022848001</v>
-      </c>
-      <c r="G13" s="152">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H13" s="152">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I13" s="96">
-        <v>1.32</v>
-      </c>
-      <c r="J13" s="97">
-        <f t="shared" si="3"/>
-        <v>3845.9505480000003</v>
-      </c>
-      <c r="K13" s="143">
-        <v>0</v>
-      </c>
-      <c r="L13" s="104">
-        <f t="shared" si="4"/>
-        <v>3845.9505480000003</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="175" t="s">
-        <v>78</v>
-      </c>
-      <c r="B14" s="176"/>
-      <c r="C14" s="59" t="str">
+        <v>13333.671716640001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="174" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" s="175"/>
+      <c r="C14" s="58" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
       </c>
-      <c r="D14" s="73"/>
-      <c r="E14" s="150">
-        <v>4149.7290022848001</v>
-      </c>
-      <c r="F14" s="151">
+      <c r="D14" s="72"/>
+      <c r="E14" s="149">
+        <v>3837.5123159999998</v>
+      </c>
+      <c r="F14" s="150"/>
+      <c r="G14" s="151">
+        <f t="shared" si="1"/>
+        <v>3837.5123159999998</v>
+      </c>
+      <c r="H14" s="151">
+        <f t="shared" si="2"/>
+        <v>153.50049264</v>
+      </c>
+      <c r="I14" s="95">
+        <v>1.32</v>
+      </c>
+      <c r="J14" s="96">
+        <f t="shared" si="3"/>
+        <v>5782.8365760000006</v>
+      </c>
+      <c r="K14" s="142">
+        <f t="shared" si="4"/>
+        <v>3559.8223320000002</v>
+      </c>
+      <c r="L14" s="103">
         <f t="shared" si="5"/>
-        <v>4149.7290022848001</v>
-      </c>
-      <c r="G14" s="152">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H14" s="152">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="96">
-        <v>1.32</v>
-      </c>
-      <c r="J14" s="97">
-        <f t="shared" si="3"/>
-        <v>3845.9505480000003</v>
-      </c>
-      <c r="K14" s="143">
-        <v>0</v>
-      </c>
-      <c r="L14" s="104">
-        <f t="shared" si="4"/>
-        <v>3845.9505480000003</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="105" t="s">
+        <v>13333.671716640001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="104" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="106"/>
-      <c r="C15" s="107"/>
-      <c r="D15" s="107"/>
+      <c r="B15" s="105"/>
+      <c r="C15" s="106"/>
+      <c r="D15" s="106"/>
       <c r="E15" s="42">
         <f>SUM(E5:E14)</f>
-        <v>234321.66826670722</v>
-      </c>
-      <c r="F15" s="108">
+        <v>301017.59000000003</v>
+      </c>
+      <c r="F15" s="107">
         <f>SUM(F5:F14)</f>
-        <v>234321.66826670722</v>
-      </c>
-      <c r="G15" s="108"/>
-      <c r="H15" s="109">
+        <v>114809.90303832441</v>
+      </c>
+      <c r="G15" s="107"/>
+      <c r="H15" s="108">
         <f>SUM(H5:H14)</f>
-        <v>0</v>
-      </c>
-      <c r="I15" s="110">
+        <v>7448.3074784670234</v>
+      </c>
+      <c r="I15" s="109">
         <f t="shared" ref="I15" si="6">SUM(I5:I14)</f>
         <v>100</v>
       </c>
       <c r="J15" s="39">
         <f>SUM(J5:J14)</f>
-        <v>291359.89</v>
+        <v>438093.67999999993</v>
       </c>
       <c r="K15" s="42">
         <f>SUM(K5:K11)</f>
-        <v>10296.959999999999</v>
+        <v>258950.106302</v>
       </c>
       <c r="L15" s="42">
         <f>SUM(L5:L14)</f>
-        <v>301656.85000000003</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="53" t="s">
-        <v>50</v>
+        <v>901433.18444014259</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="52" t="s">
+        <v>49</v>
       </c>
       <c r="E18">
         <v>7454</v>
       </c>
     </row>
-    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="27" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B19" s="28"/>
       <c r="C19" s="29"/>
-      <c r="D19" s="71"/>
+      <c r="D19" s="70"/>
       <c r="E19">
         <v>14805</v>
       </c>
@@ -3148,11 +3223,11 @@
       <c r="G19" s="28"/>
       <c r="H19" s="28"/>
       <c r="I19" s="28"/>
-      <c r="J19" s="54"/>
-      <c r="K19" s="54"/>
+      <c r="J19" s="53"/>
+      <c r="K19" s="53"/>
       <c r="L19" s="31"/>
     </row>
-    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>0</v>
       </c>
@@ -3171,12 +3246,12 @@
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J20" s="55" t="s">
+      <c r="J20" s="54" t="s">
         <v>17</v>
       </c>
       <c r="K20" s="45"/>
@@ -3184,7 +3259,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -3193,7 +3268,7 @@
         <v>3177</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="37">
@@ -3210,7 +3285,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
         <v>1</v>
       </c>
@@ -3220,15 +3295,15 @@
       <c r="C22" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="72"/>
+      <c r="D22" s="71"/>
       <c r="E22">
         <v>3056</v>
       </c>
       <c r="F22" s="46">
         <v>37971</v>
       </c>
-      <c r="G22" s="51"/>
-      <c r="H22" s="51">
+      <c r="G22" s="50"/>
+      <c r="H22" s="50">
         <v>0</v>
       </c>
       <c r="I22" s="17">
@@ -3244,7 +3319,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
         <v>2</v>
       </c>
@@ -3254,15 +3329,15 @@
       <c r="C23" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="D23" s="72"/>
+      <c r="D23" s="71"/>
       <c r="E23">
         <v>3056</v>
       </c>
       <c r="F23" s="46">
         <v>66612</v>
       </c>
-      <c r="G23" s="51"/>
-      <c r="H23" s="51">
+      <c r="G23" s="50"/>
+      <c r="H23" s="50">
         <v>0</v>
       </c>
       <c r="I23" s="17">
@@ -3278,7 +3353,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
         <v>3</v>
       </c>
@@ -3288,7 +3363,7 @@
       <c r="C24" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D24" s="72"/>
+      <c r="D24" s="71"/>
       <c r="E24">
         <f>SUM(E16:E23)</f>
         <v>34845</v>
@@ -3296,8 +3371,8 @@
       <c r="F24" s="46">
         <v>0</v>
       </c>
-      <c r="G24" s="51"/>
-      <c r="H24" s="51">
+      <c r="G24" s="50"/>
+      <c r="H24" s="50">
         <v>0</v>
       </c>
       <c r="I24" s="17">
@@ -3313,7 +3388,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
         <v>4</v>
       </c>
@@ -3323,12 +3398,12 @@
       <c r="C25" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D25" s="72"/>
+      <c r="D25" s="71"/>
       <c r="F25" s="46">
         <v>0</v>
       </c>
-      <c r="G25" s="51"/>
-      <c r="H25" s="51">
+      <c r="G25" s="50"/>
+      <c r="H25" s="50">
         <v>0</v>
       </c>
       <c r="I25" s="17">
@@ -3344,7 +3419,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
         <v>5</v>
       </c>
@@ -3354,12 +3429,12 @@
       <c r="C26" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D26" s="72"/>
+      <c r="D26" s="71"/>
       <c r="F26" s="46">
         <v>80517</v>
       </c>
-      <c r="G26" s="51"/>
-      <c r="H26" s="51">
+      <c r="G26" s="50"/>
+      <c r="H26" s="50">
         <v>0</v>
       </c>
       <c r="I26" s="17">
@@ -3375,7 +3450,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
         <v>6</v>
       </c>
@@ -3385,12 +3460,12 @@
       <c r="C27" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D27" s="72"/>
+      <c r="D27" s="71"/>
       <c r="F27" s="46">
         <v>0</v>
       </c>
-      <c r="G27" s="51"/>
-      <c r="H27" s="51">
+      <c r="G27" s="50"/>
+      <c r="H27" s="50">
         <v>0</v>
       </c>
       <c r="I27" s="17">
@@ -3406,7 +3481,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
         <v>7</v>
       </c>
@@ -3416,15 +3491,15 @@
       <c r="C28" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D28" s="72"/>
+      <c r="D28" s="71"/>
       <c r="E28" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F28" s="46">
         <v>18542</v>
       </c>
-      <c r="G28" s="51"/>
-      <c r="H28" s="51">
+      <c r="G28" s="50"/>
+      <c r="H28" s="50">
         <v>0</v>
       </c>
       <c r="I28" s="17">
@@ -3440,7 +3515,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
         <v>8</v>
       </c>
@@ -3450,15 +3525,15 @@
       <c r="C29" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D29" s="72"/>
+      <c r="D29" s="71"/>
       <c r="E29" t="s">
         <v>19</v>
       </c>
       <c r="F29" s="46">
         <v>0</v>
       </c>
-      <c r="G29" s="51"/>
-      <c r="H29" s="51">
+      <c r="G29" s="50"/>
+      <c r="H29" s="50">
         <v>0</v>
       </c>
       <c r="I29" s="17">
@@ -3474,13 +3549,13 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>11</v>
       </c>
       <c r="B30" s="9"/>
       <c r="C30" s="10"/>
-      <c r="D30" s="70"/>
+      <c r="D30" s="69"/>
       <c r="E30" t="s">
         <v>20</v>
       </c>
@@ -3489,7 +3564,7 @@
         <v>203642</v>
       </c>
       <c r="G30" s="49"/>
-      <c r="H30" s="52">
+      <c r="H30" s="51">
         <f>SUM(H22:H29)</f>
         <v>0</v>
       </c>
@@ -3507,1192 +3582,1193 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="N31"/>
     </row>
-    <row r="32" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="189" t="s">
-        <v>113</v>
-      </c>
-      <c r="F32" s="190"/>
-      <c r="G32" s="190"/>
-      <c r="H32" s="190"/>
-      <c r="I32" s="190"/>
-      <c r="J32" s="190"/>
-      <c r="K32" s="191"/>
-      <c r="L32" s="153"/>
-      <c r="M32" s="154"/>
+      <c r="E32" s="188" t="s">
+        <v>111</v>
+      </c>
+      <c r="F32" s="189"/>
+      <c r="G32" s="189"/>
+      <c r="H32" s="189"/>
+      <c r="I32" s="189"/>
+      <c r="J32" s="189"/>
+      <c r="K32" s="190"/>
+      <c r="L32" s="152"/>
+      <c r="M32" s="153"/>
       <c r="N32"/>
     </row>
-    <row r="33" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
-      <c r="E33" s="192" t="s">
-        <v>114</v>
-      </c>
-      <c r="F33" s="190"/>
-      <c r="G33" s="190"/>
-      <c r="H33" s="190"/>
-      <c r="I33" s="190"/>
-      <c r="J33" s="190"/>
-      <c r="K33" s="191"/>
-      <c r="L33" s="155"/>
-      <c r="M33" s="156"/>
+      <c r="E33" s="191" t="s">
+        <v>112</v>
+      </c>
+      <c r="F33" s="189"/>
+      <c r="G33" s="189"/>
+      <c r="H33" s="189"/>
+      <c r="I33" s="189"/>
+      <c r="J33" s="189"/>
+      <c r="K33" s="190"/>
+      <c r="L33" s="154"/>
+      <c r="M33" s="155"/>
       <c r="N33"/>
     </row>
-    <row r="34" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
-      <c r="E34" s="153"/>
-      <c r="F34" s="157"/>
-      <c r="G34" s="157"/>
-      <c r="H34" s="157"/>
-      <c r="I34" s="158"/>
-      <c r="J34" s="158">
+      <c r="E34" s="152"/>
+      <c r="F34" s="156"/>
+      <c r="G34" s="156"/>
+      <c r="H34" s="156"/>
+      <c r="I34" s="157"/>
+      <c r="J34" s="157">
         <f>'detalle y gastos'!B7</f>
         <v>0</v>
       </c>
-      <c r="K34" s="156"/>
-      <c r="L34" s="155"/>
-      <c r="M34" s="156"/>
+      <c r="K34" s="155"/>
+      <c r="L34" s="154"/>
+      <c r="M34" s="155"/>
       <c r="N34"/>
     </row>
-    <row r="35" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
-      <c r="E35" s="155" t="s">
-        <v>115</v>
-      </c>
-      <c r="F35" s="158"/>
-      <c r="G35" s="158"/>
-      <c r="H35" s="158"/>
-      <c r="I35" s="158"/>
-      <c r="J35" s="158"/>
-      <c r="K35" s="156"/>
-      <c r="L35" s="155"/>
-      <c r="M35" s="156"/>
+      <c r="E35" s="154" t="s">
+        <v>113</v>
+      </c>
+      <c r="F35" s="157"/>
+      <c r="G35" s="157"/>
+      <c r="H35" s="157"/>
+      <c r="I35" s="157"/>
+      <c r="J35" s="157"/>
+      <c r="K35" s="155"/>
+      <c r="L35" s="154"/>
+      <c r="M35" s="155"/>
       <c r="N35"/>
     </row>
-    <row r="36" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
-      <c r="E36" s="159"/>
-      <c r="F36" s="160"/>
-      <c r="G36" s="160"/>
-      <c r="H36" s="160"/>
-      <c r="I36" s="160"/>
-      <c r="J36" s="160"/>
-      <c r="K36" s="161"/>
-      <c r="L36" s="155"/>
-      <c r="M36" s="156"/>
+      <c r="E36" s="158"/>
+      <c r="F36" s="159"/>
+      <c r="G36" s="159"/>
+      <c r="H36" s="159"/>
+      <c r="I36" s="159"/>
+      <c r="J36" s="159"/>
+      <c r="K36" s="160"/>
+      <c r="L36" s="154"/>
+      <c r="M36" s="155"/>
       <c r="N36"/>
     </row>
-    <row r="37" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="193" t="s">
-        <v>50</v>
-      </c>
-      <c r="F37" s="194"/>
-      <c r="G37" s="194"/>
-      <c r="H37" s="194"/>
-      <c r="I37" s="194"/>
-      <c r="J37" s="194"/>
-      <c r="K37" s="195"/>
-      <c r="L37" s="155"/>
-      <c r="M37" s="156"/>
+      <c r="E37" s="192" t="s">
+        <v>49</v>
+      </c>
+      <c r="F37" s="193"/>
+      <c r="G37" s="193"/>
+      <c r="H37" s="193"/>
+      <c r="I37" s="193"/>
+      <c r="J37" s="193"/>
+      <c r="K37" s="194"/>
+      <c r="L37" s="154"/>
+      <c r="M37" s="155"/>
       <c r="N37"/>
     </row>
-    <row r="38" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
-      <c r="E38" s="155"/>
-      <c r="F38" s="158"/>
-      <c r="G38" s="158"/>
-      <c r="H38" s="158"/>
-      <c r="I38" s="158"/>
-      <c r="J38" s="158"/>
-      <c r="K38" s="156"/>
-      <c r="L38" s="155"/>
-      <c r="M38" s="156"/>
+      <c r="E38" s="154"/>
+      <c r="F38" s="157"/>
+      <c r="G38" s="157"/>
+      <c r="H38" s="157"/>
+      <c r="I38" s="157"/>
+      <c r="J38" s="157"/>
+      <c r="K38" s="155"/>
+      <c r="L38" s="154"/>
+      <c r="M38" s="155"/>
       <c r="N38"/>
     </row>
-    <row r="39" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
-      <c r="E39" s="155" t="s">
-        <v>116</v>
-      </c>
-      <c r="F39" s="158"/>
-      <c r="G39" s="158" t="str">
+      <c r="E39" s="154" t="s">
+        <v>114</v>
+      </c>
+      <c r="F39" s="157"/>
+      <c r="G39" s="157" t="str">
         <f>C7</f>
         <v>Maceyle Gabriela</v>
       </c>
-      <c r="H39" s="158"/>
-      <c r="I39" s="158" t="s">
-        <v>117</v>
-      </c>
-      <c r="J39" s="162">
+      <c r="H39" s="157"/>
+      <c r="I39" s="157" t="s">
+        <v>115</v>
+      </c>
+      <c r="J39" s="161">
         <v>45674</v>
       </c>
-      <c r="K39" s="156"/>
-      <c r="L39" s="196" t="s">
-        <v>118</v>
-      </c>
-      <c r="M39" s="197"/>
+      <c r="K39" s="155"/>
+      <c r="L39" s="195" t="s">
+        <v>116</v>
+      </c>
+      <c r="M39" s="196"/>
       <c r="N39"/>
     </row>
-    <row r="40" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
-      <c r="E40" s="155" t="s">
-        <v>119</v>
-      </c>
-      <c r="F40" s="163">
+      <c r="E40" s="154" t="s">
+        <v>117</v>
+      </c>
+      <c r="F40" s="162">
         <v>3</v>
       </c>
-      <c r="G40" s="158"/>
-      <c r="H40" s="158"/>
-      <c r="I40" s="158"/>
-      <c r="J40" s="158"/>
-      <c r="K40" s="156"/>
-      <c r="L40" s="155"/>
-      <c r="M40" s="156"/>
+      <c r="G40" s="157"/>
+      <c r="H40" s="157"/>
+      <c r="I40" s="157"/>
+      <c r="J40" s="157"/>
+      <c r="K40" s="155"/>
+      <c r="L40" s="154"/>
+      <c r="M40" s="155"/>
       <c r="N40"/>
     </row>
-    <row r="41" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
-      <c r="E41" s="155"/>
-      <c r="F41" s="158"/>
-      <c r="G41" s="158"/>
-      <c r="H41" s="158"/>
-      <c r="I41" s="158"/>
-      <c r="J41" s="158"/>
-      <c r="K41" s="156"/>
-      <c r="L41" s="198"/>
-      <c r="M41" s="197"/>
+      <c r="E41" s="154"/>
+      <c r="F41" s="157"/>
+      <c r="G41" s="157"/>
+      <c r="H41" s="157"/>
+      <c r="I41" s="157"/>
+      <c r="J41" s="157"/>
+      <c r="K41" s="155"/>
+      <c r="L41" s="197"/>
+      <c r="M41" s="196"/>
       <c r="N41"/>
     </row>
-    <row r="42" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
-      <c r="E42" s="155" t="s">
-        <v>49</v>
-      </c>
-      <c r="F42" s="158"/>
-      <c r="G42" s="158"/>
-      <c r="H42" s="158"/>
-      <c r="I42" s="158"/>
-      <c r="J42" s="164">
+      <c r="E42" s="154" t="s">
+        <v>48</v>
+      </c>
+      <c r="F42" s="157"/>
+      <c r="G42" s="157"/>
+      <c r="H42" s="157"/>
+      <c r="I42" s="157"/>
+      <c r="J42" s="163">
         <f>J7</f>
-        <v>36303.442294000008</v>
-      </c>
-      <c r="K42" s="156"/>
-      <c r="L42" s="155"/>
-      <c r="M42" s="156"/>
+        <v>54586.472527999998</v>
+      </c>
+      <c r="K42" s="155"/>
+      <c r="L42" s="154"/>
+      <c r="M42" s="155"/>
       <c r="N42"/>
     </row>
-    <row r="43" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
-      <c r="E43" s="165" t="s">
-        <v>120</v>
-      </c>
-      <c r="F43" s="158"/>
-      <c r="G43" s="158"/>
-      <c r="H43" s="158"/>
-      <c r="I43" s="158"/>
-      <c r="J43" s="164">
+      <c r="E43" s="164" t="s">
+        <v>118</v>
+      </c>
+      <c r="F43" s="157"/>
+      <c r="G43" s="157"/>
+      <c r="H43" s="157"/>
+      <c r="I43" s="157"/>
+      <c r="J43" s="163">
         <f>K7</f>
-        <v>1670.2426755852841</v>
-      </c>
-      <c r="K43" s="156"/>
-      <c r="L43" s="155"/>
-      <c r="M43" s="156"/>
+        <v>33602.565346000003</v>
+      </c>
+      <c r="K43" s="155"/>
+      <c r="L43" s="154"/>
+      <c r="M43" s="155"/>
       <c r="N43"/>
     </row>
-    <row r="44" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
-      <c r="E44" s="165" t="s">
-        <v>122</v>
-      </c>
-      <c r="F44" s="158"/>
-      <c r="G44" s="158"/>
-      <c r="H44" s="158"/>
-      <c r="I44" s="158"/>
-      <c r="J44" s="164">
+      <c r="E44" s="164" t="s">
+        <v>120</v>
+      </c>
+      <c r="F44" s="157"/>
+      <c r="G44" s="157"/>
+      <c r="H44" s="157"/>
+      <c r="I44" s="157"/>
+      <c r="J44" s="163">
         <f>G7+H7</f>
-        <v>0</v>
-      </c>
-      <c r="K44" s="156"/>
-      <c r="L44" s="155"/>
-      <c r="M44" s="156"/>
+        <v>39409.794500528704</v>
+      </c>
+      <c r="K44" s="155"/>
+      <c r="L44" s="154"/>
+      <c r="M44" s="155"/>
       <c r="N44"/>
     </row>
-    <row r="45" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
-      <c r="E45" s="165"/>
-      <c r="F45" s="158"/>
-      <c r="G45" s="158"/>
-      <c r="H45" s="158"/>
-      <c r="I45" s="158"/>
-      <c r="J45" s="164"/>
-      <c r="K45" s="156"/>
-      <c r="L45" s="155"/>
-      <c r="M45" s="156"/>
+      <c r="E45" s="164"/>
+      <c r="F45" s="157"/>
+      <c r="G45" s="157"/>
+      <c r="H45" s="157"/>
+      <c r="I45" s="157"/>
+      <c r="J45" s="163"/>
+      <c r="K45" s="155"/>
+      <c r="L45" s="154"/>
+      <c r="M45" s="155"/>
       <c r="N45"/>
     </row>
-    <row r="46" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
-      <c r="E46" s="165"/>
-      <c r="F46" s="158"/>
-      <c r="G46" s="158"/>
-      <c r="H46" s="158"/>
-      <c r="I46" s="158"/>
-      <c r="J46" s="164"/>
-      <c r="K46" s="156"/>
-      <c r="L46" s="155"/>
-      <c r="M46" s="156"/>
+      <c r="E46" s="164"/>
+      <c r="F46" s="157"/>
+      <c r="G46" s="157"/>
+      <c r="H46" s="157"/>
+      <c r="I46" s="157"/>
+      <c r="J46" s="163"/>
+      <c r="K46" s="155"/>
+      <c r="L46" s="154"/>
+      <c r="M46" s="155"/>
       <c r="N46"/>
     </row>
-    <row r="47" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
-      <c r="F47" s="158"/>
-      <c r="G47" s="158"/>
-      <c r="H47" s="158"/>
-      <c r="I47" s="158"/>
-      <c r="J47" s="164"/>
-      <c r="K47" s="156"/>
-      <c r="L47" s="155"/>
-      <c r="M47" s="156"/>
+      <c r="F47" s="157"/>
+      <c r="G47" s="157"/>
+      <c r="H47" s="157"/>
+      <c r="I47" s="157"/>
+      <c r="J47" s="163"/>
+      <c r="K47" s="155"/>
+      <c r="L47" s="154"/>
+      <c r="M47" s="155"/>
       <c r="N47"/>
     </row>
-    <row r="48" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
-      <c r="E48" s="165"/>
-      <c r="F48" s="158"/>
-      <c r="G48" s="158"/>
-      <c r="H48" s="158"/>
-      <c r="I48" s="158"/>
-      <c r="J48" s="164"/>
-      <c r="K48" s="156"/>
-      <c r="L48" s="155"/>
-      <c r="M48" s="156"/>
+      <c r="E48" s="164"/>
+      <c r="F48" s="157"/>
+      <c r="G48" s="157"/>
+      <c r="H48" s="157"/>
+      <c r="I48" s="157"/>
+      <c r="J48" s="163"/>
+      <c r="K48" s="155"/>
+      <c r="L48" s="154"/>
+      <c r="M48" s="155"/>
       <c r="N48"/>
     </row>
-    <row r="49" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
-      <c r="E49" s="155"/>
-      <c r="F49" s="158"/>
-      <c r="G49" s="158"/>
-      <c r="H49" s="158"/>
-      <c r="I49" s="158"/>
-      <c r="J49" s="158"/>
-      <c r="K49" s="156"/>
-      <c r="L49" s="155"/>
-      <c r="M49" s="156"/>
+      <c r="E49" s="154"/>
+      <c r="F49" s="157"/>
+      <c r="G49" s="157"/>
+      <c r="H49" s="157"/>
+      <c r="I49" s="157"/>
+      <c r="J49" s="157"/>
+      <c r="K49" s="155"/>
+      <c r="L49" s="154"/>
+      <c r="M49" s="155"/>
       <c r="N49"/>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
-      <c r="E50" s="155" t="s">
-        <v>123</v>
-      </c>
-      <c r="F50" s="158"/>
-      <c r="G50" s="158"/>
-      <c r="H50" s="158"/>
-      <c r="I50" s="158"/>
-      <c r="J50" s="158">
+      <c r="E50" s="154" t="s">
+        <v>121</v>
+      </c>
+      <c r="F50" s="157"/>
+      <c r="G50" s="157"/>
+      <c r="H50" s="157"/>
+      <c r="I50" s="157"/>
+      <c r="J50" s="157">
         <f>77200-77124.2</f>
         <v>75.80000000000291</v>
       </c>
-      <c r="K50" s="156"/>
-      <c r="L50" s="155"/>
-      <c r="M50" s="156"/>
+      <c r="K50" s="155"/>
+      <c r="L50" s="154"/>
+      <c r="M50" s="155"/>
       <c r="N50"/>
     </row>
-    <row r="51" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
-      <c r="E51" s="155"/>
-      <c r="F51" s="158"/>
-      <c r="G51" s="158"/>
-      <c r="H51" s="158"/>
-      <c r="I51" s="158"/>
-      <c r="J51" s="158"/>
-      <c r="K51" s="156"/>
-      <c r="L51" s="166"/>
-      <c r="M51" s="167"/>
+      <c r="E51" s="154"/>
+      <c r="F51" s="157"/>
+      <c r="G51" s="157"/>
+      <c r="H51" s="157"/>
+      <c r="I51" s="157"/>
+      <c r="J51" s="157"/>
+      <c r="K51" s="155"/>
+      <c r="L51" s="165"/>
+      <c r="M51" s="166"/>
       <c r="N51"/>
     </row>
-    <row r="52" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
-      <c r="E52" s="199" t="s">
-        <v>121</v>
-      </c>
-      <c r="F52" s="200"/>
-      <c r="G52" s="200"/>
-      <c r="H52" s="200"/>
-      <c r="I52" s="200"/>
-      <c r="J52" s="201">
+      <c r="E52" s="198" t="s">
+        <v>119</v>
+      </c>
+      <c r="F52" s="199"/>
+      <c r="G52" s="199"/>
+      <c r="H52" s="199"/>
+      <c r="I52" s="199"/>
+      <c r="J52" s="200">
         <f>SUM(J42:J51)</f>
-        <v>38049.484969585297</v>
-      </c>
-      <c r="K52" s="191"/>
-      <c r="L52" s="168"/>
-      <c r="M52" s="169"/>
+        <v>127674.63237452871</v>
+      </c>
+      <c r="K52" s="190"/>
+      <c r="L52" s="167"/>
+      <c r="M52" s="168"/>
       <c r="N52"/>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="N53"/>
     </row>
-    <row r="55" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="56" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E56" s="189" t="s">
+    <row r="55" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="56" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E56" s="188" t="s">
+        <v>111</v>
+      </c>
+      <c r="F56" s="189"/>
+      <c r="G56" s="189"/>
+      <c r="H56" s="189"/>
+      <c r="I56" s="189"/>
+      <c r="J56" s="189"/>
+      <c r="K56" s="190"/>
+      <c r="L56" s="152"/>
+      <c r="M56" s="153"/>
+    </row>
+    <row r="57" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E57" s="191" t="s">
+        <v>112</v>
+      </c>
+      <c r="F57" s="189"/>
+      <c r="G57" s="189"/>
+      <c r="H57" s="189"/>
+      <c r="I57" s="189"/>
+      <c r="J57" s="189"/>
+      <c r="K57" s="190"/>
+      <c r="L57" s="154"/>
+      <c r="M57" s="155"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="E58" s="152"/>
+      <c r="F58" s="156"/>
+      <c r="G58" s="156"/>
+      <c r="H58" s="156"/>
+      <c r="I58" s="157"/>
+      <c r="J58" s="157">
+        <f>J34</f>
+        <v>0</v>
+      </c>
+      <c r="K58" s="155"/>
+      <c r="L58" s="154"/>
+      <c r="M58" s="155"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="E59" s="154" t="s">
         <v>113</v>
       </c>
-      <c r="F56" s="190"/>
-      <c r="G56" s="190"/>
-      <c r="H56" s="190"/>
-      <c r="I56" s="190"/>
-      <c r="J56" s="190"/>
-      <c r="K56" s="191"/>
-      <c r="L56" s="153"/>
-      <c r="M56" s="154"/>
-    </row>
-    <row r="57" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E57" s="192" t="s">
+      <c r="F59" s="157"/>
+      <c r="G59" s="157"/>
+      <c r="H59" s="157"/>
+      <c r="I59" s="157"/>
+      <c r="J59" s="157"/>
+      <c r="K59" s="155"/>
+      <c r="L59" s="154"/>
+      <c r="M59" s="155"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="E60" s="158"/>
+      <c r="F60" s="159"/>
+      <c r="G60" s="159"/>
+      <c r="H60" s="159"/>
+      <c r="I60" s="159"/>
+      <c r="J60" s="159"/>
+      <c r="K60" s="160"/>
+      <c r="L60" s="154"/>
+      <c r="M60" s="155"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="E61" s="192" t="s">
+        <v>49</v>
+      </c>
+      <c r="F61" s="193"/>
+      <c r="G61" s="193"/>
+      <c r="H61" s="193"/>
+      <c r="I61" s="193"/>
+      <c r="J61" s="193"/>
+      <c r="K61" s="194"/>
+      <c r="L61" s="154"/>
+      <c r="M61" s="155"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="E62" s="154"/>
+      <c r="F62" s="157"/>
+      <c r="G62" s="157"/>
+      <c r="H62" s="157"/>
+      <c r="I62" s="157"/>
+      <c r="J62" s="157"/>
+      <c r="K62" s="155"/>
+      <c r="L62" s="154"/>
+      <c r="M62" s="155"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="E63" s="154" t="s">
         <v>114</v>
       </c>
-      <c r="F57" s="190"/>
-      <c r="G57" s="190"/>
-      <c r="H57" s="190"/>
-      <c r="I57" s="190"/>
-      <c r="J57" s="190"/>
-      <c r="K57" s="191"/>
-      <c r="L57" s="155"/>
-      <c r="M57" s="156"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="E58" s="153"/>
-      <c r="F58" s="157"/>
-      <c r="G58" s="157"/>
-      <c r="H58" s="157"/>
-      <c r="I58" s="158"/>
-      <c r="J58" s="158">
-        <f>J34</f>
-        <v>0</v>
-      </c>
-      <c r="K58" s="156"/>
-      <c r="L58" s="155"/>
-      <c r="M58" s="156"/>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="E59" s="155" t="s">
-        <v>115</v>
-      </c>
-      <c r="F59" s="158"/>
-      <c r="G59" s="158"/>
-      <c r="H59" s="158"/>
-      <c r="I59" s="158"/>
-      <c r="J59" s="158"/>
-      <c r="K59" s="156"/>
-      <c r="L59" s="155"/>
-      <c r="M59" s="156"/>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="E60" s="159"/>
-      <c r="F60" s="160"/>
-      <c r="G60" s="160"/>
-      <c r="H60" s="160"/>
-      <c r="I60" s="160"/>
-      <c r="J60" s="160"/>
-      <c r="K60" s="161"/>
-      <c r="L60" s="155"/>
-      <c r="M60" s="156"/>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="E61" s="193" t="s">
-        <v>50</v>
-      </c>
-      <c r="F61" s="194"/>
-      <c r="G61" s="194"/>
-      <c r="H61" s="194"/>
-      <c r="I61" s="194"/>
-      <c r="J61" s="194"/>
-      <c r="K61" s="195"/>
-      <c r="L61" s="155"/>
-      <c r="M61" s="156"/>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="E62" s="155"/>
-      <c r="F62" s="158"/>
-      <c r="G62" s="158"/>
-      <c r="H62" s="158"/>
-      <c r="I62" s="158"/>
-      <c r="J62" s="158"/>
-      <c r="K62" s="156"/>
-      <c r="L62" s="155"/>
-      <c r="M62" s="156"/>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="E63" s="155" t="s">
-        <v>116</v>
-      </c>
-      <c r="F63" s="158"/>
-      <c r="G63" s="163" t="str">
+      <c r="F63" s="157"/>
+      <c r="G63" s="162" t="str">
         <f>C8</f>
         <v>Castelao Lorena</v>
       </c>
-      <c r="H63" s="158"/>
-      <c r="I63" s="158" t="s">
+      <c r="H63" s="157"/>
+      <c r="I63" s="157" t="s">
+        <v>115</v>
+      </c>
+      <c r="J63" s="161">
+        <v>45674</v>
+      </c>
+      <c r="K63" s="155"/>
+      <c r="L63" s="195" t="s">
+        <v>116</v>
+      </c>
+      <c r="M63" s="196"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="E64" s="154" t="s">
         <v>117</v>
       </c>
-      <c r="J63" s="162">
-        <v>45674</v>
-      </c>
-      <c r="K63" s="156"/>
-      <c r="L63" s="196" t="s">
+      <c r="F64" s="162">
+        <v>4</v>
+      </c>
+      <c r="G64" s="157"/>
+      <c r="H64" s="157"/>
+      <c r="I64" s="157"/>
+      <c r="J64" s="157"/>
+      <c r="K64" s="155"/>
+      <c r="L64" s="154"/>
+      <c r="M64" s="155"/>
+    </row>
+    <row r="65" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E65" s="154"/>
+      <c r="F65" s="157"/>
+      <c r="G65" s="157"/>
+      <c r="H65" s="157"/>
+      <c r="I65" s="157"/>
+      <c r="J65" s="157"/>
+      <c r="K65" s="155"/>
+      <c r="L65" s="197"/>
+      <c r="M65" s="196"/>
+    </row>
+    <row r="66" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E66" s="154" t="s">
+        <v>48</v>
+      </c>
+      <c r="F66" s="157"/>
+      <c r="G66" s="157"/>
+      <c r="H66" s="157"/>
+      <c r="I66" s="157"/>
+      <c r="J66" s="163">
+        <f>J8</f>
+        <v>64618.817800000004</v>
+      </c>
+      <c r="K66" s="155"/>
+      <c r="L66" s="154"/>
+      <c r="M66" s="155"/>
+    </row>
+    <row r="67" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E67" s="164" t="s">
         <v>118</v>
       </c>
-      <c r="M63" s="197"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="E64" s="155" t="s">
+      <c r="F67" s="157"/>
+      <c r="G67" s="157"/>
+      <c r="H67" s="157"/>
+      <c r="I67" s="157"/>
+      <c r="J67" s="163">
+        <f>K8</f>
+        <v>39778.317725000001</v>
+      </c>
+      <c r="K67" s="155"/>
+      <c r="L67" s="154"/>
+      <c r="M67" s="155"/>
+    </row>
+    <row r="68" spans="5:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E68" s="164" t="s">
+        <v>120</v>
+      </c>
+      <c r="F68" s="157"/>
+      <c r="G68" s="157"/>
+      <c r="H68" s="157"/>
+      <c r="I68" s="157"/>
+      <c r="J68" s="163">
+        <f>G29+H29</f>
+        <v>0</v>
+      </c>
+      <c r="K68" s="155"/>
+      <c r="L68" s="154"/>
+      <c r="M68" s="155"/>
+    </row>
+    <row r="69" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E69" s="164"/>
+      <c r="F69" s="157"/>
+      <c r="G69" s="157"/>
+      <c r="H69" s="157"/>
+      <c r="I69" s="157"/>
+      <c r="J69" s="163"/>
+      <c r="K69" s="155"/>
+      <c r="L69" s="154"/>
+      <c r="M69" s="155"/>
+    </row>
+    <row r="70" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E70" s="164"/>
+      <c r="F70" s="157"/>
+      <c r="G70" s="157"/>
+      <c r="H70" s="157"/>
+      <c r="I70" s="157"/>
+      <c r="J70" s="163"/>
+      <c r="K70" s="155"/>
+      <c r="L70" s="154"/>
+      <c r="M70" s="155"/>
+    </row>
+    <row r="71" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F71" s="157"/>
+      <c r="G71" s="157"/>
+      <c r="H71" s="157"/>
+      <c r="I71" s="157"/>
+      <c r="J71" s="163"/>
+      <c r="K71" s="155"/>
+      <c r="L71" s="154"/>
+      <c r="M71" s="155"/>
+    </row>
+    <row r="72" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E72" s="164"/>
+      <c r="F72" s="157"/>
+      <c r="G72" s="157"/>
+      <c r="H72" s="157"/>
+      <c r="I72" s="157"/>
+      <c r="J72" s="163"/>
+      <c r="K72" s="155"/>
+      <c r="L72" s="154"/>
+      <c r="M72" s="155"/>
+    </row>
+    <row r="73" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E73" s="154"/>
+      <c r="F73" s="157"/>
+      <c r="G73" s="157"/>
+      <c r="H73" s="157"/>
+      <c r="I73" s="157"/>
+      <c r="J73" s="157"/>
+      <c r="K73" s="155"/>
+      <c r="L73" s="154"/>
+      <c r="M73" s="155"/>
+    </row>
+    <row r="74" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E74" s="154"/>
+      <c r="F74" s="157"/>
+      <c r="G74" s="157"/>
+      <c r="H74" s="157"/>
+      <c r="I74" s="157"/>
+      <c r="J74" s="157"/>
+      <c r="K74" s="155"/>
+      <c r="L74" s="154"/>
+      <c r="M74" s="155"/>
+    </row>
+    <row r="75" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E75" s="154"/>
+      <c r="F75" s="157"/>
+      <c r="G75" s="157"/>
+      <c r="H75" s="157"/>
+      <c r="I75" s="157"/>
+      <c r="J75" s="157"/>
+      <c r="K75" s="155"/>
+      <c r="L75" s="165"/>
+      <c r="M75" s="166"/>
+    </row>
+    <row r="76" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E76" s="198" t="s">
         <v>119</v>
       </c>
-      <c r="F64" s="163">
-        <v>4</v>
-      </c>
-      <c r="G64" s="158"/>
-      <c r="H64" s="158"/>
-      <c r="I64" s="158"/>
-      <c r="J64" s="158"/>
-      <c r="K64" s="156"/>
-      <c r="L64" s="155"/>
-      <c r="M64" s="156"/>
-    </row>
-    <row r="65" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E65" s="155"/>
-      <c r="F65" s="158"/>
-      <c r="G65" s="158"/>
-      <c r="H65" s="158"/>
-      <c r="I65" s="158"/>
-      <c r="J65" s="158"/>
-      <c r="K65" s="156"/>
-      <c r="L65" s="198"/>
-      <c r="M65" s="197"/>
-    </row>
-    <row r="66" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E66" s="155" t="s">
+      <c r="F76" s="199"/>
+      <c r="G76" s="199"/>
+      <c r="H76" s="199"/>
+      <c r="I76" s="199"/>
+      <c r="J76" s="200">
+        <f>SUM(J66:J75)</f>
+        <v>104397.13552500001</v>
+      </c>
+      <c r="K76" s="190"/>
+      <c r="L76" s="167"/>
+      <c r="M76" s="168"/>
+    </row>
+    <row r="82" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="83" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E83" s="188" t="s">
+        <v>111</v>
+      </c>
+      <c r="F83" s="189"/>
+      <c r="G83" s="189"/>
+      <c r="H83" s="189"/>
+      <c r="I83" s="189"/>
+      <c r="J83" s="189"/>
+      <c r="K83" s="190"/>
+      <c r="L83" s="152"/>
+      <c r="M83" s="153"/>
+    </row>
+    <row r="84" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E84" s="191" t="s">
+        <v>112</v>
+      </c>
+      <c r="F84" s="189"/>
+      <c r="G84" s="189"/>
+      <c r="H84" s="189"/>
+      <c r="I84" s="189"/>
+      <c r="J84" s="189"/>
+      <c r="K84" s="190"/>
+      <c r="L84" s="154"/>
+      <c r="M84" s="155"/>
+    </row>
+    <row r="85" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E85" s="152"/>
+      <c r="F85" s="156"/>
+      <c r="G85" s="156"/>
+      <c r="H85" s="156"/>
+      <c r="I85" s="157"/>
+      <c r="J85" s="157">
+        <f>'detalle y gastos'!B7</f>
+        <v>0</v>
+      </c>
+      <c r="K85" s="155"/>
+      <c r="L85" s="154"/>
+      <c r="M85" s="155"/>
+    </row>
+    <row r="86" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E86" s="154" t="s">
+        <v>113</v>
+      </c>
+      <c r="F86" s="157"/>
+      <c r="G86" s="157"/>
+      <c r="H86" s="157"/>
+      <c r="I86" s="157"/>
+      <c r="J86" s="157"/>
+      <c r="K86" s="155"/>
+      <c r="L86" s="154"/>
+      <c r="M86" s="155"/>
+    </row>
+    <row r="87" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E87" s="158"/>
+      <c r="F87" s="159"/>
+      <c r="G87" s="159"/>
+      <c r="H87" s="159"/>
+      <c r="I87" s="159"/>
+      <c r="J87" s="159"/>
+      <c r="K87" s="160"/>
+      <c r="L87" s="154"/>
+      <c r="M87" s="155"/>
+    </row>
+    <row r="88" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E88" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="F66" s="158"/>
-      <c r="G66" s="158"/>
-      <c r="H66" s="158"/>
-      <c r="I66" s="158"/>
-      <c r="J66" s="164">
-        <f>J8</f>
-        <v>42975.583775000006</v>
-      </c>
-      <c r="K66" s="156"/>
-      <c r="L66" s="155"/>
-      <c r="M66" s="156"/>
-    </row>
-    <row r="67" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E67" s="165" t="s">
-        <v>120</v>
-      </c>
-      <c r="F67" s="158"/>
-      <c r="G67" s="158"/>
-      <c r="H67" s="158"/>
-      <c r="I67" s="158"/>
-      <c r="J67" s="164">
-        <f>K8</f>
-        <v>1842.432642140468</v>
-      </c>
-      <c r="K67" s="156"/>
-      <c r="L67" s="155"/>
-      <c r="M67" s="156"/>
-    </row>
-    <row r="68" spans="5:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E68" s="165" t="s">
-        <v>122</v>
-      </c>
-      <c r="F68" s="158"/>
-      <c r="G68" s="158"/>
-      <c r="H68" s="158"/>
-      <c r="I68" s="158"/>
-      <c r="J68" s="164">
-        <f>G29+H29</f>
-        <v>0</v>
-      </c>
-      <c r="K68" s="156"/>
-      <c r="L68" s="155"/>
-      <c r="M68" s="156"/>
-    </row>
-    <row r="69" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="E69" s="165"/>
-      <c r="F69" s="158"/>
-      <c r="G69" s="158"/>
-      <c r="H69" s="158"/>
-      <c r="I69" s="158"/>
-      <c r="J69" s="164"/>
-      <c r="K69" s="156"/>
-      <c r="L69" s="155"/>
-      <c r="M69" s="156"/>
-    </row>
-    <row r="70" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="E70" s="165"/>
-      <c r="F70" s="158"/>
-      <c r="G70" s="158"/>
-      <c r="H70" s="158"/>
-      <c r="I70" s="158"/>
-      <c r="J70" s="164"/>
-      <c r="K70" s="156"/>
-      <c r="L70" s="155"/>
-      <c r="M70" s="156"/>
-    </row>
-    <row r="71" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="F71" s="158"/>
-      <c r="G71" s="158"/>
-      <c r="H71" s="158"/>
-      <c r="I71" s="158"/>
-      <c r="J71" s="164"/>
-      <c r="K71" s="156"/>
-      <c r="L71" s="155"/>
-      <c r="M71" s="156"/>
-    </row>
-    <row r="72" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="E72" s="165"/>
-      <c r="F72" s="158"/>
-      <c r="G72" s="158"/>
-      <c r="H72" s="158"/>
-      <c r="I72" s="158"/>
-      <c r="J72" s="164"/>
-      <c r="K72" s="156"/>
-      <c r="L72" s="155"/>
-      <c r="M72" s="156"/>
-    </row>
-    <row r="73" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="E73" s="155"/>
-      <c r="F73" s="158"/>
-      <c r="G73" s="158"/>
-      <c r="H73" s="158"/>
-      <c r="I73" s="158"/>
-      <c r="J73" s="158"/>
-      <c r="K73" s="156"/>
-      <c r="L73" s="155"/>
-      <c r="M73" s="156"/>
-    </row>
-    <row r="74" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="E74" s="155"/>
-      <c r="F74" s="158"/>
-      <c r="G74" s="158"/>
-      <c r="H74" s="158"/>
-      <c r="I74" s="158"/>
-      <c r="J74" s="158"/>
-      <c r="K74" s="156"/>
-      <c r="L74" s="155"/>
-      <c r="M74" s="156"/>
-    </row>
-    <row r="75" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E75" s="155"/>
-      <c r="F75" s="158"/>
-      <c r="G75" s="158"/>
-      <c r="H75" s="158"/>
-      <c r="I75" s="158"/>
-      <c r="J75" s="158"/>
-      <c r="K75" s="156"/>
-      <c r="L75" s="166"/>
-      <c r="M75" s="167"/>
-    </row>
-    <row r="76" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E76" s="199" t="s">
-        <v>121</v>
-      </c>
-      <c r="F76" s="200"/>
-      <c r="G76" s="200"/>
-      <c r="H76" s="200"/>
-      <c r="I76" s="200"/>
-      <c r="J76" s="201">
-        <f>SUM(J66:J75)</f>
-        <v>44818.016417140476</v>
-      </c>
-      <c r="K76" s="191"/>
-      <c r="L76" s="168"/>
-      <c r="M76" s="169"/>
-    </row>
-    <row r="82" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="83" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E83" s="189" t="s">
-        <v>113</v>
-      </c>
-      <c r="F83" s="190"/>
-      <c r="G83" s="190"/>
-      <c r="H83" s="190"/>
-      <c r="I83" s="190"/>
-      <c r="J83" s="190"/>
-      <c r="K83" s="191"/>
-      <c r="L83" s="153"/>
-      <c r="M83" s="154"/>
-    </row>
-    <row r="84" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E84" s="192" t="s">
+      <c r="F88" s="193"/>
+      <c r="G88" s="193"/>
+      <c r="H88" s="193"/>
+      <c r="I88" s="193"/>
+      <c r="J88" s="193"/>
+      <c r="K88" s="194"/>
+      <c r="L88" s="154"/>
+      <c r="M88" s="155"/>
+    </row>
+    <row r="89" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E89" s="154"/>
+      <c r="F89" s="157"/>
+      <c r="G89" s="157"/>
+      <c r="H89" s="157"/>
+      <c r="I89" s="157"/>
+      <c r="J89" s="157"/>
+      <c r="K89" s="155"/>
+      <c r="L89" s="154"/>
+      <c r="M89" s="155"/>
+    </row>
+    <row r="90" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E90" s="154" t="s">
         <v>114</v>
       </c>
-      <c r="F84" s="190"/>
-      <c r="G84" s="190"/>
-      <c r="H84" s="190"/>
-      <c r="I84" s="190"/>
-      <c r="J84" s="190"/>
-      <c r="K84" s="191"/>
-      <c r="L84" s="155"/>
-      <c r="M84" s="156"/>
-    </row>
-    <row r="85" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E85" s="153"/>
-      <c r="F85" s="157"/>
-      <c r="G85" s="157"/>
-      <c r="H85" s="157"/>
-      <c r="I85" s="158"/>
-      <c r="J85" s="158">
-        <f>'detalle y gastos'!B7</f>
-        <v>0</v>
-      </c>
-      <c r="K85" s="156"/>
-      <c r="L85" s="155"/>
-      <c r="M85" s="156"/>
-    </row>
-    <row r="86" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E86" s="155" t="s">
-        <v>115</v>
-      </c>
-      <c r="F86" s="158"/>
-      <c r="G86" s="158"/>
-      <c r="H86" s="158"/>
-      <c r="I86" s="158"/>
-      <c r="J86" s="158"/>
-      <c r="K86" s="156"/>
-      <c r="L86" s="155"/>
-      <c r="M86" s="156"/>
-    </row>
-    <row r="87" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E87" s="159"/>
-      <c r="F87" s="160"/>
-      <c r="G87" s="160"/>
-      <c r="H87" s="160"/>
-      <c r="I87" s="160"/>
-      <c r="J87" s="160"/>
-      <c r="K87" s="161"/>
-      <c r="L87" s="155"/>
-      <c r="M87" s="156"/>
-    </row>
-    <row r="88" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E88" s="193" t="s">
-        <v>50</v>
-      </c>
-      <c r="F88" s="194"/>
-      <c r="G88" s="194"/>
-      <c r="H88" s="194"/>
-      <c r="I88" s="194"/>
-      <c r="J88" s="194"/>
-      <c r="K88" s="195"/>
-      <c r="L88" s="155"/>
-      <c r="M88" s="156"/>
-    </row>
-    <row r="89" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E89" s="155"/>
-      <c r="F89" s="158"/>
-      <c r="G89" s="158"/>
-      <c r="H89" s="158"/>
-      <c r="I89" s="158"/>
-      <c r="J89" s="158"/>
-      <c r="K89" s="156"/>
-      <c r="L89" s="155"/>
-      <c r="M89" s="156"/>
-    </row>
-    <row r="90" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E90" s="155" t="s">
-        <v>116</v>
-      </c>
-      <c r="F90" s="158"/>
-      <c r="G90" s="163" t="str">
+      <c r="F90" s="157"/>
+      <c r="G90" s="162" t="str">
         <f>C10</f>
         <v>Valdez Norberto</v>
       </c>
-      <c r="H90" s="158"/>
-      <c r="I90" s="158" t="s">
+      <c r="H90" s="157"/>
+      <c r="I90" s="157" t="s">
+        <v>115</v>
+      </c>
+      <c r="J90" s="161">
+        <v>45674</v>
+      </c>
+      <c r="K90" s="155"/>
+      <c r="L90" s="195" t="s">
+        <v>116</v>
+      </c>
+      <c r="M90" s="196"/>
+    </row>
+    <row r="91" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E91" s="154" t="s">
         <v>117</v>
       </c>
-      <c r="J90" s="162">
-        <v>45674</v>
-      </c>
-      <c r="K90" s="156"/>
-      <c r="L90" s="196" t="s">
+      <c r="F91" s="162">
+        <v>6</v>
+      </c>
+      <c r="G91" s="157"/>
+      <c r="H91" s="157"/>
+      <c r="I91" s="157"/>
+      <c r="J91" s="157"/>
+      <c r="K91" s="155"/>
+      <c r="L91" s="154"/>
+      <c r="M91" s="155"/>
+    </row>
+    <row r="92" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E92" s="154"/>
+      <c r="F92" s="157"/>
+      <c r="G92" s="157"/>
+      <c r="H92" s="157"/>
+      <c r="I92" s="157"/>
+      <c r="J92" s="157"/>
+      <c r="K92" s="155"/>
+      <c r="L92" s="197"/>
+      <c r="M92" s="196"/>
+    </row>
+    <row r="93" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E93" s="154" t="s">
+        <v>48</v>
+      </c>
+      <c r="F93" s="157"/>
+      <c r="G93" s="157"/>
+      <c r="H93" s="157"/>
+      <c r="I93" s="157"/>
+      <c r="J93" s="163">
+        <f>J10</f>
+        <v>54674.091264000002</v>
+      </c>
+      <c r="K93" s="155"/>
+      <c r="L93" s="154"/>
+      <c r="M93" s="155"/>
+    </row>
+    <row r="94" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E94" s="164" t="s">
         <v>118</v>
       </c>
-      <c r="M90" s="197"/>
-    </row>
-    <row r="91" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E91" s="155" t="s">
+      <c r="F94" s="157"/>
+      <c r="G94" s="157"/>
+      <c r="H94" s="157"/>
+      <c r="I94" s="157"/>
+      <c r="J94" s="163">
+        <f>K10</f>
+        <v>33656.502048000002</v>
+      </c>
+      <c r="K94" s="155"/>
+      <c r="L94" s="154"/>
+      <c r="M94" s="155"/>
+    </row>
+    <row r="95" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E95" s="164" t="s">
+        <v>121</v>
+      </c>
+      <c r="F95" s="157"/>
+      <c r="G95" s="157"/>
+      <c r="H95" s="157"/>
+      <c r="I95" s="157"/>
+      <c r="J95" s="163">
+        <v>23.89</v>
+      </c>
+      <c r="K95" s="155"/>
+      <c r="L95" s="154"/>
+      <c r="M95" s="155"/>
+    </row>
+    <row r="96" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E96" s="164"/>
+      <c r="F96" s="157"/>
+      <c r="G96" s="157"/>
+      <c r="H96" s="157"/>
+      <c r="I96" s="157"/>
+      <c r="J96" s="163"/>
+      <c r="K96" s="155"/>
+      <c r="L96" s="154"/>
+      <c r="M96" s="155"/>
+    </row>
+    <row r="97" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E97" s="164"/>
+      <c r="F97" s="157"/>
+      <c r="G97" s="157"/>
+      <c r="H97" s="157"/>
+      <c r="I97" s="157"/>
+      <c r="J97" s="163"/>
+      <c r="K97" s="155"/>
+      <c r="L97" s="154"/>
+      <c r="M97" s="155"/>
+    </row>
+    <row r="98" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F98" s="157"/>
+      <c r="G98" s="157"/>
+      <c r="H98" s="157"/>
+      <c r="I98" s="157"/>
+      <c r="J98" s="163"/>
+      <c r="K98" s="155"/>
+      <c r="L98" s="154"/>
+      <c r="M98" s="155"/>
+    </row>
+    <row r="99" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E99" s="164"/>
+      <c r="F99" s="157"/>
+      <c r="G99" s="157"/>
+      <c r="H99" s="157"/>
+      <c r="I99" s="157"/>
+      <c r="J99" s="163"/>
+      <c r="K99" s="155"/>
+      <c r="L99" s="154"/>
+      <c r="M99" s="155"/>
+    </row>
+    <row r="100" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E100" s="154"/>
+      <c r="F100" s="157"/>
+      <c r="G100" s="157"/>
+      <c r="H100" s="157"/>
+      <c r="I100" s="157"/>
+      <c r="J100" s="157"/>
+      <c r="K100" s="155"/>
+      <c r="L100" s="154"/>
+      <c r="M100" s="155"/>
+    </row>
+    <row r="101" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E101" s="154"/>
+      <c r="F101" s="157"/>
+      <c r="G101" s="157"/>
+      <c r="H101" s="157"/>
+      <c r="I101" s="157"/>
+      <c r="J101" s="157"/>
+      <c r="K101" s="155"/>
+      <c r="L101" s="154"/>
+      <c r="M101" s="155"/>
+    </row>
+    <row r="102" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E102" s="154"/>
+      <c r="F102" s="157"/>
+      <c r="G102" s="157"/>
+      <c r="H102" s="157"/>
+      <c r="I102" s="157"/>
+      <c r="J102" s="157"/>
+      <c r="K102" s="155"/>
+      <c r="L102" s="165"/>
+      <c r="M102" s="166"/>
+    </row>
+    <row r="103" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E103" s="198" t="s">
         <v>119</v>
       </c>
-      <c r="F91" s="163">
-        <v>6</v>
-      </c>
-      <c r="G91" s="158"/>
-      <c r="H91" s="158"/>
-      <c r="I91" s="158"/>
-      <c r="J91" s="158"/>
-      <c r="K91" s="156"/>
-      <c r="L91" s="155"/>
-      <c r="M91" s="156"/>
-    </row>
-    <row r="92" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E92" s="155"/>
-      <c r="F92" s="158"/>
-      <c r="G92" s="158"/>
-      <c r="H92" s="158"/>
-      <c r="I92" s="158"/>
-      <c r="J92" s="158"/>
-      <c r="K92" s="156"/>
-      <c r="L92" s="198"/>
-      <c r="M92" s="197"/>
-    </row>
-    <row r="93" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E93" s="155" t="s">
+      <c r="F103" s="199"/>
+      <c r="G103" s="199"/>
+      <c r="H103" s="199"/>
+      <c r="I103" s="199"/>
+      <c r="J103" s="200">
+        <f>SUM(J93:J102)</f>
+        <v>88354.483312000011</v>
+      </c>
+      <c r="K103" s="190"/>
+      <c r="L103" s="167"/>
+      <c r="M103" s="168"/>
+    </row>
+    <row r="107" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="108" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E108" s="188" t="s">
+        <v>111</v>
+      </c>
+      <c r="F108" s="189"/>
+      <c r="G108" s="189"/>
+      <c r="H108" s="189"/>
+      <c r="I108" s="189"/>
+      <c r="J108" s="189"/>
+      <c r="K108" s="190"/>
+      <c r="L108" s="152"/>
+      <c r="M108" s="153"/>
+    </row>
+    <row r="109" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E109" s="191" t="s">
+        <v>112</v>
+      </c>
+      <c r="F109" s="189"/>
+      <c r="G109" s="189"/>
+      <c r="H109" s="189"/>
+      <c r="I109" s="189"/>
+      <c r="J109" s="189"/>
+      <c r="K109" s="190"/>
+      <c r="L109" s="154"/>
+      <c r="M109" s="155"/>
+    </row>
+    <row r="110" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E110" s="152"/>
+      <c r="F110" s="156"/>
+      <c r="G110" s="156"/>
+      <c r="H110" s="156"/>
+      <c r="I110" s="157"/>
+      <c r="J110" s="157">
+        <f>'detalle y gastos'!B7</f>
+        <v>0</v>
+      </c>
+      <c r="K110" s="155"/>
+      <c r="L110" s="154"/>
+      <c r="M110" s="155"/>
+    </row>
+    <row r="111" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E111" s="154" t="s">
+        <v>113</v>
+      </c>
+      <c r="F111" s="157"/>
+      <c r="G111" s="157"/>
+      <c r="H111" s="157"/>
+      <c r="I111" s="157"/>
+      <c r="J111" s="157"/>
+      <c r="K111" s="155"/>
+      <c r="L111" s="154"/>
+      <c r="M111" s="155"/>
+    </row>
+    <row r="112" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E112" s="158"/>
+      <c r="F112" s="159"/>
+      <c r="G112" s="159"/>
+      <c r="H112" s="159"/>
+      <c r="I112" s="159"/>
+      <c r="J112" s="159"/>
+      <c r="K112" s="160"/>
+      <c r="L112" s="154"/>
+      <c r="M112" s="155"/>
+    </row>
+    <row r="113" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E113" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="F93" s="158"/>
-      <c r="G93" s="158"/>
-      <c r="H93" s="158"/>
-      <c r="I93" s="158"/>
-      <c r="J93" s="164">
-        <f>J10</f>
-        <v>36361.714272000005</v>
-      </c>
-      <c r="K93" s="156"/>
-      <c r="L93" s="155"/>
-      <c r="M93" s="156"/>
-    </row>
-    <row r="94" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E94" s="165" t="s">
-        <v>120</v>
-      </c>
-      <c r="F94" s="158"/>
-      <c r="G94" s="158"/>
-      <c r="H94" s="158"/>
-      <c r="I94" s="158"/>
-      <c r="J94" s="164">
-        <f>K10</f>
-        <v>1050.358795986622</v>
-      </c>
-      <c r="K94" s="156"/>
-      <c r="L94" s="155"/>
-      <c r="M94" s="156"/>
-    </row>
-    <row r="95" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E95" s="165" t="s">
-        <v>123</v>
-      </c>
-      <c r="F95" s="158"/>
-      <c r="G95" s="158"/>
-      <c r="H95" s="158"/>
-      <c r="I95" s="158"/>
-      <c r="J95" s="164">
-        <v>23.89</v>
-      </c>
-      <c r="K95" s="156"/>
-      <c r="L95" s="155"/>
-      <c r="M95" s="156"/>
-    </row>
-    <row r="96" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E96" s="165"/>
-      <c r="F96" s="158"/>
-      <c r="G96" s="158"/>
-      <c r="H96" s="158"/>
-      <c r="I96" s="158"/>
-      <c r="J96" s="164"/>
-      <c r="K96" s="156"/>
-      <c r="L96" s="155"/>
-      <c r="M96" s="156"/>
-    </row>
-    <row r="97" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E97" s="165"/>
-      <c r="F97" s="158"/>
-      <c r="G97" s="158"/>
-      <c r="H97" s="158"/>
-      <c r="I97" s="158"/>
-      <c r="J97" s="164"/>
-      <c r="K97" s="156"/>
-      <c r="L97" s="155"/>
-      <c r="M97" s="156"/>
-    </row>
-    <row r="98" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="F98" s="158"/>
-      <c r="G98" s="158"/>
-      <c r="H98" s="158"/>
-      <c r="I98" s="158"/>
-      <c r="J98" s="164"/>
-      <c r="K98" s="156"/>
-      <c r="L98" s="155"/>
-      <c r="M98" s="156"/>
-    </row>
-    <row r="99" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E99" s="165"/>
-      <c r="F99" s="158"/>
-      <c r="G99" s="158"/>
-      <c r="H99" s="158"/>
-      <c r="I99" s="158"/>
-      <c r="J99" s="164"/>
-      <c r="K99" s="156"/>
-      <c r="L99" s="155"/>
-      <c r="M99" s="156"/>
-    </row>
-    <row r="100" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E100" s="155"/>
-      <c r="F100" s="158"/>
-      <c r="G100" s="158"/>
-      <c r="H100" s="158"/>
-      <c r="I100" s="158"/>
-      <c r="J100" s="158"/>
-      <c r="K100" s="156"/>
-      <c r="L100" s="155"/>
-      <c r="M100" s="156"/>
-    </row>
-    <row r="101" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E101" s="155"/>
-      <c r="F101" s="158"/>
-      <c r="G101" s="158"/>
-      <c r="H101" s="158"/>
-      <c r="I101" s="158"/>
-      <c r="J101" s="158"/>
-      <c r="K101" s="156"/>
-      <c r="L101" s="155"/>
-      <c r="M101" s="156"/>
-    </row>
-    <row r="102" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E102" s="155"/>
-      <c r="F102" s="158"/>
-      <c r="G102" s="158"/>
-      <c r="H102" s="158"/>
-      <c r="I102" s="158"/>
-      <c r="J102" s="158"/>
-      <c r="K102" s="156"/>
-      <c r="L102" s="166"/>
-      <c r="M102" s="167"/>
-    </row>
-    <row r="103" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E103" s="199" t="s">
-        <v>121</v>
-      </c>
-      <c r="F103" s="200"/>
-      <c r="G103" s="200"/>
-      <c r="H103" s="200"/>
-      <c r="I103" s="200"/>
-      <c r="J103" s="201">
-        <f>SUM(J93:J102)</f>
-        <v>37435.963067986624</v>
-      </c>
-      <c r="K103" s="191"/>
-      <c r="L103" s="168"/>
-      <c r="M103" s="169"/>
-    </row>
-    <row r="107" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="108" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E108" s="189" t="s">
-        <v>113</v>
-      </c>
-      <c r="F108" s="190"/>
-      <c r="G108" s="190"/>
-      <c r="H108" s="190"/>
-      <c r="I108" s="190"/>
-      <c r="J108" s="190"/>
-      <c r="K108" s="191"/>
-      <c r="L108" s="153"/>
-      <c r="M108" s="154"/>
-    </row>
-    <row r="109" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E109" s="192" t="s">
+      <c r="F113" s="193"/>
+      <c r="G113" s="193"/>
+      <c r="H113" s="193"/>
+      <c r="I113" s="193"/>
+      <c r="J113" s="193"/>
+      <c r="K113" s="194"/>
+      <c r="L113" s="154"/>
+      <c r="M113" s="155"/>
+    </row>
+    <row r="114" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E114" s="154"/>
+      <c r="F114" s="157"/>
+      <c r="G114" s="157"/>
+      <c r="H114" s="157"/>
+      <c r="I114" s="157"/>
+      <c r="J114" s="157"/>
+      <c r="K114" s="155"/>
+      <c r="L114" s="154"/>
+      <c r="M114" s="155"/>
+    </row>
+    <row r="115" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E115" s="154" t="s">
         <v>114</v>
       </c>
-      <c r="F109" s="190"/>
-      <c r="G109" s="190"/>
-      <c r="H109" s="190"/>
-      <c r="I109" s="190"/>
-      <c r="J109" s="190"/>
-      <c r="K109" s="191"/>
-      <c r="L109" s="155"/>
-      <c r="M109" s="156"/>
-    </row>
-    <row r="110" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E110" s="153"/>
-      <c r="F110" s="157"/>
-      <c r="G110" s="157"/>
-      <c r="H110" s="157"/>
-      <c r="I110" s="158"/>
-      <c r="J110" s="158">
-        <f>'detalle y gastos'!B7</f>
-        <v>0</v>
-      </c>
-      <c r="K110" s="156"/>
-      <c r="L110" s="155"/>
-      <c r="M110" s="156"/>
-    </row>
-    <row r="111" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E111" s="155" t="s">
-        <v>115</v>
-      </c>
-      <c r="F111" s="158"/>
-      <c r="G111" s="158"/>
-      <c r="H111" s="158"/>
-      <c r="I111" s="158"/>
-      <c r="J111" s="158"/>
-      <c r="K111" s="156"/>
-      <c r="L111" s="155"/>
-      <c r="M111" s="156"/>
-    </row>
-    <row r="112" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E112" s="159"/>
-      <c r="F112" s="160"/>
-      <c r="G112" s="160"/>
-      <c r="H112" s="160"/>
-      <c r="I112" s="160"/>
-      <c r="J112" s="160"/>
-      <c r="K112" s="161"/>
-      <c r="L112" s="155"/>
-      <c r="M112" s="156"/>
-    </row>
-    <row r="113" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E113" s="193" t="s">
-        <v>50</v>
-      </c>
-      <c r="F113" s="194"/>
-      <c r="G113" s="194"/>
-      <c r="H113" s="194"/>
-      <c r="I113" s="194"/>
-      <c r="J113" s="194"/>
-      <c r="K113" s="195"/>
-      <c r="L113" s="155"/>
-      <c r="M113" s="156"/>
-    </row>
-    <row r="114" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E114" s="155"/>
-      <c r="F114" s="158"/>
-      <c r="G114" s="158"/>
-      <c r="H114" s="158"/>
-      <c r="I114" s="158"/>
-      <c r="J114" s="158"/>
-      <c r="K114" s="156"/>
-      <c r="L114" s="155"/>
-      <c r="M114" s="156"/>
-    </row>
-    <row r="115" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E115" s="155" t="s">
-        <v>116</v>
-      </c>
-      <c r="F115" s="158"/>
-      <c r="G115" s="163" t="str">
+      <c r="F115" s="157"/>
+      <c r="G115" s="162" t="str">
         <f>C5</f>
         <v>Gomez Elizabeth</v>
       </c>
-      <c r="H115" s="158"/>
-      <c r="I115" s="158" t="s">
+      <c r="H115" s="157"/>
+      <c r="I115" s="157" t="s">
+        <v>115</v>
+      </c>
+      <c r="J115" s="161">
+        <v>45674</v>
+      </c>
+      <c r="K115" s="155"/>
+      <c r="L115" s="195" t="s">
+        <v>116</v>
+      </c>
+      <c r="M115" s="196"/>
+    </row>
+    <row r="116" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E116" s="154" t="s">
         <v>117</v>
       </c>
-      <c r="J115" s="162">
-        <v>45674</v>
-      </c>
-      <c r="K115" s="156"/>
-      <c r="L115" s="196" t="s">
+      <c r="F116" s="162">
+        <v>1</v>
+      </c>
+      <c r="G116" s="157"/>
+      <c r="H116" s="157"/>
+      <c r="I116" s="157"/>
+      <c r="J116" s="157"/>
+      <c r="K116" s="155"/>
+      <c r="L116" s="154"/>
+      <c r="M116" s="155"/>
+    </row>
+    <row r="117" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E117" s="154"/>
+      <c r="F117" s="157"/>
+      <c r="G117" s="157"/>
+      <c r="H117" s="157"/>
+      <c r="I117" s="157"/>
+      <c r="J117" s="157"/>
+      <c r="K117" s="155"/>
+      <c r="L117" s="197"/>
+      <c r="M117" s="196"/>
+    </row>
+    <row r="118" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E118" s="154" t="s">
+        <v>48</v>
+      </c>
+      <c r="F118" s="157"/>
+      <c r="G118" s="157"/>
+      <c r="H118" s="157"/>
+      <c r="I118" s="157"/>
+      <c r="J118" s="163">
+        <f>J5</f>
+        <v>60456.927839999997</v>
+      </c>
+      <c r="K118" s="155"/>
+      <c r="L118" s="154"/>
+      <c r="M118" s="155"/>
+    </row>
+    <row r="119" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E119" s="164" t="s">
         <v>118</v>
       </c>
-      <c r="M115" s="197"/>
-    </row>
-    <row r="116" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E116" s="155" t="s">
-        <v>119</v>
-      </c>
-      <c r="F116" s="163">
-        <v>1</v>
-      </c>
-      <c r="G116" s="158"/>
-      <c r="H116" s="158"/>
-      <c r="I116" s="158"/>
-      <c r="J116" s="158"/>
-      <c r="K116" s="156"/>
-      <c r="L116" s="155"/>
-      <c r="M116" s="156"/>
-    </row>
-    <row r="117" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E117" s="155"/>
-      <c r="F117" s="158"/>
-      <c r="G117" s="158"/>
-      <c r="H117" s="158"/>
-      <c r="I117" s="158"/>
-      <c r="J117" s="158"/>
-      <c r="K117" s="156"/>
-      <c r="L117" s="198"/>
-      <c r="M117" s="197"/>
-    </row>
-    <row r="118" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E118" s="155" t="s">
-        <v>49</v>
-      </c>
-      <c r="F118" s="158"/>
-      <c r="G118" s="158"/>
-      <c r="H118" s="158"/>
-      <c r="I118" s="158"/>
-      <c r="J118" s="164">
-        <f>J5</f>
-        <v>40207.664820000005</v>
-      </c>
-      <c r="K118" s="156"/>
-      <c r="L118" s="155"/>
-      <c r="M118" s="156"/>
-    </row>
-    <row r="119" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E119" s="165" t="s">
-        <v>120</v>
-      </c>
-      <c r="F119" s="158"/>
-      <c r="G119" s="158"/>
-      <c r="H119" s="158"/>
-      <c r="I119" s="158"/>
-      <c r="J119" s="164">
+      <c r="F119" s="157"/>
+      <c r="G119" s="157"/>
+      <c r="H119" s="157"/>
+      <c r="I119" s="157"/>
+      <c r="J119" s="163">
         <f>K5</f>
-        <v>1411.9577257525084</v>
-      </c>
-      <c r="K119" s="156"/>
-      <c r="L119" s="155"/>
-      <c r="M119" s="156"/>
-    </row>
-    <row r="120" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E120" s="165" t="s">
-        <v>124</v>
-      </c>
-      <c r="F120" s="158"/>
-      <c r="G120" s="158"/>
-      <c r="H120" s="158"/>
-      <c r="I120" s="158"/>
-      <c r="J120" s="164">
+        <v>37216.324380000005</v>
+      </c>
+      <c r="K119" s="155"/>
+      <c r="L119" s="154"/>
+      <c r="M119" s="155"/>
+    </row>
+    <row r="120" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E120" s="164" t="s">
+        <v>122</v>
+      </c>
+      <c r="F120" s="157"/>
+      <c r="G120" s="157"/>
+      <c r="H120" s="157"/>
+      <c r="I120" s="157"/>
+      <c r="J120" s="163">
         <f>-20862.34+20810</f>
         <v>-52.340000000000146</v>
       </c>
-      <c r="K120" s="156"/>
-      <c r="L120" s="155"/>
-      <c r="M120" s="156"/>
-    </row>
-    <row r="121" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E121" s="165"/>
-      <c r="F121" s="158"/>
-      <c r="G121" s="158"/>
-      <c r="H121" s="158"/>
-      <c r="I121" s="158"/>
-      <c r="J121" s="164"/>
-      <c r="K121" s="156"/>
-      <c r="L121" s="155"/>
-      <c r="M121" s="156"/>
-    </row>
-    <row r="122" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E122" s="165"/>
-      <c r="F122" s="158"/>
-      <c r="G122" s="158"/>
-      <c r="H122" s="158"/>
-      <c r="I122" s="158"/>
-      <c r="J122" s="164"/>
-      <c r="K122" s="156"/>
-      <c r="L122" s="155"/>
-      <c r="M122" s="156"/>
-    </row>
-    <row r="123" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="F123" s="158"/>
-      <c r="G123" s="158"/>
-      <c r="H123" s="158"/>
-      <c r="I123" s="158"/>
-      <c r="J123" s="164"/>
-      <c r="K123" s="156"/>
-      <c r="L123" s="155"/>
-      <c r="M123" s="156"/>
-    </row>
-    <row r="124" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E124" s="165"/>
-      <c r="F124" s="158"/>
-      <c r="G124" s="158"/>
-      <c r="H124" s="158"/>
-      <c r="I124" s="158"/>
-      <c r="J124" s="164"/>
-      <c r="K124" s="156"/>
-      <c r="L124" s="155"/>
-      <c r="M124" s="156"/>
-    </row>
-    <row r="125" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E125" s="155"/>
-      <c r="F125" s="158"/>
-      <c r="G125" s="158"/>
-      <c r="H125" s="158"/>
-      <c r="I125" s="158"/>
-      <c r="J125" s="158"/>
-      <c r="K125" s="156"/>
-      <c r="L125" s="155"/>
-      <c r="M125" s="156"/>
-    </row>
-    <row r="126" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E126" s="155"/>
-      <c r="F126" s="158"/>
-      <c r="G126" s="158"/>
-      <c r="H126" s="158"/>
-      <c r="I126" s="158"/>
-      <c r="J126" s="158"/>
-      <c r="K126" s="156"/>
-      <c r="L126" s="155"/>
-      <c r="M126" s="156"/>
-    </row>
-    <row r="127" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E127" s="155"/>
-      <c r="F127" s="158"/>
-      <c r="G127" s="158"/>
-      <c r="H127" s="158"/>
-      <c r="I127" s="158"/>
-      <c r="J127" s="158"/>
-      <c r="K127" s="156"/>
-      <c r="L127" s="166"/>
-      <c r="M127" s="167"/>
-    </row>
-    <row r="128" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E128" s="199" t="s">
-        <v>121</v>
-      </c>
-      <c r="F128" s="200"/>
-      <c r="G128" s="200"/>
-      <c r="H128" s="200"/>
-      <c r="I128" s="200"/>
-      <c r="J128" s="201">
+      <c r="K120" s="155"/>
+      <c r="L120" s="154"/>
+      <c r="M120" s="155"/>
+    </row>
+    <row r="121" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E121" s="164"/>
+      <c r="F121" s="157"/>
+      <c r="G121" s="157"/>
+      <c r="H121" s="157"/>
+      <c r="I121" s="157"/>
+      <c r="J121" s="163"/>
+      <c r="K121" s="155"/>
+      <c r="L121" s="154"/>
+      <c r="M121" s="155"/>
+    </row>
+    <row r="122" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E122" s="164"/>
+      <c r="F122" s="157"/>
+      <c r="G122" s="157"/>
+      <c r="H122" s="157"/>
+      <c r="I122" s="157"/>
+      <c r="J122" s="163"/>
+      <c r="K122" s="155"/>
+      <c r="L122" s="154"/>
+      <c r="M122" s="155"/>
+    </row>
+    <row r="123" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F123" s="157"/>
+      <c r="G123" s="157"/>
+      <c r="H123" s="157"/>
+      <c r="I123" s="157"/>
+      <c r="J123" s="163"/>
+      <c r="K123" s="155"/>
+      <c r="L123" s="154"/>
+      <c r="M123" s="155"/>
+    </row>
+    <row r="124" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E124" s="164"/>
+      <c r="F124" s="157"/>
+      <c r="G124" s="157"/>
+      <c r="H124" s="157"/>
+      <c r="I124" s="157"/>
+      <c r="J124" s="163"/>
+      <c r="K124" s="155"/>
+      <c r="L124" s="154"/>
+      <c r="M124" s="155"/>
+    </row>
+    <row r="125" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E125" s="154"/>
+      <c r="F125" s="157"/>
+      <c r="G125" s="157"/>
+      <c r="H125" s="157"/>
+      <c r="I125" s="157"/>
+      <c r="J125" s="157"/>
+      <c r="K125" s="155"/>
+      <c r="L125" s="154"/>
+      <c r="M125" s="155"/>
+    </row>
+    <row r="126" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E126" s="154"/>
+      <c r="F126" s="157"/>
+      <c r="G126" s="157"/>
+      <c r="H126" s="157"/>
+      <c r="I126" s="157"/>
+      <c r="J126" s="157"/>
+      <c r="K126" s="155"/>
+      <c r="L126" s="154"/>
+      <c r="M126" s="155"/>
+    </row>
+    <row r="127" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E127" s="154"/>
+      <c r="F127" s="157"/>
+      <c r="G127" s="157"/>
+      <c r="H127" s="157"/>
+      <c r="I127" s="157"/>
+      <c r="J127" s="157"/>
+      <c r="K127" s="155"/>
+      <c r="L127" s="165"/>
+      <c r="M127" s="166"/>
+    </row>
+    <row r="128" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E128" s="198" t="s">
+        <v>119</v>
+      </c>
+      <c r="F128" s="199"/>
+      <c r="G128" s="199"/>
+      <c r="H128" s="199"/>
+      <c r="I128" s="199"/>
+      <c r="J128" s="200">
         <f>SUM(J118:J127)</f>
-        <v>41567.282545752518</v>
-      </c>
-      <c r="K128" s="191"/>
-      <c r="L128" s="168"/>
-      <c r="M128" s="169"/>
+        <v>97620.912219999998</v>
+      </c>
+      <c r="K128" s="190"/>
+      <c r="L128" s="167"/>
+      <c r="M128" s="168"/>
     </row>
   </sheetData>
-  <mergeCells count="45">
+  <mergeCells count="46">
+    <mergeCell ref="H1:I1"/>
     <mergeCell ref="E128:I128"/>
     <mergeCell ref="J128:K128"/>
     <mergeCell ref="E108:K108"/>
@@ -4748,520 +4824,520 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="7" width="15.44140625" customWidth="1"/>
-    <col min="8" max="8" width="18.33203125" customWidth="1"/>
-    <col min="9" max="9" width="13.5546875" customWidth="1"/>
-    <col min="10" max="10" width="22.5546875" customWidth="1"/>
-    <col min="11" max="11" width="13.88671875" customWidth="1"/>
+    <col min="6" max="7" width="15.42578125" customWidth="1"/>
+    <col min="8" max="8" width="18.28515625" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" customWidth="1"/>
+    <col min="10" max="10" width="22.5703125" customWidth="1"/>
+    <col min="11" max="11" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B1" s="112" t="s">
+    <row r="1" spans="1:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="B1" s="111" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" s="112" t="s">
+        <v>123</v>
+      </c>
+      <c r="D1" s="113"/>
+      <c r="F1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G1" t="s">
         <v>81</v>
       </c>
-      <c r="C1" s="113" t="s">
-        <v>125</v>
-      </c>
-      <c r="D1" s="114"/>
-      <c r="F1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="H1" s="143">
+        <v>10296.959999999999</v>
+      </c>
+      <c r="K1" s="114"/>
+      <c r="L1" s="115"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H2" s="116"/>
+      <c r="I2" s="116"/>
+      <c r="J2" s="116"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B3" s="117" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" s="111" t="s">
         <v>83</v>
       </c>
-      <c r="H1" s="144">
-        <v>10296.959999999999</v>
-      </c>
-      <c r="K1" s="115"/>
-      <c r="L1" s="116"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="H2" s="117"/>
-      <c r="I2" s="117"/>
-      <c r="J2" s="117"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B3" s="118" t="s">
+      <c r="D3" s="111" t="s">
+        <v>83</v>
+      </c>
+      <c r="E3" s="111" t="s">
         <v>84</v>
       </c>
-      <c r="C3" s="112" t="s">
+      <c r="F3" s="111" t="s">
         <v>85</v>
       </c>
-      <c r="D3" s="112" t="s">
-        <v>85</v>
-      </c>
-      <c r="E3" s="112" t="s">
+      <c r="G3" s="111" t="s">
         <v>86</v>
       </c>
-      <c r="F3" s="112" t="s">
+      <c r="H3" s="118" t="s">
         <v>87</v>
       </c>
-      <c r="G3" s="112" t="s">
+      <c r="I3" s="117"/>
+      <c r="J3" s="117"/>
+      <c r="K3" s="5"/>
+      <c r="M3" s="119"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B4" s="117"/>
+      <c r="C4" s="111" t="s">
         <v>88</v>
       </c>
-      <c r="H3" s="119" t="s">
+      <c r="D4" s="111" t="s">
         <v>89</v>
       </c>
-      <c r="I3" s="118"/>
-      <c r="J3" s="118"/>
-      <c r="K3" s="5"/>
-      <c r="M3" s="120"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B4" s="118"/>
-      <c r="C4" s="112" t="s">
-        <v>90</v>
-      </c>
-      <c r="D4" s="112" t="s">
-        <v>91</v>
-      </c>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="H4" s="121">
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="H4" s="120">
         <f>H1</f>
         <v>10296.959999999999</v>
       </c>
-      <c r="I4" s="121"/>
-      <c r="J4" s="121"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="I4" s="120"/>
+      <c r="J4" s="120"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="B5" s="118">
+        <v>90</v>
+      </c>
+      <c r="B5" s="117">
         <v>1</v>
       </c>
       <c r="C5">
         <v>7735</v>
       </c>
-      <c r="D5" s="114">
+      <c r="D5" s="113">
         <f>C5+82</f>
         <v>7817</v>
       </c>
-      <c r="E5" s="118">
+      <c r="E5" s="117">
         <f>D5-C5</f>
         <v>82</v>
       </c>
-      <c r="F5" s="118">
+      <c r="F5" s="117">
         <f>E5*100/D14</f>
         <v>13.7123745819398</v>
       </c>
       <c r="G5" s="5"/>
-      <c r="H5" s="122">
+      <c r="H5" s="121">
         <f>H4*(F5/100)</f>
         <v>1411.9577257525084</v>
       </c>
-      <c r="I5" s="118"/>
+      <c r="I5" s="117"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
-      <c r="L5" s="123"/>
-      <c r="M5" s="124"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="L5" s="122"/>
+      <c r="M5" s="123"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="B6" s="118">
+        <v>91</v>
+      </c>
+      <c r="B6" s="117">
         <v>2</v>
       </c>
       <c r="C6">
         <v>7076</v>
       </c>
-      <c r="D6" s="114">
+      <c r="D6" s="113">
         <f>C6+98</f>
         <v>7174</v>
       </c>
-      <c r="E6" s="118">
+      <c r="E6" s="117">
         <f>D6-C6</f>
         <v>98</v>
       </c>
-      <c r="F6" s="118">
+      <c r="F6" s="117">
         <f>E6*100/D14</f>
         <v>16.387959866220736</v>
       </c>
       <c r="G6" s="5"/>
-      <c r="H6" s="122">
+      <c r="H6" s="121">
         <f>H4*(F6/100)</f>
         <v>1687.4616722408025</v>
       </c>
-      <c r="I6" s="118"/>
+      <c r="I6" s="117"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
-      <c r="L6" s="123"/>
-      <c r="M6" s="124"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="L6" s="122"/>
+      <c r="M6" s="123"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="B7" s="118">
+        <v>92</v>
+      </c>
+      <c r="B7" s="117">
         <v>3</v>
       </c>
       <c r="C7">
         <v>7694</v>
       </c>
-      <c r="D7" s="114">
+      <c r="D7" s="113">
         <f>C7+97</f>
         <v>7791</v>
       </c>
-      <c r="E7" s="118">
+      <c r="E7" s="117">
         <f t="shared" ref="E7:E11" si="0">D7-C7</f>
         <v>97</v>
       </c>
-      <c r="F7" s="118">
+      <c r="F7" s="117">
         <f>E7*100/D14</f>
         <v>16.220735785953178</v>
       </c>
-      <c r="H7" s="125">
+      <c r="H7" s="124">
         <f>H4*(F7/100)</f>
         <v>1670.2426755852841</v>
       </c>
-      <c r="I7" s="112"/>
+      <c r="I7" s="111"/>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
-      <c r="L7" s="123"/>
-      <c r="M7" s="124"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="L7" s="122"/>
+      <c r="M7" s="123"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="B8" s="118">
+        <v>93</v>
+      </c>
+      <c r="B8" s="117">
         <v>4</v>
       </c>
       <c r="C8">
         <v>9262</v>
       </c>
-      <c r="D8" s="114">
+      <c r="D8" s="113">
         <f>C8+107</f>
         <v>9369</v>
       </c>
-      <c r="E8" s="118">
+      <c r="E8" s="117">
         <f t="shared" si="0"/>
         <v>107</v>
       </c>
-      <c r="F8" s="118">
+      <c r="F8" s="117">
         <f>E8*100/D14</f>
         <v>17.892976588628763</v>
       </c>
       <c r="G8" s="5"/>
-      <c r="H8" s="122">
+      <c r="H8" s="121">
         <f>H4*(F8/100)</f>
         <v>1842.432642140468</v>
       </c>
-      <c r="I8" s="118"/>
+      <c r="I8" s="117"/>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
-      <c r="L8" s="123"/>
-      <c r="M8" s="124"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="L8" s="122"/>
+      <c r="M8" s="123"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B9" s="118">
+        <v>94</v>
+      </c>
+      <c r="B9" s="117">
         <v>5</v>
       </c>
       <c r="C9">
         <v>10635</v>
       </c>
-      <c r="D9" s="114">
+      <c r="D9" s="113">
         <f>C9+60</f>
         <v>10695</v>
       </c>
-      <c r="E9" s="118">
+      <c r="E9" s="117">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="F9" s="118">
+      <c r="F9" s="117">
         <f>E9*100/D14</f>
         <v>10.033444816053512</v>
       </c>
       <c r="G9" s="5"/>
-      <c r="H9" s="122">
+      <c r="H9" s="121">
         <f>H4*(F9/100)</f>
         <v>1033.1397993311036</v>
       </c>
-      <c r="I9" s="118"/>
+      <c r="I9" s="117"/>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
-      <c r="L9" s="123"/>
-      <c r="M9" s="124"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="L9" s="122"/>
+      <c r="M9" s="123"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="B10" s="118">
+        <v>95</v>
+      </c>
+      <c r="B10" s="117">
         <v>6</v>
       </c>
       <c r="C10">
         <v>10706</v>
       </c>
-      <c r="D10" s="114">
+      <c r="D10" s="113">
         <f>C10+37+12+12</f>
         <v>10767</v>
       </c>
-      <c r="E10" s="118">
+      <c r="E10" s="117">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="F10" s="118">
+      <c r="F10" s="117">
         <f>E10*100/D14</f>
         <v>10.200668896321071</v>
       </c>
       <c r="G10" s="5"/>
-      <c r="H10" s="122">
+      <c r="H10" s="121">
         <f>H4*(F10/100)</f>
         <v>1050.358795986622</v>
       </c>
-      <c r="I10" s="118"/>
+      <c r="I10" s="117"/>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
-      <c r="L10" s="123"/>
-      <c r="M10" s="124"/>
-    </row>
-    <row r="11" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L10" s="122"/>
+      <c r="M10" s="123"/>
+    </row>
+    <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B11" s="118">
+        <v>96</v>
+      </c>
+      <c r="B11" s="117">
         <v>7</v>
       </c>
       <c r="C11">
         <v>13147</v>
       </c>
-      <c r="D11" s="114">
+      <c r="D11" s="113">
         <f>C11+93</f>
         <v>13240</v>
       </c>
-      <c r="E11" s="118">
+      <c r="E11" s="117">
         <f t="shared" si="0"/>
         <v>93</v>
       </c>
-      <c r="F11" s="118">
+      <c r="F11" s="117">
         <f>E11*100/D14</f>
         <v>15.551839464882944</v>
       </c>
       <c r="G11" s="5"/>
-      <c r="H11" s="122">
+      <c r="H11" s="121">
         <f>H4*(F11/100)</f>
         <v>1601.3666889632107</v>
       </c>
-      <c r="I11" s="118"/>
+      <c r="I11" s="117"/>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
-      <c r="L11" s="123"/>
-      <c r="M11" s="124"/>
-    </row>
-    <row r="12" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="126"/>
-      <c r="C12" s="127">
+      <c r="L11" s="122"/>
+      <c r="M11" s="123"/>
+    </row>
+    <row r="12" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="125"/>
+      <c r="C12" s="126">
         <f>SUM(C5:C11)</f>
         <v>66255</v>
       </c>
-      <c r="D12" s="127">
+      <c r="D12" s="126">
         <f>SUM(D5:D11)</f>
         <v>66853</v>
       </c>
-      <c r="E12" s="128">
+      <c r="E12" s="127">
         <f>SUM(E5:E11)</f>
         <v>598</v>
       </c>
-      <c r="F12" s="127">
+      <c r="F12" s="126">
         <f>SUM(F5:F11)</f>
         <v>100.00000000000003</v>
       </c>
-      <c r="G12" s="62"/>
-      <c r="H12" s="127">
+      <c r="G12" s="61"/>
+      <c r="H12" s="126">
         <f>SUM(H5:H11)</f>
         <v>10296.959999999999</v>
       </c>
-      <c r="I12" s="126"/>
-      <c r="J12" s="126"/>
-      <c r="K12" s="126"/>
-      <c r="L12" s="129"/>
-    </row>
-    <row r="13" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C13" s="130"/>
-      <c r="H13" s="118"/>
-      <c r="I13" s="118"/>
-      <c r="J13" s="118"/>
-    </row>
-    <row r="14" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I12" s="125"/>
+      <c r="J12" s="125"/>
+      <c r="K12" s="125"/>
+      <c r="L12" s="128"/>
+    </row>
+    <row r="13" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="129"/>
+      <c r="H13" s="117"/>
+      <c r="I13" s="117"/>
+      <c r="J13" s="117"/>
+    </row>
+    <row r="14" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>99</v>
-      </c>
-      <c r="D14" s="131">
+        <v>97</v>
+      </c>
+      <c r="D14" s="130">
         <f>D12-C12</f>
         <v>598</v>
       </c>
-      <c r="H14" s="118"/>
-      <c r="I14" s="118"/>
-      <c r="J14" s="118"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H14" s="117"/>
+      <c r="I14" s="117"/>
+      <c r="J14" s="117"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>100</v>
-      </c>
-      <c r="H15" s="118"/>
-      <c r="I15" s="118"/>
-      <c r="J15" s="118"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B16" s="118"/>
-      <c r="C16" s="112"/>
-      <c r="D16" s="112"/>
-      <c r="E16" s="112"/>
-      <c r="F16" s="112"/>
-      <c r="H16" s="112"/>
-      <c r="I16" s="112"/>
-      <c r="J16" s="112"/>
+        <v>98</v>
+      </c>
+      <c r="H15" s="117"/>
+      <c r="I15" s="117"/>
+      <c r="J15" s="117"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B16" s="117"/>
+      <c r="C16" s="111"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="111"/>
+      <c r="F16" s="111"/>
+      <c r="H16" s="111"/>
+      <c r="I16" s="111"/>
+      <c r="J16" s="111"/>
       <c r="K16" s="5"/>
     </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B17" s="118"/>
-      <c r="C17" s="112"/>
-      <c r="D17" s="112"/>
-      <c r="E17" s="112"/>
-      <c r="F17" s="112"/>
-      <c r="H17" s="121"/>
-      <c r="I17" s="121"/>
-      <c r="J17" s="121"/>
-    </row>
-    <row r="18" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="H18" s="118"/>
-      <c r="I18" s="118"/>
-      <c r="J18" s="118"/>
-    </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="C19" s="132"/>
-      <c r="D19" s="133"/>
-      <c r="E19" s="133"/>
-      <c r="F19" s="133"/>
-      <c r="G19" s="133"/>
-      <c r="H19" s="134"/>
-      <c r="I19" s="134"/>
-      <c r="J19" s="134"/>
-      <c r="K19" s="133"/>
-      <c r="L19" s="133"/>
-      <c r="M19" s="135"/>
-    </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="C20" s="136"/>
+    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B17" s="117"/>
+      <c r="C17" s="111"/>
+      <c r="D17" s="111"/>
+      <c r="E17" s="111"/>
+      <c r="F17" s="111"/>
+      <c r="H17" s="120"/>
+      <c r="I17" s="120"/>
+      <c r="J17" s="120"/>
+    </row>
+    <row r="18" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H18" s="117"/>
+      <c r="I18" s="117"/>
+      <c r="J18" s="117"/>
+    </row>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C19" s="131"/>
+      <c r="D19" s="132"/>
+      <c r="E19" s="132"/>
+      <c r="F19" s="132"/>
+      <c r="G19" s="132"/>
+      <c r="H19" s="133"/>
+      <c r="I19" s="133"/>
+      <c r="J19" s="133"/>
+      <c r="K19" s="132"/>
+      <c r="L19" s="132"/>
+      <c r="M19" s="134"/>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C20" s="135"/>
       <c r="E20" t="s">
-        <v>101</v>
-      </c>
-      <c r="H20" s="137">
+        <v>99</v>
+      </c>
+      <c r="H20" s="136">
         <f>D14</f>
         <v>598</v>
       </c>
-      <c r="I20" s="137"/>
-      <c r="J20" s="137"/>
+      <c r="I20" s="136"/>
+      <c r="J20" s="136"/>
       <c r="K20" t="s">
-        <v>102</v>
-      </c>
-      <c r="M20" s="138"/>
-    </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="C21" s="136"/>
+        <v>100</v>
+      </c>
+      <c r="M20" s="137"/>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C21" s="135"/>
       <c r="D21" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E21">
         <v>7</v>
       </c>
       <c r="F21" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G21">
         <v>197</v>
       </c>
       <c r="H21" t="s">
+        <v>103</v>
+      </c>
+      <c r="K21" t="s">
+        <v>104</v>
+      </c>
+      <c r="M21" s="137"/>
+    </row>
+    <row r="22" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C22" s="138"/>
+      <c r="D22" s="139"/>
+      <c r="E22" s="139"/>
+      <c r="F22" s="139"/>
+      <c r="G22" s="139"/>
+      <c r="H22" s="139"/>
+      <c r="I22" s="139"/>
+      <c r="J22" s="139"/>
+      <c r="K22" s="139"/>
+      <c r="L22" s="139"/>
+      <c r="M22" s="140"/>
+    </row>
+    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K25" s="141" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="G26" s="5"/>
+      <c r="K26" s="119"/>
+    </row>
+    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="I27" t="s">
         <v>105</v>
-      </c>
-      <c r="K21" t="s">
-        <v>106</v>
-      </c>
-      <c r="M21" s="138"/>
-    </row>
-    <row r="22" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C22" s="139"/>
-      <c r="D22" s="140"/>
-      <c r="E22" s="140"/>
-      <c r="F22" s="140"/>
-      <c r="G22" s="140"/>
-      <c r="H22" s="140"/>
-      <c r="I22" s="140"/>
-      <c r="J22" s="140"/>
-      <c r="K22" s="140"/>
-      <c r="L22" s="140"/>
-      <c r="M22" s="141"/>
-    </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="K25" s="142" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="G26" s="5"/>
-      <c r="K26" s="120"/>
-    </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="I27" t="s">
-        <v>107</v>
       </c>
       <c r="J27" t="s">
         <v>5</v>
       </c>
       <c r="K27" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13" x14ac:dyDescent="0.25">
       <c r="G28" s="5"/>
       <c r="H28" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I28" s="5">
         <v>29829</v>
       </c>
-      <c r="J28" s="123">
+      <c r="J28" s="122">
         <v>16000</v>
       </c>
-      <c r="K28" s="124">
+      <c r="K28" s="123">
         <f t="shared" ref="K28" si="1">I28+J28</f>
         <v>45829</v>
       </c>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:13" x14ac:dyDescent="0.25">
       <c r="J31" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="K31">
         <v>117067</v>
       </c>
     </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
       <c r="J32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K32">
         <v>-55000</v>
       </c>
     </row>
-    <row r="33" spans="10:11" x14ac:dyDescent="0.3">
-      <c r="J33" s="120" t="s">
-        <v>111</v>
+    <row r="33" spans="10:11" x14ac:dyDescent="0.25">
+      <c r="J33" s="119" t="s">
+        <v>109</v>
       </c>
       <c r="K33">
         <v>43965</v>
       </c>
     </row>
-    <row r="34" spans="10:11" x14ac:dyDescent="0.3">
-      <c r="K34" s="114">
+    <row r="34" spans="10:11" x14ac:dyDescent="0.25">
+      <c r="K34" s="113">
         <f>SUM(K31:K33)</f>
         <v>106032</v>
       </c>
@@ -5275,62 +5351,62 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:P14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.109375" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="12" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="10.33203125" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="11.109375" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" customWidth="1"/>
-    <col min="9" max="9" width="0.109375" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" customWidth="1"/>
+    <col min="9" max="9" width="0.140625" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="0.109375" customWidth="1"/>
+    <col min="11" max="11" width="0.140625" customWidth="1"/>
     <col min="12" max="13" width="12" customWidth="1"/>
     <col min="14" max="14" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D1" s="56">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="D1" s="55">
         <v>50000</v>
       </c>
-      <c r="H1" s="206">
+      <c r="H1" s="205">
         <v>250000</v>
       </c>
-      <c r="I1" s="206"/>
-      <c r="J1" s="206"/>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="53" t="s">
-        <v>50</v>
+      <c r="I1" s="205"/>
+      <c r="J1" s="205"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="52" t="s">
+        <v>49</v>
       </c>
       <c r="B2" s="1"/>
       <c r="P2" s="21"/>
     </row>
-    <row r="3" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B3" s="28"/>
       <c r="C3" s="29"/>
       <c r="D3" s="30" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E3" s="28"/>
       <c r="F3" s="30" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G3" s="28"/>
       <c r="H3" s="28"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="54"/>
-      <c r="L3" s="54"/>
-      <c r="M3" s="54"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="53"/>
+      <c r="L3" s="53"/>
+      <c r="M3" s="53"/>
       <c r="N3" s="31"/>
       <c r="P3" s="21"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
@@ -5344,44 +5420,44 @@
         <v>19</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="55" t="s">
+      <c r="I4" s="54" t="s">
         <v>17</v>
       </c>
       <c r="J4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K4" s="67"/>
+      <c r="L4" s="203" t="s">
+        <v>60</v>
+      </c>
+      <c r="M4" s="80" t="s">
+        <v>5</v>
+      </c>
+      <c r="N4" s="201" t="s">
         <v>54</v>
       </c>
-      <c r="K4" s="68"/>
-      <c r="L4" s="204" t="s">
-        <v>61</v>
-      </c>
-      <c r="M4" s="81" t="s">
-        <v>5</v>
-      </c>
-      <c r="N4" s="202" t="s">
-        <v>55</v>
-      </c>
       <c r="P4" s="21"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
       <c r="D5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="57" t="s">
-        <v>47</v>
+      <c r="E5" s="56" t="s">
+        <v>46</v>
       </c>
       <c r="F5" s="7"/>
       <c r="G5" s="37">
@@ -5393,25 +5469,25 @@
       <c r="I5" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="J5" s="65" t="s">
-        <v>60</v>
-      </c>
-      <c r="K5" s="58"/>
-      <c r="L5" s="205"/>
-      <c r="M5" s="82" t="s">
-        <v>62</v>
-      </c>
-      <c r="N5" s="203"/>
+      <c r="J5" s="64" t="s">
+        <v>59</v>
+      </c>
+      <c r="K5" s="57"/>
+      <c r="L5" s="204"/>
+      <c r="M5" s="81" t="s">
+        <v>61</v>
+      </c>
+      <c r="N5" s="202"/>
       <c r="P5" s="21"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>1</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="60" t="s">
+      <c r="C6" s="59" t="s">
         <v>30</v>
       </c>
       <c r="D6" s="46">
@@ -5424,7 +5500,7 @@
         <f>+D6-E6</f>
         <v>0</v>
       </c>
-      <c r="G6" s="51">
+      <c r="G6" s="50">
         <v>0</v>
       </c>
       <c r="H6" s="17">
@@ -5434,11 +5510,11 @@
         <f>H$1*H6</f>
         <v>30250</v>
       </c>
-      <c r="J6" s="66">
+      <c r="J6" s="65">
         <v>9706.619999999999</v>
       </c>
-      <c r="K6" s="69"/>
-      <c r="L6" s="66">
+      <c r="K6" s="68"/>
+      <c r="L6" s="65">
         <f>(J6+K6)*5%+(J6+K6)*5%+(J6+K6)*5%+(J6+K6)*5%+(J6+K6)*5%</f>
         <v>2426.6549999999997</v>
       </c>
@@ -5446,20 +5522,20 @@
         <f>H$1*H6</f>
         <v>30250</v>
       </c>
-      <c r="N6" s="67">
+      <c r="N6" s="66">
         <f>J6+K6+L6+M6</f>
         <v>42383.274999999994</v>
       </c>
       <c r="P6" s="21"/>
     </row>
-    <row r="7" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <v>2</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="60" t="s">
+      <c r="C7" s="59" t="s">
         <v>31</v>
       </c>
       <c r="D7" s="46">
@@ -5472,7 +5548,7 @@
         <f t="shared" ref="F7:F13" si="0">+D7-E7</f>
         <v>0</v>
       </c>
-      <c r="G7" s="51">
+      <c r="G7" s="50">
         <v>0</v>
       </c>
       <c r="H7" s="17">
@@ -5482,11 +5558,11 @@
         <f t="shared" ref="I7:I13" si="1">H$1*H7</f>
         <v>30500</v>
       </c>
-      <c r="J7" s="66">
+      <c r="J7" s="65">
         <v>19573.68</v>
       </c>
-      <c r="K7" s="69"/>
-      <c r="L7" s="66">
+      <c r="K7" s="68"/>
+      <c r="L7" s="65">
         <f t="shared" ref="L7:L13" si="2">(J7+K7)*5%+(J7+K7)*5%+(J7+K7)*5%+(J7+K7)*5%+(J7+K7)*5%</f>
         <v>4893.42</v>
       </c>
@@ -5494,20 +5570,20 @@
         <f t="shared" ref="M7:M13" si="3">H$1*H7</f>
         <v>30500</v>
       </c>
-      <c r="N7" s="67">
+      <c r="N7" s="66">
         <f t="shared" ref="N7:N13" si="4">J7+K7+L7+M7</f>
         <v>54967.1</v>
       </c>
       <c r="P7" s="21"/>
     </row>
-    <row r="8" spans="1:16" ht="27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>3</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="60" t="s">
+      <c r="C8" s="59" t="s">
         <v>32</v>
       </c>
       <c r="D8" s="46">
@@ -5520,7 +5596,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G8" s="51">
+      <c r="G8" s="50">
         <v>0</v>
       </c>
       <c r="H8" s="17">
@@ -5530,11 +5606,11 @@
         <f t="shared" si="1"/>
         <v>29250</v>
       </c>
-      <c r="J8" s="66">
-        <v>0</v>
-      </c>
-      <c r="K8" s="69"/>
-      <c r="L8" s="66">
+      <c r="J8" s="65">
+        <v>0</v>
+      </c>
+      <c r="K8" s="68"/>
+      <c r="L8" s="65">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5542,20 +5618,20 @@
         <f t="shared" si="3"/>
         <v>29250</v>
       </c>
-      <c r="N8" s="67">
+      <c r="N8" s="66">
         <f t="shared" si="4"/>
         <v>29250</v>
       </c>
       <c r="P8" s="21"/>
     </row>
-    <row r="9" spans="1:16" ht="27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>4</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="60" t="s">
+      <c r="C9" s="59" t="s">
         <v>33</v>
       </c>
       <c r="D9" s="46">
@@ -5568,7 +5644,7 @@
         <f>+D9-E9</f>
         <v>0</v>
       </c>
-      <c r="G9" s="51">
+      <c r="G9" s="50">
         <v>0</v>
       </c>
       <c r="H9" s="17">
@@ -5578,11 +5654,11 @@
         <f t="shared" si="1"/>
         <v>29250</v>
       </c>
-      <c r="J9" s="66">
+      <c r="J9" s="65">
         <v>18771.480000000003</v>
       </c>
-      <c r="K9" s="69"/>
-      <c r="L9" s="66">
+      <c r="K9" s="68"/>
+      <c r="L9" s="65">
         <f t="shared" si="2"/>
         <v>4692.8700000000008</v>
       </c>
@@ -5590,20 +5666,20 @@
         <f t="shared" si="3"/>
         <v>29250</v>
       </c>
-      <c r="N9" s="67">
+      <c r="N9" s="66">
         <f t="shared" si="4"/>
         <v>52714.350000000006</v>
       </c>
       <c r="P9" s="21"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>5</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="60" t="s">
+      <c r="C10" s="59" t="s">
         <v>30</v>
       </c>
       <c r="D10" s="46">
@@ -5616,7 +5692,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G10" s="51">
+      <c r="G10" s="50">
         <v>0</v>
       </c>
       <c r="H10" s="17">
@@ -5626,11 +5702,11 @@
         <f t="shared" si="1"/>
         <v>34250</v>
       </c>
-      <c r="J10" s="66">
+      <c r="J10" s="65">
         <v>10990.140000000001</v>
       </c>
-      <c r="K10" s="69"/>
-      <c r="L10" s="66">
+      <c r="K10" s="68"/>
+      <c r="L10" s="65">
         <f t="shared" si="2"/>
         <v>2747.5350000000003</v>
       </c>
@@ -5638,20 +5714,20 @@
         <f t="shared" si="3"/>
         <v>34250</v>
       </c>
-      <c r="N10" s="67">
+      <c r="N10" s="66">
         <f t="shared" si="4"/>
         <v>47987.675000000003</v>
       </c>
       <c r="P10" s="21"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>6</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="60" t="s">
+      <c r="C11" s="59" t="s">
         <v>30</v>
       </c>
       <c r="D11" s="46">
@@ -5664,7 +5740,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G11" s="51">
+      <c r="G11" s="50">
         <v>0</v>
       </c>
       <c r="H11" s="17">
@@ -5674,11 +5750,11 @@
         <f t="shared" si="1"/>
         <v>33000</v>
       </c>
-      <c r="J11" s="66">
+      <c r="J11" s="65">
         <v>10589.04</v>
       </c>
-      <c r="K11" s="69"/>
-      <c r="L11" s="66">
+      <c r="K11" s="68"/>
+      <c r="L11" s="65">
         <f t="shared" si="2"/>
         <v>2647.2600000000007</v>
       </c>
@@ -5686,20 +5762,20 @@
         <f t="shared" si="3"/>
         <v>33000</v>
       </c>
-      <c r="N11" s="67">
+      <c r="N11" s="66">
         <f t="shared" si="4"/>
         <v>46236.3</v>
       </c>
       <c r="P11" s="21"/>
     </row>
-    <row r="12" spans="1:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>7</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="60" t="s">
+      <c r="C12" s="59" t="s">
         <v>32</v>
       </c>
       <c r="D12" s="46">
@@ -5712,7 +5788,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G12" s="51">
+      <c r="G12" s="50">
         <v>0</v>
       </c>
       <c r="H12" s="17">
@@ -5722,11 +5798,11 @@
         <f t="shared" si="1"/>
         <v>31750</v>
       </c>
-      <c r="J12" s="66">
-        <v>0</v>
-      </c>
-      <c r="K12" s="69"/>
-      <c r="L12" s="66">
+      <c r="J12" s="65">
+        <v>0</v>
+      </c>
+      <c r="K12" s="68"/>
+      <c r="L12" s="65">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5734,20 +5810,20 @@
         <f t="shared" si="3"/>
         <v>31750</v>
       </c>
-      <c r="N12" s="67">
+      <c r="N12" s="66">
         <f t="shared" si="4"/>
         <v>31750</v>
       </c>
       <c r="P12" s="21"/>
     </row>
-    <row r="13" spans="1:16" ht="27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>8</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="60" t="s">
+      <c r="C13" s="59" t="s">
         <v>34</v>
       </c>
       <c r="D13" s="46">
@@ -5760,7 +5836,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G13" s="51">
+      <c r="G13" s="50">
         <v>0</v>
       </c>
       <c r="H13" s="17">
@@ -5770,11 +5846,11 @@
         <f t="shared" si="1"/>
         <v>31750</v>
       </c>
-      <c r="J13" s="66">
-        <v>0</v>
-      </c>
-      <c r="K13" s="69"/>
-      <c r="L13" s="66">
+      <c r="J13" s="65">
+        <v>0</v>
+      </c>
+      <c r="K13" s="68"/>
+      <c r="L13" s="65">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5782,13 +5858,13 @@
         <f t="shared" si="3"/>
         <v>31750</v>
       </c>
-      <c r="N13" s="67">
+      <c r="N13" s="66">
         <f t="shared" si="4"/>
         <v>31750</v>
       </c>
       <c r="P13" s="21"/>
     </row>
-    <row r="14" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>11</v>
       </c>
@@ -5806,7 +5882,7 @@
         <f t="shared" ref="F14" si="5">SUM(F6:F13)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="52">
+      <c r="G14" s="51">
         <f>SUM(G6:G13)</f>
         <v>0</v>
       </c>
@@ -5854,68 +5930,65 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N128"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="1.77734375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" customWidth="1"/>
-    <col min="6" max="6" width="10.6640625" customWidth="1"/>
-    <col min="7" max="7" width="9.5546875" customWidth="1"/>
-    <col min="8" max="8" width="10.33203125" customWidth="1"/>
-    <col min="9" max="9" width="8.33203125" customWidth="1"/>
-    <col min="10" max="10" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.44140625" customWidth="1"/>
-    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.5546875" style="21"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="1.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" customWidth="1"/>
+    <col min="7" max="7" width="9.5703125" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" customWidth="1"/>
+    <col min="9" max="9" width="8.28515625" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.5703125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="211" t="s">
-        <v>130</v>
-      </c>
-      <c r="B1" s="211"/>
-      <c r="C1" s="211"/>
-      <c r="D1" s="210">
-        <f>350535.51+12600</f>
-        <v>363135.51</v>
-      </c>
-      <c r="E1" s="210"/>
-      <c r="F1" s="211" t="s">
-        <v>134</v>
-      </c>
-      <c r="G1" s="211"/>
-      <c r="H1" s="211"/>
-      <c r="I1" s="207">
+    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="209" t="s">
+        <v>126</v>
+      </c>
+      <c r="B1" s="209"/>
+      <c r="C1" s="209"/>
+      <c r="D1" s="208"/>
+      <c r="E1" s="208"/>
+      <c r="F1" s="209" t="s">
+        <v>131</v>
+      </c>
+      <c r="G1" s="209"/>
+      <c r="H1" s="209"/>
+      <c r="I1" s="210">
         <v>800000</v>
       </c>
-      <c r="J1" s="207"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="98"/>
-      <c r="B2" s="99"/>
-      <c r="C2" s="100"/>
-      <c r="D2" s="100"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="102"/>
-      <c r="K2" s="102"/>
-      <c r="L2" s="103"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="183" t="s">
+      <c r="J1" s="210"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="97"/>
+      <c r="B2" s="98"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="98"/>
+      <c r="H2" s="98"/>
+      <c r="I2" s="98"/>
+      <c r="J2" s="101"/>
+      <c r="K2" s="101"/>
+      <c r="L2" s="102"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="182" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="184"/>
-      <c r="C3" s="179" t="s">
+      <c r="B3" s="183"/>
+      <c r="C3" s="178" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="181" t="s">
-        <v>56</v>
+      <c r="D3" s="180" t="s">
+        <v>55</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>19</v>
@@ -5923,486 +5996,486 @@
       <c r="F3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="179" t="s">
+      <c r="G3" s="178" t="s">
+        <v>125</v>
+      </c>
+      <c r="H3" s="178" t="s">
+        <v>44</v>
+      </c>
+      <c r="I3" s="176" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="180" t="s">
+        <v>128</v>
+      </c>
+      <c r="K3" s="170" t="s">
+        <v>127</v>
+      </c>
+      <c r="L3" s="206" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="184"/>
+      <c r="B4" s="185"/>
+      <c r="C4" s="179"/>
+      <c r="D4" s="181"/>
+      <c r="E4" s="57" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G4" s="179"/>
+      <c r="H4" s="179"/>
+      <c r="I4" s="177"/>
+      <c r="J4" s="181"/>
+      <c r="K4" s="171" t="s">
         <v>129</v>
       </c>
-      <c r="H3" s="179" t="s">
-        <v>45</v>
-      </c>
-      <c r="I3" s="177" t="s">
-        <v>7</v>
-      </c>
-      <c r="J3" s="181" t="s">
-        <v>132</v>
-      </c>
-      <c r="K3" s="173" t="s">
-        <v>131</v>
-      </c>
-      <c r="L3" s="208" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="185"/>
-      <c r="B4" s="186"/>
-      <c r="C4" s="180"/>
-      <c r="D4" s="182"/>
-      <c r="E4" s="58" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="G4" s="180"/>
-      <c r="H4" s="180"/>
-      <c r="I4" s="178"/>
-      <c r="J4" s="182"/>
-      <c r="K4" s="174" t="s">
-        <v>133</v>
-      </c>
-      <c r="L4" s="209"/>
-    </row>
-    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="175">
+      <c r="L4" s="207"/>
+    </row>
+    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="174">
         <v>1</v>
       </c>
-      <c r="B5" s="176"/>
-      <c r="C5" s="111" t="s">
-        <v>66</v>
-      </c>
-      <c r="D5" s="59"/>
-      <c r="E5" s="150">
-        <v>0</v>
-      </c>
-      <c r="F5" s="151">
+      <c r="B5" s="175"/>
+      <c r="C5" s="110" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" s="58"/>
+      <c r="E5" s="149">
+        <v>160512.70037999999</v>
+      </c>
+      <c r="F5" s="150">
         <f>E5</f>
-        <v>0</v>
-      </c>
-      <c r="G5" s="152">
+        <v>160512.70037999999</v>
+      </c>
+      <c r="G5" s="151">
         <f>E5-F5</f>
         <v>0</v>
       </c>
-      <c r="H5" s="152">
+      <c r="H5" s="151">
         <f>IF(G5&gt;0,G5*4%,0)</f>
         <v>0</v>
       </c>
-      <c r="I5" s="96">
+      <c r="I5" s="95">
         <v>13.8</v>
       </c>
-      <c r="J5" s="212">
-        <f>D$1*I5/100</f>
-        <v>50112.700380000009</v>
-      </c>
-      <c r="K5" s="213">
+      <c r="J5" s="172">
+        <f t="shared" ref="J5:J14" si="0">D$1*I5/100</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="173">
         <f>I$1*I5/100</f>
         <v>110400</v>
       </c>
-      <c r="L5" s="104">
+      <c r="L5" s="103">
         <f>G5+H5+J5+K5</f>
-        <v>160512.70037999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="27" x14ac:dyDescent="0.3">
-      <c r="A6" s="175">
+        <v>110400</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="174">
         <v>2</v>
       </c>
-      <c r="B6" s="176"/>
-      <c r="C6" s="111" t="s">
-        <v>67</v>
-      </c>
-      <c r="D6" s="73" t="s">
-        <v>72</v>
-      </c>
-      <c r="E6" s="150">
-        <v>0</v>
-      </c>
-      <c r="F6" s="151">
-        <f t="shared" ref="F6:F9" si="0">E6</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="152">
+      <c r="B6" s="175"/>
+      <c r="C6" s="110" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="72" t="s">
+        <v>71</v>
+      </c>
+      <c r="E6" s="149">
+        <v>137947.87148599999</v>
+      </c>
+      <c r="F6" s="150">
+        <f>343581.33-F7-F13-F14</f>
+        <v>167947.86799000003</v>
+      </c>
+      <c r="G6" s="151">
         <f t="shared" ref="G6:G14" si="1">E6-F6</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="152">
+        <v>-29999.996504000039</v>
+      </c>
+      <c r="H6" s="151">
         <f t="shared" ref="H6:H14" si="2">IF(G6&gt;0,G6*4%,0)</f>
         <v>0</v>
       </c>
-      <c r="I6" s="96">
+      <c r="I6" s="95">
         <v>11.86</v>
       </c>
-      <c r="J6" s="212">
-        <f>D$1*I6/100</f>
-        <v>43067.871485999996</v>
-      </c>
-      <c r="K6" s="213">
+      <c r="J6" s="172">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K6" s="173">
         <f t="shared" ref="K6:K14" si="3">I$1*I6/100</f>
         <v>94880</v>
       </c>
-      <c r="L6" s="104">
+      <c r="L6" s="103">
         <f t="shared" ref="L6:L14" si="4">G6+H6+J6+K6</f>
-        <v>137947.87148599999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="27" x14ac:dyDescent="0.3">
-      <c r="A7" s="175">
+        <v>64880.003495999961</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="174">
         <v>3</v>
       </c>
-      <c r="B7" s="176"/>
-      <c r="C7" s="111" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" s="73" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" s="150">
-        <v>0</v>
-      </c>
-      <c r="F7" s="151">
+      <c r="B7" s="175"/>
+      <c r="C7" s="110" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="72" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" s="149">
+        <v>144926.684546</v>
+      </c>
+      <c r="F7" s="150">
+        <f>E7</f>
+        <v>144926.684546</v>
+      </c>
+      <c r="G7" s="151">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H7" s="151">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I7" s="95">
+        <v>12.46</v>
+      </c>
+      <c r="J7" s="172">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G7" s="152">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H7" s="152">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I7" s="96">
-        <v>12.46</v>
-      </c>
-      <c r="J7" s="212">
-        <f>D$1*I7/100</f>
-        <v>45246.684546000004</v>
-      </c>
-      <c r="K7" s="213">
+      <c r="K7" s="173">
         <f t="shared" si="3"/>
         <v>99680</v>
       </c>
-      <c r="L7" s="104">
+      <c r="L7" s="103">
         <f t="shared" si="4"/>
-        <v>144926.684546</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="175">
+        <v>99680</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A8" s="174">
         <v>4</v>
       </c>
-      <c r="B8" s="176"/>
-      <c r="C8" s="111" t="s">
-        <v>68</v>
-      </c>
-      <c r="D8" s="73" t="s">
-        <v>74</v>
-      </c>
-      <c r="E8" s="150">
-        <v>0</v>
-      </c>
-      <c r="F8" s="151">
+      <c r="B8" s="175"/>
+      <c r="C8" s="110" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="72" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" s="149">
+        <v>171562.48772500001</v>
+      </c>
+      <c r="F8" s="150">
+        <f>E8</f>
+        <v>171562.48772500001</v>
+      </c>
+      <c r="G8" s="151">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="151">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I8" s="95">
+        <v>14.75</v>
+      </c>
+      <c r="J8" s="172">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G8" s="152">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H8" s="152">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I8" s="96">
-        <v>14.75</v>
-      </c>
-      <c r="J8" s="212">
-        <f>D$1*I8/100</f>
-        <v>53562.487724999999</v>
-      </c>
-      <c r="K8" s="213">
+      <c r="K8" s="173">
         <f t="shared" si="3"/>
         <v>118000</v>
       </c>
-      <c r="L8" s="104">
+      <c r="L8" s="103">
         <f t="shared" si="4"/>
-        <v>171562.48772500001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="175">
+        <v>118000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="174">
         <v>5</v>
       </c>
-      <c r="B9" s="176"/>
-      <c r="C9" s="111" t="s">
-        <v>69</v>
-      </c>
-      <c r="D9" s="73" t="s">
-        <v>75</v>
-      </c>
-      <c r="E9" s="150">
-        <v>0</v>
-      </c>
-      <c r="F9" s="151">
+      <c r="B9" s="175"/>
+      <c r="C9" s="110" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" s="72" t="s">
+        <v>74</v>
+      </c>
+      <c r="E9" s="149">
+        <v>144345.11679100001</v>
+      </c>
+      <c r="F9" s="150">
+        <f>159931.14-F12</f>
+        <v>144345.12416600002</v>
+      </c>
+      <c r="G9" s="151">
+        <f t="shared" si="1"/>
+        <v>-7.3750000155996531E-3</v>
+      </c>
+      <c r="H9" s="151">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I9" s="95">
+        <v>12.41</v>
+      </c>
+      <c r="J9" s="172">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G9" s="152">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H9" s="152">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I9" s="96">
-        <v>12.41</v>
-      </c>
-      <c r="J9" s="212">
-        <f>D$1*I9/100</f>
-        <v>45065.116791</v>
-      </c>
-      <c r="K9" s="213">
+      <c r="K9" s="173">
         <f t="shared" si="3"/>
         <v>99280</v>
       </c>
-      <c r="L9" s="104">
+      <c r="L9" s="103">
         <f>G9+H9+J9+K9</f>
-        <v>144345.11679100001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="175">
+        <v>99279.992624999984</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="174">
         <v>6</v>
       </c>
-      <c r="B10" s="176"/>
-      <c r="C10" s="111" t="s">
-        <v>70</v>
-      </c>
-      <c r="D10" s="73"/>
-      <c r="E10" s="150">
-        <v>0</v>
-      </c>
-      <c r="F10" s="151">
-        <f>E10</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="152">
+      <c r="B10" s="175"/>
+      <c r="C10" s="110" t="s">
+        <v>69</v>
+      </c>
+      <c r="D10" s="72"/>
+      <c r="E10" s="149">
+        <v>145159.311648</v>
+      </c>
+      <c r="F10" s="150">
+        <f>150000</f>
+        <v>150000</v>
+      </c>
+      <c r="G10" s="151">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="152">
+        <v>-4840.6883519999974</v>
+      </c>
+      <c r="H10" s="151">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I10" s="96">
+      <c r="I10" s="95">
         <v>12.48</v>
       </c>
-      <c r="J10" s="212">
-        <f>D$1*I10/100</f>
-        <v>45319.311648000003</v>
-      </c>
-      <c r="K10" s="213">
+      <c r="J10" s="172">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="173">
         <f t="shared" si="3"/>
         <v>99840</v>
       </c>
-      <c r="L10" s="104">
+      <c r="L10" s="103">
         <f t="shared" si="4"/>
-        <v>145159.311648</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="175">
+        <v>94999.311648000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="174">
         <v>7</v>
       </c>
-      <c r="B11" s="176"/>
-      <c r="C11" s="111" t="s">
-        <v>71</v>
-      </c>
-      <c r="D11" s="73"/>
-      <c r="E11" s="150">
-        <v>0</v>
-      </c>
-      <c r="F11" s="151">
+      <c r="B11" s="175"/>
+      <c r="C11" s="110" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="72"/>
+      <c r="E11" s="149">
+        <v>212388.54412600002</v>
+      </c>
+      <c r="F11" s="150">
         <f>E11</f>
-        <v>0</v>
-      </c>
-      <c r="G11" s="152">
+        <v>212388.54412600002</v>
+      </c>
+      <c r="G11" s="151">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H11" s="152">
+      <c r="H11" s="151">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I11" s="96">
+      <c r="I11" s="95">
         <v>18.260000000000002</v>
       </c>
-      <c r="J11" s="212">
-        <f>D$1*I11/100</f>
-        <v>66308.544126000008</v>
-      </c>
-      <c r="K11" s="213">
+      <c r="J11" s="172">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="173">
         <f t="shared" si="3"/>
         <v>146080.00000000003</v>
       </c>
-      <c r="L11" s="104">
+      <c r="L11" s="103">
         <f t="shared" si="4"/>
-        <v>212388.54412600002</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="175" t="s">
-        <v>76</v>
-      </c>
-      <c r="B12" s="176"/>
-      <c r="C12" s="111" t="str">
+        <v>146080.00000000003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="174" t="s">
+        <v>75</v>
+      </c>
+      <c r="B12" s="175"/>
+      <c r="C12" s="110" t="str">
         <f>C9</f>
         <v>Grand Jorge</v>
       </c>
-      <c r="D12" s="73"/>
-      <c r="E12" s="150">
-        <v>0</v>
-      </c>
-      <c r="F12" s="151">
-        <f t="shared" ref="F12:F14" si="5">E12</f>
-        <v>0</v>
-      </c>
-      <c r="G12" s="152">
+      <c r="D12" s="72"/>
+      <c r="E12" s="149">
+        <v>15586.015834000002</v>
+      </c>
+      <c r="F12" s="150">
+        <f>E12</f>
+        <v>15586.015834000002</v>
+      </c>
+      <c r="G12" s="151">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H12" s="152">
+      <c r="H12" s="151">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I12" s="96">
+      <c r="I12" s="95">
         <v>1.34</v>
       </c>
-      <c r="J12" s="212">
-        <f>D$1*I12/100</f>
-        <v>4866.0158340000007</v>
-      </c>
-      <c r="K12" s="213">
+      <c r="J12" s="172">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K12" s="173">
         <f t="shared" si="3"/>
         <v>10720</v>
       </c>
-      <c r="L12" s="104">
+      <c r="L12" s="103">
         <f t="shared" si="4"/>
-        <v>15586.015834000002</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="175" t="s">
-        <v>77</v>
-      </c>
-      <c r="B13" s="176"/>
-      <c r="C13" s="111" t="str">
+        <v>10720</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="174" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" s="175"/>
+      <c r="C13" s="110" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
       </c>
-      <c r="D13" s="73"/>
-      <c r="E13" s="150">
-        <v>0</v>
-      </c>
-      <c r="F13" s="151">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="G13" s="152">
+      <c r="D13" s="72"/>
+      <c r="E13" s="149">
+        <v>15353.388731999999</v>
+      </c>
+      <c r="F13" s="150">
+        <f>E13</f>
+        <v>15353.388731999999</v>
+      </c>
+      <c r="G13" s="151">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H13" s="152">
+      <c r="H13" s="151">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I13" s="96">
+      <c r="I13" s="95">
         <v>1.32</v>
       </c>
-      <c r="J13" s="212">
-        <f>D$1*I13/100</f>
-        <v>4793.3887320000003</v>
-      </c>
-      <c r="K13" s="213">
+      <c r="J13" s="172">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K13" s="173">
         <f t="shared" si="3"/>
         <v>10560</v>
       </c>
-      <c r="L13" s="104">
+      <c r="L13" s="103">
         <f t="shared" si="4"/>
-        <v>15353.388731999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="175" t="s">
-        <v>78</v>
-      </c>
-      <c r="B14" s="176"/>
-      <c r="C14" s="59" t="str">
+        <v>10560</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="174" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" s="175"/>
+      <c r="C14" s="58" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
       </c>
-      <c r="D14" s="73"/>
-      <c r="E14" s="150">
-        <v>0</v>
-      </c>
-      <c r="F14" s="151">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="152">
+      <c r="D14" s="72"/>
+      <c r="E14" s="149">
+        <v>15353.388731999999</v>
+      </c>
+      <c r="F14" s="150">
+        <f>E14</f>
+        <v>15353.388731999999</v>
+      </c>
+      <c r="G14" s="151">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H14" s="152">
+      <c r="H14" s="151">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I14" s="96">
+      <c r="I14" s="95">
         <v>1.32</v>
       </c>
-      <c r="J14" s="212">
-        <f>D$1*I14/100</f>
-        <v>4793.3887320000003</v>
-      </c>
-      <c r="K14" s="213">
+      <c r="J14" s="172">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K14" s="173">
         <f t="shared" si="3"/>
         <v>10560</v>
       </c>
-      <c r="L14" s="104">
+      <c r="L14" s="103">
         <f t="shared" si="4"/>
-        <v>15353.388731999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="105" t="s">
+        <v>10560</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="104" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="106"/>
-      <c r="C15" s="107"/>
-      <c r="D15" s="107"/>
+      <c r="B15" s="105"/>
+      <c r="C15" s="106"/>
+      <c r="D15" s="106"/>
       <c r="E15" s="42">
         <f>SUM(E5:E14)</f>
-        <v>0</v>
+        <v>1163135.51</v>
       </c>
       <c r="F15" s="42">
-        <f t="shared" ref="F15:H15" si="6">SUM(F5:F14)</f>
-        <v>0</v>
+        <f t="shared" ref="F15:H15" si="5">SUM(F5:F14)</f>
+        <v>1197976.2022310002</v>
       </c>
       <c r="G15" s="42">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>-34840.692231000052</v>
       </c>
       <c r="H15" s="42">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I15" s="110">
-        <f t="shared" ref="I15" si="7">SUM(I5:I14)</f>
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I15" s="109">
+        <f t="shared" ref="I15" si="6">SUM(I5:I14)</f>
         <v>100</v>
       </c>
       <c r="J15" s="39">
         <f>SUM(J5:J14)</f>
-        <v>363135.51000000007</v>
+        <v>0</v>
       </c>
       <c r="K15" s="42">
         <f>SUM(K5:K14)</f>
@@ -6410,24 +6483,24 @@
       </c>
       <c r="L15" s="42">
         <f>SUM(L5:L14)</f>
-        <v>1163135.51</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="53" t="s">
-        <v>50</v>
+        <v>765159.30776899995</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="52" t="s">
+        <v>49</v>
       </c>
       <c r="E18">
         <v>7454</v>
       </c>
     </row>
-    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="27" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B19" s="28"/>
       <c r="C19" s="29"/>
-      <c r="D19" s="71"/>
+      <c r="D19" s="70"/>
       <c r="E19">
         <v>14805</v>
       </c>
@@ -6435,11 +6508,11 @@
       <c r="G19" s="28"/>
       <c r="H19" s="28"/>
       <c r="I19" s="28"/>
-      <c r="J19" s="54"/>
-      <c r="K19" s="54"/>
+      <c r="J19" s="53"/>
+      <c r="K19" s="53"/>
       <c r="L19" s="31"/>
     </row>
-    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>0</v>
       </c>
@@ -6458,12 +6531,12 @@
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J20" s="55" t="s">
+      <c r="J20" s="54" t="s">
         <v>17</v>
       </c>
       <c r="K20" s="45"/>
@@ -6471,7 +6544,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -6480,7 +6553,7 @@
         <v>3177</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="37">
@@ -6497,7 +6570,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
         <v>1</v>
       </c>
@@ -6507,15 +6580,15 @@
       <c r="C22" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="72"/>
+      <c r="D22" s="71"/>
       <c r="E22">
         <v>3056</v>
       </c>
       <c r="F22" s="46">
         <v>37971</v>
       </c>
-      <c r="G22" s="51"/>
-      <c r="H22" s="51">
+      <c r="G22" s="50"/>
+      <c r="H22" s="50">
         <v>0</v>
       </c>
       <c r="I22" s="17">
@@ -6531,7 +6604,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
         <v>2</v>
       </c>
@@ -6541,22 +6614,22 @@
       <c r="C23" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="D23" s="72"/>
+      <c r="D23" s="71"/>
       <c r="E23">
         <v>3056</v>
       </c>
       <c r="F23" s="46">
         <v>66612</v>
       </c>
-      <c r="G23" s="51"/>
-      <c r="H23" s="51">
+      <c r="G23" s="50"/>
+      <c r="H23" s="50">
         <v>0</v>
       </c>
       <c r="I23" s="17">
         <v>0.122</v>
       </c>
       <c r="J23" s="44">
-        <f t="shared" ref="J23:J29" si="8">0*I23</f>
+        <f t="shared" ref="J23:J29" si="7">0*I23</f>
         <v>0</v>
       </c>
       <c r="K23" s="41"/>
@@ -6565,7 +6638,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
         <v>3</v>
       </c>
@@ -6575,7 +6648,7 @@
       <c r="C24" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D24" s="72"/>
+      <c r="D24" s="71"/>
       <c r="E24">
         <f>SUM(E16:E23)</f>
         <v>34845</v>
@@ -6583,15 +6656,15 @@
       <c r="F24" s="46">
         <v>0</v>
       </c>
-      <c r="G24" s="51"/>
-      <c r="H24" s="51">
+      <c r="G24" s="50"/>
+      <c r="H24" s="50">
         <v>0</v>
       </c>
       <c r="I24" s="17">
         <v>0.11700000000000001</v>
       </c>
       <c r="J24" s="44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K24" s="41"/>
@@ -6600,7 +6673,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
         <v>4</v>
       </c>
@@ -6610,19 +6683,19 @@
       <c r="C25" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D25" s="72"/>
+      <c r="D25" s="71"/>
       <c r="F25" s="46">
         <v>0</v>
       </c>
-      <c r="G25" s="51"/>
-      <c r="H25" s="51">
+      <c r="G25" s="50"/>
+      <c r="H25" s="50">
         <v>0</v>
       </c>
       <c r="I25" s="17">
         <v>0.11700000000000001</v>
       </c>
       <c r="J25" s="44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K25" s="41"/>
@@ -6631,7 +6704,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
         <v>5</v>
       </c>
@@ -6641,19 +6714,19 @@
       <c r="C26" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D26" s="72"/>
+      <c r="D26" s="71"/>
       <c r="F26" s="46">
         <v>80517</v>
       </c>
-      <c r="G26" s="51"/>
-      <c r="H26" s="51">
+      <c r="G26" s="50"/>
+      <c r="H26" s="50">
         <v>0</v>
       </c>
       <c r="I26" s="17">
         <v>0.13700000000000001</v>
       </c>
       <c r="J26" s="44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K26" s="41"/>
@@ -6662,7 +6735,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
         <v>6</v>
       </c>
@@ -6672,19 +6745,19 @@
       <c r="C27" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D27" s="72"/>
+      <c r="D27" s="71"/>
       <c r="F27" s="46">
         <v>0</v>
       </c>
-      <c r="G27" s="51"/>
-      <c r="H27" s="51">
+      <c r="G27" s="50"/>
+      <c r="H27" s="50">
         <v>0</v>
       </c>
       <c r="I27" s="17">
         <v>0.13200000000000001</v>
       </c>
       <c r="J27" s="44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K27" s="41"/>
@@ -6693,7 +6766,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
         <v>7</v>
       </c>
@@ -6703,22 +6776,22 @@
       <c r="C28" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D28" s="72"/>
+      <c r="D28" s="71"/>
       <c r="E28" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F28" s="46">
         <v>18542</v>
       </c>
-      <c r="G28" s="51"/>
-      <c r="H28" s="51">
+      <c r="G28" s="50"/>
+      <c r="H28" s="50">
         <v>0</v>
       </c>
       <c r="I28" s="17">
         <v>0.127</v>
       </c>
       <c r="J28" s="44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K28" s="41"/>
@@ -6727,7 +6800,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
         <v>8</v>
       </c>
@@ -6737,22 +6810,22 @@
       <c r="C29" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D29" s="72"/>
+      <c r="D29" s="71"/>
       <c r="E29" t="s">
         <v>19</v>
       </c>
       <c r="F29" s="46">
         <v>0</v>
       </c>
-      <c r="G29" s="51"/>
-      <c r="H29" s="51">
+      <c r="G29" s="50"/>
+      <c r="H29" s="50">
         <v>0</v>
       </c>
       <c r="I29" s="17">
         <v>0.127</v>
       </c>
       <c r="J29" s="44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K29" s="41"/>
@@ -6761,13 +6834,13 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>11</v>
       </c>
       <c r="B30" s="9"/>
       <c r="C30" s="10"/>
-      <c r="D30" s="70"/>
+      <c r="D30" s="69"/>
       <c r="E30" t="s">
         <v>20</v>
       </c>
@@ -6776,16 +6849,16 @@
         <v>203642</v>
       </c>
       <c r="G30" s="49"/>
-      <c r="H30" s="52">
+      <c r="H30" s="51">
         <f>SUM(H22:H29)</f>
         <v>0</v>
       </c>
       <c r="I30" s="15">
-        <f t="shared" ref="I30:J30" si="9">SUM(I22:I29)</f>
+        <f t="shared" ref="I30:J30" si="8">SUM(I22:I29)</f>
         <v>1</v>
       </c>
       <c r="J30" s="39">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K30" s="42"/>
@@ -6794,1189 +6867,1189 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="N31"/>
     </row>
-    <row r="32" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="189" t="s">
-        <v>113</v>
-      </c>
-      <c r="F32" s="190"/>
-      <c r="G32" s="190"/>
-      <c r="H32" s="190"/>
-      <c r="I32" s="190"/>
-      <c r="J32" s="190"/>
-      <c r="K32" s="191"/>
-      <c r="L32" s="153"/>
-      <c r="M32" s="154"/>
+      <c r="E32" s="188" t="s">
+        <v>111</v>
+      </c>
+      <c r="F32" s="189"/>
+      <c r="G32" s="189"/>
+      <c r="H32" s="189"/>
+      <c r="I32" s="189"/>
+      <c r="J32" s="189"/>
+      <c r="K32" s="190"/>
+      <c r="L32" s="152"/>
+      <c r="M32" s="153"/>
       <c r="N32"/>
     </row>
-    <row r="33" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
-      <c r="E33" s="192" t="s">
-        <v>114</v>
-      </c>
-      <c r="F33" s="190"/>
-      <c r="G33" s="190"/>
-      <c r="H33" s="190"/>
-      <c r="I33" s="190"/>
-      <c r="J33" s="190"/>
-      <c r="K33" s="191"/>
-      <c r="L33" s="155"/>
-      <c r="M33" s="156"/>
+      <c r="E33" s="191" t="s">
+        <v>112</v>
+      </c>
+      <c r="F33" s="189"/>
+      <c r="G33" s="189"/>
+      <c r="H33" s="189"/>
+      <c r="I33" s="189"/>
+      <c r="J33" s="189"/>
+      <c r="K33" s="190"/>
+      <c r="L33" s="154"/>
+      <c r="M33" s="155"/>
       <c r="N33"/>
     </row>
-    <row r="34" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
-      <c r="E34" s="153"/>
-      <c r="F34" s="157"/>
-      <c r="G34" s="157"/>
-      <c r="H34" s="157"/>
-      <c r="I34" s="158"/>
-      <c r="J34" s="158">
+      <c r="E34" s="152"/>
+      <c r="F34" s="156"/>
+      <c r="G34" s="156"/>
+      <c r="H34" s="156"/>
+      <c r="I34" s="157"/>
+      <c r="J34" s="157">
         <f>'detalle y gastos'!B7</f>
         <v>0</v>
       </c>
-      <c r="K34" s="156"/>
-      <c r="L34" s="155"/>
-      <c r="M34" s="156"/>
+      <c r="K34" s="155"/>
+      <c r="L34" s="154"/>
+      <c r="M34" s="155"/>
       <c r="N34"/>
     </row>
-    <row r="35" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
-      <c r="E35" s="155" t="s">
-        <v>115</v>
-      </c>
-      <c r="F35" s="158"/>
-      <c r="G35" s="158"/>
-      <c r="H35" s="158"/>
-      <c r="I35" s="158"/>
-      <c r="J35" s="158"/>
-      <c r="K35" s="156"/>
-      <c r="L35" s="155"/>
-      <c r="M35" s="156"/>
+      <c r="E35" s="154" t="s">
+        <v>113</v>
+      </c>
+      <c r="F35" s="157"/>
+      <c r="G35" s="157"/>
+      <c r="H35" s="157"/>
+      <c r="I35" s="157"/>
+      <c r="J35" s="157"/>
+      <c r="K35" s="155"/>
+      <c r="L35" s="154"/>
+      <c r="M35" s="155"/>
       <c r="N35"/>
     </row>
-    <row r="36" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
-      <c r="E36" s="159"/>
-      <c r="F36" s="160"/>
-      <c r="G36" s="160"/>
-      <c r="H36" s="160"/>
-      <c r="I36" s="160"/>
-      <c r="J36" s="160"/>
-      <c r="K36" s="161"/>
-      <c r="L36" s="155"/>
-      <c r="M36" s="156"/>
+      <c r="E36" s="158"/>
+      <c r="F36" s="159"/>
+      <c r="G36" s="159"/>
+      <c r="H36" s="159"/>
+      <c r="I36" s="159"/>
+      <c r="J36" s="159"/>
+      <c r="K36" s="160"/>
+      <c r="L36" s="154"/>
+      <c r="M36" s="155"/>
       <c r="N36"/>
     </row>
-    <row r="37" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="193" t="s">
-        <v>50</v>
-      </c>
-      <c r="F37" s="194"/>
-      <c r="G37" s="194"/>
-      <c r="H37" s="194"/>
-      <c r="I37" s="194"/>
-      <c r="J37" s="194"/>
-      <c r="K37" s="195"/>
-      <c r="L37" s="155"/>
-      <c r="M37" s="156"/>
+      <c r="E37" s="192" t="s">
+        <v>49</v>
+      </c>
+      <c r="F37" s="193"/>
+      <c r="G37" s="193"/>
+      <c r="H37" s="193"/>
+      <c r="I37" s="193"/>
+      <c r="J37" s="193"/>
+      <c r="K37" s="194"/>
+      <c r="L37" s="154"/>
+      <c r="M37" s="155"/>
       <c r="N37"/>
     </row>
-    <row r="38" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
-      <c r="E38" s="155"/>
-      <c r="F38" s="158"/>
-      <c r="G38" s="158"/>
-      <c r="H38" s="158"/>
-      <c r="I38" s="158"/>
-      <c r="J38" s="158"/>
-      <c r="K38" s="156"/>
-      <c r="L38" s="155"/>
-      <c r="M38" s="156"/>
+      <c r="E38" s="154"/>
+      <c r="F38" s="157"/>
+      <c r="G38" s="157"/>
+      <c r="H38" s="157"/>
+      <c r="I38" s="157"/>
+      <c r="J38" s="157"/>
+      <c r="K38" s="155"/>
+      <c r="L38" s="154"/>
+      <c r="M38" s="155"/>
       <c r="N38"/>
     </row>
-    <row r="39" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
-      <c r="E39" s="155" t="s">
-        <v>116</v>
-      </c>
-      <c r="F39" s="158"/>
-      <c r="G39" s="158" t="str">
+      <c r="E39" s="154" t="s">
+        <v>114</v>
+      </c>
+      <c r="F39" s="157"/>
+      <c r="G39" s="157" t="str">
         <f>C7</f>
         <v>Maceyle Gabriela</v>
       </c>
-      <c r="H39" s="158"/>
-      <c r="I39" s="158" t="s">
-        <v>117</v>
-      </c>
-      <c r="J39" s="162">
+      <c r="H39" s="157"/>
+      <c r="I39" s="157" t="s">
+        <v>115</v>
+      </c>
+      <c r="J39" s="161">
         <v>45674</v>
       </c>
-      <c r="K39" s="156"/>
-      <c r="L39" s="196" t="s">
-        <v>118</v>
-      </c>
-      <c r="M39" s="197"/>
+      <c r="K39" s="155"/>
+      <c r="L39" s="195" t="s">
+        <v>116</v>
+      </c>
+      <c r="M39" s="196"/>
       <c r="N39"/>
     </row>
-    <row r="40" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
-      <c r="E40" s="155" t="s">
-        <v>119</v>
-      </c>
-      <c r="F40" s="163">
+      <c r="E40" s="154" t="s">
+        <v>117</v>
+      </c>
+      <c r="F40" s="162">
         <v>3</v>
       </c>
-      <c r="G40" s="158"/>
-      <c r="H40" s="158"/>
-      <c r="I40" s="158"/>
-      <c r="J40" s="158"/>
-      <c r="K40" s="156"/>
-      <c r="L40" s="155"/>
-      <c r="M40" s="156"/>
+      <c r="G40" s="157"/>
+      <c r="H40" s="157"/>
+      <c r="I40" s="157"/>
+      <c r="J40" s="157"/>
+      <c r="K40" s="155"/>
+      <c r="L40" s="154"/>
+      <c r="M40" s="155"/>
       <c r="N40"/>
     </row>
-    <row r="41" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
-      <c r="E41" s="155"/>
-      <c r="F41" s="158"/>
-      <c r="G41" s="158"/>
-      <c r="H41" s="158"/>
-      <c r="I41" s="158"/>
-      <c r="J41" s="158"/>
-      <c r="K41" s="156"/>
-      <c r="L41" s="198"/>
-      <c r="M41" s="197"/>
+      <c r="E41" s="154"/>
+      <c r="F41" s="157"/>
+      <c r="G41" s="157"/>
+      <c r="H41" s="157"/>
+      <c r="I41" s="157"/>
+      <c r="J41" s="157"/>
+      <c r="K41" s="155"/>
+      <c r="L41" s="197"/>
+      <c r="M41" s="196"/>
       <c r="N41"/>
     </row>
-    <row r="42" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
-      <c r="E42" s="155" t="s">
-        <v>49</v>
-      </c>
-      <c r="F42" s="158"/>
-      <c r="G42" s="158"/>
-      <c r="H42" s="158"/>
-      <c r="I42" s="158"/>
-      <c r="J42" s="164">
+      <c r="E42" s="154" t="s">
+        <v>48</v>
+      </c>
+      <c r="F42" s="157"/>
+      <c r="G42" s="157"/>
+      <c r="H42" s="157"/>
+      <c r="I42" s="157"/>
+      <c r="J42" s="163">
         <f>J7</f>
-        <v>45246.684546000004</v>
-      </c>
-      <c r="K42" s="156"/>
-      <c r="L42" s="155"/>
-      <c r="M42" s="156"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="155"/>
+      <c r="L42" s="154"/>
+      <c r="M42" s="155"/>
       <c r="N42"/>
     </row>
-    <row r="43" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
-      <c r="E43" s="165" t="s">
-        <v>120</v>
-      </c>
-      <c r="F43" s="158"/>
-      <c r="G43" s="158"/>
-      <c r="H43" s="158"/>
-      <c r="I43" s="158"/>
-      <c r="J43" s="164">
+      <c r="E43" s="164" t="s">
+        <v>118</v>
+      </c>
+      <c r="F43" s="157"/>
+      <c r="G43" s="157"/>
+      <c r="H43" s="157"/>
+      <c r="I43" s="157"/>
+      <c r="J43" s="163">
         <f>K7</f>
         <v>99680</v>
       </c>
-      <c r="K43" s="156"/>
-      <c r="L43" s="155"/>
-      <c r="M43" s="156"/>
+      <c r="K43" s="155"/>
+      <c r="L43" s="154"/>
+      <c r="M43" s="155"/>
       <c r="N43"/>
     </row>
-    <row r="44" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
-      <c r="E44" s="165" t="s">
-        <v>122</v>
-      </c>
-      <c r="F44" s="158"/>
-      <c r="G44" s="158"/>
-      <c r="H44" s="158"/>
-      <c r="I44" s="158"/>
-      <c r="J44" s="164">
+      <c r="E44" s="164" t="s">
+        <v>120</v>
+      </c>
+      <c r="F44" s="157"/>
+      <c r="G44" s="157"/>
+      <c r="H44" s="157"/>
+      <c r="I44" s="157"/>
+      <c r="J44" s="163">
         <f>G7+H7</f>
         <v>0</v>
       </c>
-      <c r="K44" s="156"/>
-      <c r="L44" s="155"/>
-      <c r="M44" s="156"/>
+      <c r="K44" s="155"/>
+      <c r="L44" s="154"/>
+      <c r="M44" s="155"/>
       <c r="N44"/>
     </row>
-    <row r="45" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
-      <c r="E45" s="165"/>
-      <c r="F45" s="158"/>
-      <c r="G45" s="158"/>
-      <c r="H45" s="158"/>
-      <c r="I45" s="158"/>
-      <c r="J45" s="164"/>
-      <c r="K45" s="156"/>
-      <c r="L45" s="155"/>
-      <c r="M45" s="156"/>
+      <c r="E45" s="164"/>
+      <c r="F45" s="157"/>
+      <c r="G45" s="157"/>
+      <c r="H45" s="157"/>
+      <c r="I45" s="157"/>
+      <c r="J45" s="163"/>
+      <c r="K45" s="155"/>
+      <c r="L45" s="154"/>
+      <c r="M45" s="155"/>
       <c r="N45"/>
     </row>
-    <row r="46" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
-      <c r="E46" s="165"/>
-      <c r="F46" s="158"/>
-      <c r="G46" s="158"/>
-      <c r="H46" s="158"/>
-      <c r="I46" s="158"/>
-      <c r="J46" s="164"/>
-      <c r="K46" s="156"/>
-      <c r="L46" s="155"/>
-      <c r="M46" s="156"/>
+      <c r="E46" s="164"/>
+      <c r="F46" s="157"/>
+      <c r="G46" s="157"/>
+      <c r="H46" s="157"/>
+      <c r="I46" s="157"/>
+      <c r="J46" s="163"/>
+      <c r="K46" s="155"/>
+      <c r="L46" s="154"/>
+      <c r="M46" s="155"/>
       <c r="N46"/>
     </row>
-    <row r="47" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
-      <c r="F47" s="158"/>
-      <c r="G47" s="158"/>
-      <c r="H47" s="158"/>
-      <c r="I47" s="158"/>
-      <c r="J47" s="164"/>
-      <c r="K47" s="156"/>
-      <c r="L47" s="155"/>
-      <c r="M47" s="156"/>
+      <c r="F47" s="157"/>
+      <c r="G47" s="157"/>
+      <c r="H47" s="157"/>
+      <c r="I47" s="157"/>
+      <c r="J47" s="163"/>
+      <c r="K47" s="155"/>
+      <c r="L47" s="154"/>
+      <c r="M47" s="155"/>
       <c r="N47"/>
     </row>
-    <row r="48" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
-      <c r="E48" s="165"/>
-      <c r="F48" s="158"/>
-      <c r="G48" s="158"/>
-      <c r="H48" s="158"/>
-      <c r="I48" s="158"/>
-      <c r="J48" s="164"/>
-      <c r="K48" s="156"/>
-      <c r="L48" s="155"/>
-      <c r="M48" s="156"/>
+      <c r="E48" s="164"/>
+      <c r="F48" s="157"/>
+      <c r="G48" s="157"/>
+      <c r="H48" s="157"/>
+      <c r="I48" s="157"/>
+      <c r="J48" s="163"/>
+      <c r="K48" s="155"/>
+      <c r="L48" s="154"/>
+      <c r="M48" s="155"/>
       <c r="N48"/>
     </row>
-    <row r="49" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
-      <c r="E49" s="155"/>
-      <c r="F49" s="158"/>
-      <c r="G49" s="158"/>
-      <c r="H49" s="158"/>
-      <c r="I49" s="158"/>
-      <c r="J49" s="158"/>
-      <c r="K49" s="156"/>
-      <c r="L49" s="155"/>
-      <c r="M49" s="156"/>
+      <c r="E49" s="154"/>
+      <c r="F49" s="157"/>
+      <c r="G49" s="157"/>
+      <c r="H49" s="157"/>
+      <c r="I49" s="157"/>
+      <c r="J49" s="157"/>
+      <c r="K49" s="155"/>
+      <c r="L49" s="154"/>
+      <c r="M49" s="155"/>
       <c r="N49"/>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
-      <c r="E50" s="155" t="s">
-        <v>123</v>
-      </c>
-      <c r="F50" s="158"/>
-      <c r="G50" s="158"/>
-      <c r="H50" s="158"/>
-      <c r="I50" s="158"/>
-      <c r="J50" s="158">
+      <c r="E50" s="154" t="s">
+        <v>121</v>
+      </c>
+      <c r="F50" s="157"/>
+      <c r="G50" s="157"/>
+      <c r="H50" s="157"/>
+      <c r="I50" s="157"/>
+      <c r="J50" s="157">
         <f>77200-77124.2</f>
         <v>75.80000000000291</v>
       </c>
-      <c r="K50" s="156"/>
-      <c r="L50" s="155"/>
-      <c r="M50" s="156"/>
+      <c r="K50" s="155"/>
+      <c r="L50" s="154"/>
+      <c r="M50" s="155"/>
       <c r="N50"/>
     </row>
-    <row r="51" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
-      <c r="E51" s="155"/>
-      <c r="F51" s="158"/>
-      <c r="G51" s="158"/>
-      <c r="H51" s="158"/>
-      <c r="I51" s="158"/>
-      <c r="J51" s="158"/>
-      <c r="K51" s="156"/>
-      <c r="L51" s="166"/>
-      <c r="M51" s="167"/>
+      <c r="E51" s="154"/>
+      <c r="F51" s="157"/>
+      <c r="G51" s="157"/>
+      <c r="H51" s="157"/>
+      <c r="I51" s="157"/>
+      <c r="J51" s="157"/>
+      <c r="K51" s="155"/>
+      <c r="L51" s="165"/>
+      <c r="M51" s="166"/>
       <c r="N51"/>
     </row>
-    <row r="52" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
-      <c r="E52" s="199" t="s">
-        <v>121</v>
-      </c>
-      <c r="F52" s="200"/>
-      <c r="G52" s="200"/>
-      <c r="H52" s="200"/>
-      <c r="I52" s="200"/>
-      <c r="J52" s="201">
+      <c r="E52" s="198" t="s">
+        <v>119</v>
+      </c>
+      <c r="F52" s="199"/>
+      <c r="G52" s="199"/>
+      <c r="H52" s="199"/>
+      <c r="I52" s="199"/>
+      <c r="J52" s="200">
         <f>SUM(J42:J51)</f>
-        <v>145002.48454600002</v>
-      </c>
-      <c r="K52" s="191"/>
-      <c r="L52" s="168"/>
-      <c r="M52" s="169"/>
+        <v>99755.8</v>
+      </c>
+      <c r="K52" s="190"/>
+      <c r="L52" s="167"/>
+      <c r="M52" s="168"/>
       <c r="N52"/>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="N53"/>
     </row>
-    <row r="55" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="56" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E56" s="189" t="s">
+    <row r="55" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="56" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E56" s="188" t="s">
+        <v>111</v>
+      </c>
+      <c r="F56" s="189"/>
+      <c r="G56" s="189"/>
+      <c r="H56" s="189"/>
+      <c r="I56" s="189"/>
+      <c r="J56" s="189"/>
+      <c r="K56" s="190"/>
+      <c r="L56" s="152"/>
+      <c r="M56" s="153"/>
+    </row>
+    <row r="57" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E57" s="191" t="s">
+        <v>112</v>
+      </c>
+      <c r="F57" s="189"/>
+      <c r="G57" s="189"/>
+      <c r="H57" s="189"/>
+      <c r="I57" s="189"/>
+      <c r="J57" s="189"/>
+      <c r="K57" s="190"/>
+      <c r="L57" s="154"/>
+      <c r="M57" s="155"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="E58" s="152"/>
+      <c r="F58" s="156"/>
+      <c r="G58" s="156"/>
+      <c r="H58" s="156"/>
+      <c r="I58" s="157"/>
+      <c r="J58" s="157">
+        <f>J34</f>
+        <v>0</v>
+      </c>
+      <c r="K58" s="155"/>
+      <c r="L58" s="154"/>
+      <c r="M58" s="155"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="E59" s="154" t="s">
         <v>113</v>
       </c>
-      <c r="F56" s="190"/>
-      <c r="G56" s="190"/>
-      <c r="H56" s="190"/>
-      <c r="I56" s="190"/>
-      <c r="J56" s="190"/>
-      <c r="K56" s="191"/>
-      <c r="L56" s="153"/>
-      <c r="M56" s="154"/>
-    </row>
-    <row r="57" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E57" s="192" t="s">
+      <c r="F59" s="157"/>
+      <c r="G59" s="157"/>
+      <c r="H59" s="157"/>
+      <c r="I59" s="157"/>
+      <c r="J59" s="157"/>
+      <c r="K59" s="155"/>
+      <c r="L59" s="154"/>
+      <c r="M59" s="155"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="E60" s="158"/>
+      <c r="F60" s="159"/>
+      <c r="G60" s="159"/>
+      <c r="H60" s="159"/>
+      <c r="I60" s="159"/>
+      <c r="J60" s="159"/>
+      <c r="K60" s="160"/>
+      <c r="L60" s="154"/>
+      <c r="M60" s="155"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="E61" s="192" t="s">
+        <v>49</v>
+      </c>
+      <c r="F61" s="193"/>
+      <c r="G61" s="193"/>
+      <c r="H61" s="193"/>
+      <c r="I61" s="193"/>
+      <c r="J61" s="193"/>
+      <c r="K61" s="194"/>
+      <c r="L61" s="154"/>
+      <c r="M61" s="155"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="E62" s="154"/>
+      <c r="F62" s="157"/>
+      <c r="G62" s="157"/>
+      <c r="H62" s="157"/>
+      <c r="I62" s="157"/>
+      <c r="J62" s="157"/>
+      <c r="K62" s="155"/>
+      <c r="L62" s="154"/>
+      <c r="M62" s="155"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="E63" s="154" t="s">
         <v>114</v>
       </c>
-      <c r="F57" s="190"/>
-      <c r="G57" s="190"/>
-      <c r="H57" s="190"/>
-      <c r="I57" s="190"/>
-      <c r="J57" s="190"/>
-      <c r="K57" s="191"/>
-      <c r="L57" s="155"/>
-      <c r="M57" s="156"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="E58" s="153"/>
-      <c r="F58" s="157"/>
-      <c r="G58" s="157"/>
-      <c r="H58" s="157"/>
-      <c r="I58" s="158"/>
-      <c r="J58" s="158">
-        <f>J34</f>
-        <v>0</v>
-      </c>
-      <c r="K58" s="156"/>
-      <c r="L58" s="155"/>
-      <c r="M58" s="156"/>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="E59" s="155" t="s">
-        <v>115</v>
-      </c>
-      <c r="F59" s="158"/>
-      <c r="G59" s="158"/>
-      <c r="H59" s="158"/>
-      <c r="I59" s="158"/>
-      <c r="J59" s="158"/>
-      <c r="K59" s="156"/>
-      <c r="L59" s="155"/>
-      <c r="M59" s="156"/>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="E60" s="159"/>
-      <c r="F60" s="160"/>
-      <c r="G60" s="160"/>
-      <c r="H60" s="160"/>
-      <c r="I60" s="160"/>
-      <c r="J60" s="160"/>
-      <c r="K60" s="161"/>
-      <c r="L60" s="155"/>
-      <c r="M60" s="156"/>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="E61" s="193" t="s">
-        <v>50</v>
-      </c>
-      <c r="F61" s="194"/>
-      <c r="G61" s="194"/>
-      <c r="H61" s="194"/>
-      <c r="I61" s="194"/>
-      <c r="J61" s="194"/>
-      <c r="K61" s="195"/>
-      <c r="L61" s="155"/>
-      <c r="M61" s="156"/>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="E62" s="155"/>
-      <c r="F62" s="158"/>
-      <c r="G62" s="158"/>
-      <c r="H62" s="158"/>
-      <c r="I62" s="158"/>
-      <c r="J62" s="158"/>
-      <c r="K62" s="156"/>
-      <c r="L62" s="155"/>
-      <c r="M62" s="156"/>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="E63" s="155" t="s">
-        <v>116</v>
-      </c>
-      <c r="F63" s="158"/>
-      <c r="G63" s="163" t="str">
+      <c r="F63" s="157"/>
+      <c r="G63" s="162" t="str">
         <f>C8</f>
         <v>Castelao Lorena</v>
       </c>
-      <c r="H63" s="158"/>
-      <c r="I63" s="158" t="s">
+      <c r="H63" s="157"/>
+      <c r="I63" s="157" t="s">
+        <v>115</v>
+      </c>
+      <c r="J63" s="161">
+        <v>45674</v>
+      </c>
+      <c r="K63" s="155"/>
+      <c r="L63" s="195" t="s">
+        <v>116</v>
+      </c>
+      <c r="M63" s="196"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="E64" s="154" t="s">
         <v>117</v>
       </c>
-      <c r="J63" s="162">
-        <v>45674</v>
-      </c>
-      <c r="K63" s="156"/>
-      <c r="L63" s="196" t="s">
+      <c r="F64" s="162">
+        <v>4</v>
+      </c>
+      <c r="G64" s="157"/>
+      <c r="H64" s="157"/>
+      <c r="I64" s="157"/>
+      <c r="J64" s="157"/>
+      <c r="K64" s="155"/>
+      <c r="L64" s="154"/>
+      <c r="M64" s="155"/>
+    </row>
+    <row r="65" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E65" s="154"/>
+      <c r="F65" s="157"/>
+      <c r="G65" s="157"/>
+      <c r="H65" s="157"/>
+      <c r="I65" s="157"/>
+      <c r="J65" s="157"/>
+      <c r="K65" s="155"/>
+      <c r="L65" s="197"/>
+      <c r="M65" s="196"/>
+    </row>
+    <row r="66" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E66" s="154" t="s">
+        <v>48</v>
+      </c>
+      <c r="F66" s="157"/>
+      <c r="G66" s="157"/>
+      <c r="H66" s="157"/>
+      <c r="I66" s="157"/>
+      <c r="J66" s="163">
+        <f>J8</f>
+        <v>0</v>
+      </c>
+      <c r="K66" s="155"/>
+      <c r="L66" s="154"/>
+      <c r="M66" s="155"/>
+    </row>
+    <row r="67" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E67" s="164" t="s">
         <v>118</v>
       </c>
-      <c r="M63" s="197"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="E64" s="155" t="s">
-        <v>119</v>
-      </c>
-      <c r="F64" s="163">
-        <v>4</v>
-      </c>
-      <c r="G64" s="158"/>
-      <c r="H64" s="158"/>
-      <c r="I64" s="158"/>
-      <c r="J64" s="158"/>
-      <c r="K64" s="156"/>
-      <c r="L64" s="155"/>
-      <c r="M64" s="156"/>
-    </row>
-    <row r="65" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E65" s="155"/>
-      <c r="F65" s="158"/>
-      <c r="G65" s="158"/>
-      <c r="H65" s="158"/>
-      <c r="I65" s="158"/>
-      <c r="J65" s="158"/>
-      <c r="K65" s="156"/>
-      <c r="L65" s="198"/>
-      <c r="M65" s="197"/>
-    </row>
-    <row r="66" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E66" s="155" t="s">
-        <v>49</v>
-      </c>
-      <c r="F66" s="158"/>
-      <c r="G66" s="158"/>
-      <c r="H66" s="158"/>
-      <c r="I66" s="158"/>
-      <c r="J66" s="164">
-        <f>J8</f>
-        <v>53562.487724999999</v>
-      </c>
-      <c r="K66" s="156"/>
-      <c r="L66" s="155"/>
-      <c r="M66" s="156"/>
-    </row>
-    <row r="67" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E67" s="165" t="s">
-        <v>120</v>
-      </c>
-      <c r="F67" s="158"/>
-      <c r="G67" s="158"/>
-      <c r="H67" s="158"/>
-      <c r="I67" s="158"/>
-      <c r="J67" s="164">
+      <c r="F67" s="157"/>
+      <c r="G67" s="157"/>
+      <c r="H67" s="157"/>
+      <c r="I67" s="157"/>
+      <c r="J67" s="163">
         <f>K8</f>
         <v>118000</v>
       </c>
-      <c r="K67" s="156"/>
-      <c r="L67" s="155"/>
-      <c r="M67" s="156"/>
-    </row>
-    <row r="68" spans="5:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E68" s="165" t="s">
-        <v>122</v>
-      </c>
-      <c r="F68" s="158"/>
-      <c r="G68" s="158"/>
-      <c r="H68" s="158"/>
-      <c r="I68" s="158"/>
-      <c r="J68" s="164">
+      <c r="K67" s="155"/>
+      <c r="L67" s="154"/>
+      <c r="M67" s="155"/>
+    </row>
+    <row r="68" spans="5:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E68" s="164" t="s">
+        <v>120</v>
+      </c>
+      <c r="F68" s="157"/>
+      <c r="G68" s="157"/>
+      <c r="H68" s="157"/>
+      <c r="I68" s="157"/>
+      <c r="J68" s="163">
         <f>G29+H29</f>
         <v>0</v>
       </c>
-      <c r="K68" s="156"/>
-      <c r="L68" s="155"/>
-      <c r="M68" s="156"/>
-    </row>
-    <row r="69" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="E69" s="165"/>
-      <c r="F69" s="158"/>
-      <c r="G69" s="158"/>
-      <c r="H69" s="158"/>
-      <c r="I69" s="158"/>
-      <c r="J69" s="164"/>
-      <c r="K69" s="156"/>
-      <c r="L69" s="155"/>
-      <c r="M69" s="156"/>
-    </row>
-    <row r="70" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="E70" s="165"/>
-      <c r="F70" s="158"/>
-      <c r="G70" s="158"/>
-      <c r="H70" s="158"/>
-      <c r="I70" s="158"/>
-      <c r="J70" s="164"/>
-      <c r="K70" s="156"/>
-      <c r="L70" s="155"/>
-      <c r="M70" s="156"/>
-    </row>
-    <row r="71" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="F71" s="158"/>
-      <c r="G71" s="158"/>
-      <c r="H71" s="158"/>
-      <c r="I71" s="158"/>
-      <c r="J71" s="164"/>
-      <c r="K71" s="156"/>
-      <c r="L71" s="155"/>
-      <c r="M71" s="156"/>
-    </row>
-    <row r="72" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="E72" s="165"/>
-      <c r="F72" s="158"/>
-      <c r="G72" s="158"/>
-      <c r="H72" s="158"/>
-      <c r="I72" s="158"/>
-      <c r="J72" s="164"/>
-      <c r="K72" s="156"/>
-      <c r="L72" s="155"/>
-      <c r="M72" s="156"/>
-    </row>
-    <row r="73" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="E73" s="155"/>
-      <c r="F73" s="158"/>
-      <c r="G73" s="158"/>
-      <c r="H73" s="158"/>
-      <c r="I73" s="158"/>
-      <c r="J73" s="158"/>
-      <c r="K73" s="156"/>
-      <c r="L73" s="155"/>
-      <c r="M73" s="156"/>
-    </row>
-    <row r="74" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="E74" s="155"/>
-      <c r="F74" s="158"/>
-      <c r="G74" s="158"/>
-      <c r="H74" s="158"/>
-      <c r="I74" s="158"/>
-      <c r="J74" s="158"/>
-      <c r="K74" s="156"/>
-      <c r="L74" s="155"/>
-      <c r="M74" s="156"/>
-    </row>
-    <row r="75" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E75" s="155"/>
-      <c r="F75" s="158"/>
-      <c r="G75" s="158"/>
-      <c r="H75" s="158"/>
-      <c r="I75" s="158"/>
-      <c r="J75" s="158"/>
-      <c r="K75" s="156"/>
-      <c r="L75" s="166"/>
-      <c r="M75" s="167"/>
-    </row>
-    <row r="76" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E76" s="199" t="s">
-        <v>121</v>
-      </c>
-      <c r="F76" s="200"/>
-      <c r="G76" s="200"/>
-      <c r="H76" s="200"/>
-      <c r="I76" s="200"/>
-      <c r="J76" s="201">
+      <c r="K68" s="155"/>
+      <c r="L68" s="154"/>
+      <c r="M68" s="155"/>
+    </row>
+    <row r="69" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E69" s="164"/>
+      <c r="F69" s="157"/>
+      <c r="G69" s="157"/>
+      <c r="H69" s="157"/>
+      <c r="I69" s="157"/>
+      <c r="J69" s="163"/>
+      <c r="K69" s="155"/>
+      <c r="L69" s="154"/>
+      <c r="M69" s="155"/>
+    </row>
+    <row r="70" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E70" s="164"/>
+      <c r="F70" s="157"/>
+      <c r="G70" s="157"/>
+      <c r="H70" s="157"/>
+      <c r="I70" s="157"/>
+      <c r="J70" s="163"/>
+      <c r="K70" s="155"/>
+      <c r="L70" s="154"/>
+      <c r="M70" s="155"/>
+    </row>
+    <row r="71" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F71" s="157"/>
+      <c r="G71" s="157"/>
+      <c r="H71" s="157"/>
+      <c r="I71" s="157"/>
+      <c r="J71" s="163"/>
+      <c r="K71" s="155"/>
+      <c r="L71" s="154"/>
+      <c r="M71" s="155"/>
+    </row>
+    <row r="72" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E72" s="164"/>
+      <c r="F72" s="157"/>
+      <c r="G72" s="157"/>
+      <c r="H72" s="157"/>
+      <c r="I72" s="157"/>
+      <c r="J72" s="163"/>
+      <c r="K72" s="155"/>
+      <c r="L72" s="154"/>
+      <c r="M72" s="155"/>
+    </row>
+    <row r="73" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E73" s="154"/>
+      <c r="F73" s="157"/>
+      <c r="G73" s="157"/>
+      <c r="H73" s="157"/>
+      <c r="I73" s="157"/>
+      <c r="J73" s="157"/>
+      <c r="K73" s="155"/>
+      <c r="L73" s="154"/>
+      <c r="M73" s="155"/>
+    </row>
+    <row r="74" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E74" s="154"/>
+      <c r="F74" s="157"/>
+      <c r="G74" s="157"/>
+      <c r="H74" s="157"/>
+      <c r="I74" s="157"/>
+      <c r="J74" s="157"/>
+      <c r="K74" s="155"/>
+      <c r="L74" s="154"/>
+      <c r="M74" s="155"/>
+    </row>
+    <row r="75" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E75" s="154"/>
+      <c r="F75" s="157"/>
+      <c r="G75" s="157"/>
+      <c r="H75" s="157"/>
+      <c r="I75" s="157"/>
+      <c r="J75" s="157"/>
+      <c r="K75" s="155"/>
+      <c r="L75" s="165"/>
+      <c r="M75" s="166"/>
+    </row>
+    <row r="76" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E76" s="198" t="s">
+        <v>119</v>
+      </c>
+      <c r="F76" s="199"/>
+      <c r="G76" s="199"/>
+      <c r="H76" s="199"/>
+      <c r="I76" s="199"/>
+      <c r="J76" s="200">
         <f>SUM(J66:J75)</f>
-        <v>171562.48772500001</v>
-      </c>
-      <c r="K76" s="191"/>
-      <c r="L76" s="168"/>
-      <c r="M76" s="169"/>
-    </row>
-    <row r="82" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="83" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E83" s="189" t="s">
+        <v>118000</v>
+      </c>
+      <c r="K76" s="190"/>
+      <c r="L76" s="167"/>
+      <c r="M76" s="168"/>
+    </row>
+    <row r="82" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="83" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E83" s="188" t="s">
+        <v>111</v>
+      </c>
+      <c r="F83" s="189"/>
+      <c r="G83" s="189"/>
+      <c r="H83" s="189"/>
+      <c r="I83" s="189"/>
+      <c r="J83" s="189"/>
+      <c r="K83" s="190"/>
+      <c r="L83" s="152"/>
+      <c r="M83" s="153"/>
+    </row>
+    <row r="84" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E84" s="191" t="s">
+        <v>112</v>
+      </c>
+      <c r="F84" s="189"/>
+      <c r="G84" s="189"/>
+      <c r="H84" s="189"/>
+      <c r="I84" s="189"/>
+      <c r="J84" s="189"/>
+      <c r="K84" s="190"/>
+      <c r="L84" s="154"/>
+      <c r="M84" s="155"/>
+    </row>
+    <row r="85" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E85" s="152"/>
+      <c r="F85" s="156"/>
+      <c r="G85" s="156"/>
+      <c r="H85" s="156"/>
+      <c r="I85" s="157"/>
+      <c r="J85" s="157">
+        <f>'detalle y gastos'!B7</f>
+        <v>0</v>
+      </c>
+      <c r="K85" s="155"/>
+      <c r="L85" s="154"/>
+      <c r="M85" s="155"/>
+    </row>
+    <row r="86" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E86" s="154" t="s">
         <v>113</v>
       </c>
-      <c r="F83" s="190"/>
-      <c r="G83" s="190"/>
-      <c r="H83" s="190"/>
-      <c r="I83" s="190"/>
-      <c r="J83" s="190"/>
-      <c r="K83" s="191"/>
-      <c r="L83" s="153"/>
-      <c r="M83" s="154"/>
-    </row>
-    <row r="84" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E84" s="192" t="s">
+      <c r="F86" s="157"/>
+      <c r="G86" s="157"/>
+      <c r="H86" s="157"/>
+      <c r="I86" s="157"/>
+      <c r="J86" s="157"/>
+      <c r="K86" s="155"/>
+      <c r="L86" s="154"/>
+      <c r="M86" s="155"/>
+    </row>
+    <row r="87" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E87" s="158"/>
+      <c r="F87" s="159"/>
+      <c r="G87" s="159"/>
+      <c r="H87" s="159"/>
+      <c r="I87" s="159"/>
+      <c r="J87" s="159"/>
+      <c r="K87" s="160"/>
+      <c r="L87" s="154"/>
+      <c r="M87" s="155"/>
+    </row>
+    <row r="88" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E88" s="192" t="s">
+        <v>49</v>
+      </c>
+      <c r="F88" s="193"/>
+      <c r="G88" s="193"/>
+      <c r="H88" s="193"/>
+      <c r="I88" s="193"/>
+      <c r="J88" s="193"/>
+      <c r="K88" s="194"/>
+      <c r="L88" s="154"/>
+      <c r="M88" s="155"/>
+    </row>
+    <row r="89" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E89" s="154"/>
+      <c r="F89" s="157"/>
+      <c r="G89" s="157"/>
+      <c r="H89" s="157"/>
+      <c r="I89" s="157"/>
+      <c r="J89" s="157"/>
+      <c r="K89" s="155"/>
+      <c r="L89" s="154"/>
+      <c r="M89" s="155"/>
+    </row>
+    <row r="90" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E90" s="154" t="s">
         <v>114</v>
       </c>
-      <c r="F84" s="190"/>
-      <c r="G84" s="190"/>
-      <c r="H84" s="190"/>
-      <c r="I84" s="190"/>
-      <c r="J84" s="190"/>
-      <c r="K84" s="191"/>
-      <c r="L84" s="155"/>
-      <c r="M84" s="156"/>
-    </row>
-    <row r="85" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E85" s="153"/>
-      <c r="F85" s="157"/>
-      <c r="G85" s="157"/>
-      <c r="H85" s="157"/>
-      <c r="I85" s="158"/>
-      <c r="J85" s="158">
-        <f>'detalle y gastos'!B7</f>
-        <v>0</v>
-      </c>
-      <c r="K85" s="156"/>
-      <c r="L85" s="155"/>
-      <c r="M85" s="156"/>
-    </row>
-    <row r="86" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E86" s="155" t="s">
-        <v>115</v>
-      </c>
-      <c r="F86" s="158"/>
-      <c r="G86" s="158"/>
-      <c r="H86" s="158"/>
-      <c r="I86" s="158"/>
-      <c r="J86" s="158"/>
-      <c r="K86" s="156"/>
-      <c r="L86" s="155"/>
-      <c r="M86" s="156"/>
-    </row>
-    <row r="87" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E87" s="159"/>
-      <c r="F87" s="160"/>
-      <c r="G87" s="160"/>
-      <c r="H87" s="160"/>
-      <c r="I87" s="160"/>
-      <c r="J87" s="160"/>
-      <c r="K87" s="161"/>
-      <c r="L87" s="155"/>
-      <c r="M87" s="156"/>
-    </row>
-    <row r="88" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E88" s="193" t="s">
-        <v>50</v>
-      </c>
-      <c r="F88" s="194"/>
-      <c r="G88" s="194"/>
-      <c r="H88" s="194"/>
-      <c r="I88" s="194"/>
-      <c r="J88" s="194"/>
-      <c r="K88" s="195"/>
-      <c r="L88" s="155"/>
-      <c r="M88" s="156"/>
-    </row>
-    <row r="89" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E89" s="155"/>
-      <c r="F89" s="158"/>
-      <c r="G89" s="158"/>
-      <c r="H89" s="158"/>
-      <c r="I89" s="158"/>
-      <c r="J89" s="158"/>
-      <c r="K89" s="156"/>
-      <c r="L89" s="155"/>
-      <c r="M89" s="156"/>
-    </row>
-    <row r="90" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E90" s="155" t="s">
-        <v>116</v>
-      </c>
-      <c r="F90" s="158"/>
-      <c r="G90" s="163" t="str">
+      <c r="F90" s="157"/>
+      <c r="G90" s="162" t="str">
         <f>C10</f>
         <v>Valdez Norberto</v>
       </c>
-      <c r="H90" s="158"/>
-      <c r="I90" s="158" t="s">
+      <c r="H90" s="157"/>
+      <c r="I90" s="157" t="s">
+        <v>115</v>
+      </c>
+      <c r="J90" s="161">
+        <v>45674</v>
+      </c>
+      <c r="K90" s="155"/>
+      <c r="L90" s="195" t="s">
+        <v>116</v>
+      </c>
+      <c r="M90" s="196"/>
+    </row>
+    <row r="91" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E91" s="154" t="s">
         <v>117</v>
       </c>
-      <c r="J90" s="162">
-        <v>45674</v>
-      </c>
-      <c r="K90" s="156"/>
-      <c r="L90" s="196" t="s">
+      <c r="F91" s="162">
+        <v>6</v>
+      </c>
+      <c r="G91" s="157"/>
+      <c r="H91" s="157"/>
+      <c r="I91" s="157"/>
+      <c r="J91" s="157"/>
+      <c r="K91" s="155"/>
+      <c r="L91" s="154"/>
+      <c r="M91" s="155"/>
+    </row>
+    <row r="92" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E92" s="154"/>
+      <c r="F92" s="157"/>
+      <c r="G92" s="157"/>
+      <c r="H92" s="157"/>
+      <c r="I92" s="157"/>
+      <c r="J92" s="157"/>
+      <c r="K92" s="155"/>
+      <c r="L92" s="197"/>
+      <c r="M92" s="196"/>
+    </row>
+    <row r="93" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E93" s="154" t="s">
+        <v>48</v>
+      </c>
+      <c r="F93" s="157"/>
+      <c r="G93" s="157"/>
+      <c r="H93" s="157"/>
+      <c r="I93" s="157"/>
+      <c r="J93" s="163">
+        <f>J10</f>
+        <v>0</v>
+      </c>
+      <c r="K93" s="155"/>
+      <c r="L93" s="154"/>
+      <c r="M93" s="155"/>
+    </row>
+    <row r="94" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E94" s="164" t="s">
         <v>118</v>
       </c>
-      <c r="M90" s="197"/>
-    </row>
-    <row r="91" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E91" s="155" t="s">
-        <v>119</v>
-      </c>
-      <c r="F91" s="163">
-        <v>6</v>
-      </c>
-      <c r="G91" s="158"/>
-      <c r="H91" s="158"/>
-      <c r="I91" s="158"/>
-      <c r="J91" s="158"/>
-      <c r="K91" s="156"/>
-      <c r="L91" s="155"/>
-      <c r="M91" s="156"/>
-    </row>
-    <row r="92" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E92" s="155"/>
-      <c r="F92" s="158"/>
-      <c r="G92" s="158"/>
-      <c r="H92" s="158"/>
-      <c r="I92" s="158"/>
-      <c r="J92" s="158"/>
-      <c r="K92" s="156"/>
-      <c r="L92" s="198"/>
-      <c r="M92" s="197"/>
-    </row>
-    <row r="93" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E93" s="155" t="s">
-        <v>49</v>
-      </c>
-      <c r="F93" s="158"/>
-      <c r="G93" s="158"/>
-      <c r="H93" s="158"/>
-      <c r="I93" s="158"/>
-      <c r="J93" s="164">
-        <f>J10</f>
-        <v>45319.311648000003</v>
-      </c>
-      <c r="K93" s="156"/>
-      <c r="L93" s="155"/>
-      <c r="M93" s="156"/>
-    </row>
-    <row r="94" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E94" s="165" t="s">
-        <v>120</v>
-      </c>
-      <c r="F94" s="158"/>
-      <c r="G94" s="158"/>
-      <c r="H94" s="158"/>
-      <c r="I94" s="158"/>
-      <c r="J94" s="164">
+      <c r="F94" s="157"/>
+      <c r="G94" s="157"/>
+      <c r="H94" s="157"/>
+      <c r="I94" s="157"/>
+      <c r="J94" s="163">
         <f>K10</f>
         <v>99840</v>
       </c>
-      <c r="K94" s="156"/>
-      <c r="L94" s="155"/>
-      <c r="M94" s="156"/>
-    </row>
-    <row r="95" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E95" s="165" t="s">
-        <v>123</v>
-      </c>
-      <c r="F95" s="158"/>
-      <c r="G95" s="158"/>
-      <c r="H95" s="158"/>
-      <c r="I95" s="158"/>
-      <c r="J95" s="164">
+      <c r="K94" s="155"/>
+      <c r="L94" s="154"/>
+      <c r="M94" s="155"/>
+    </row>
+    <row r="95" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E95" s="164" t="s">
+        <v>121</v>
+      </c>
+      <c r="F95" s="157"/>
+      <c r="G95" s="157"/>
+      <c r="H95" s="157"/>
+      <c r="I95" s="157"/>
+      <c r="J95" s="163">
         <v>23.89</v>
       </c>
-      <c r="K95" s="156"/>
-      <c r="L95" s="155"/>
-      <c r="M95" s="156"/>
-    </row>
-    <row r="96" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E96" s="165"/>
-      <c r="F96" s="158"/>
-      <c r="G96" s="158"/>
-      <c r="H96" s="158"/>
-      <c r="I96" s="158"/>
-      <c r="J96" s="164"/>
-      <c r="K96" s="156"/>
-      <c r="L96" s="155"/>
-      <c r="M96" s="156"/>
-    </row>
-    <row r="97" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E97" s="165"/>
-      <c r="F97" s="158"/>
-      <c r="G97" s="158"/>
-      <c r="H97" s="158"/>
-      <c r="I97" s="158"/>
-      <c r="J97" s="164"/>
-      <c r="K97" s="156"/>
-      <c r="L97" s="155"/>
-      <c r="M97" s="156"/>
-    </row>
-    <row r="98" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="F98" s="158"/>
-      <c r="G98" s="158"/>
-      <c r="H98" s="158"/>
-      <c r="I98" s="158"/>
-      <c r="J98" s="164"/>
-      <c r="K98" s="156"/>
-      <c r="L98" s="155"/>
-      <c r="M98" s="156"/>
-    </row>
-    <row r="99" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E99" s="165"/>
-      <c r="F99" s="158"/>
-      <c r="G99" s="158"/>
-      <c r="H99" s="158"/>
-      <c r="I99" s="158"/>
-      <c r="J99" s="164"/>
-      <c r="K99" s="156"/>
-      <c r="L99" s="155"/>
-      <c r="M99" s="156"/>
-    </row>
-    <row r="100" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E100" s="155"/>
-      <c r="F100" s="158"/>
-      <c r="G100" s="158"/>
-      <c r="H100" s="158"/>
-      <c r="I100" s="158"/>
-      <c r="J100" s="158"/>
-      <c r="K100" s="156"/>
-      <c r="L100" s="155"/>
-      <c r="M100" s="156"/>
-    </row>
-    <row r="101" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E101" s="155"/>
-      <c r="F101" s="158"/>
-      <c r="G101" s="158"/>
-      <c r="H101" s="158"/>
-      <c r="I101" s="158"/>
-      <c r="J101" s="158"/>
-      <c r="K101" s="156"/>
-      <c r="L101" s="155"/>
-      <c r="M101" s="156"/>
-    </row>
-    <row r="102" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E102" s="155"/>
-      <c r="F102" s="158"/>
-      <c r="G102" s="158"/>
-      <c r="H102" s="158"/>
-      <c r="I102" s="158"/>
-      <c r="J102" s="158"/>
-      <c r="K102" s="156"/>
-      <c r="L102" s="166"/>
-      <c r="M102" s="167"/>
-    </row>
-    <row r="103" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E103" s="199" t="s">
-        <v>121</v>
-      </c>
-      <c r="F103" s="200"/>
-      <c r="G103" s="200"/>
-      <c r="H103" s="200"/>
-      <c r="I103" s="200"/>
-      <c r="J103" s="201">
+      <c r="K95" s="155"/>
+      <c r="L95" s="154"/>
+      <c r="M95" s="155"/>
+    </row>
+    <row r="96" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E96" s="164"/>
+      <c r="F96" s="157"/>
+      <c r="G96" s="157"/>
+      <c r="H96" s="157"/>
+      <c r="I96" s="157"/>
+      <c r="J96" s="163"/>
+      <c r="K96" s="155"/>
+      <c r="L96" s="154"/>
+      <c r="M96" s="155"/>
+    </row>
+    <row r="97" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E97" s="164"/>
+      <c r="F97" s="157"/>
+      <c r="G97" s="157"/>
+      <c r="H97" s="157"/>
+      <c r="I97" s="157"/>
+      <c r="J97" s="163"/>
+      <c r="K97" s="155"/>
+      <c r="L97" s="154"/>
+      <c r="M97" s="155"/>
+    </row>
+    <row r="98" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F98" s="157"/>
+      <c r="G98" s="157"/>
+      <c r="H98" s="157"/>
+      <c r="I98" s="157"/>
+      <c r="J98" s="163"/>
+      <c r="K98" s="155"/>
+      <c r="L98" s="154"/>
+      <c r="M98" s="155"/>
+    </row>
+    <row r="99" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E99" s="164"/>
+      <c r="F99" s="157"/>
+      <c r="G99" s="157"/>
+      <c r="H99" s="157"/>
+      <c r="I99" s="157"/>
+      <c r="J99" s="163"/>
+      <c r="K99" s="155"/>
+      <c r="L99" s="154"/>
+      <c r="M99" s="155"/>
+    </row>
+    <row r="100" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E100" s="154"/>
+      <c r="F100" s="157"/>
+      <c r="G100" s="157"/>
+      <c r="H100" s="157"/>
+      <c r="I100" s="157"/>
+      <c r="J100" s="157"/>
+      <c r="K100" s="155"/>
+      <c r="L100" s="154"/>
+      <c r="M100" s="155"/>
+    </row>
+    <row r="101" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E101" s="154"/>
+      <c r="F101" s="157"/>
+      <c r="G101" s="157"/>
+      <c r="H101" s="157"/>
+      <c r="I101" s="157"/>
+      <c r="J101" s="157"/>
+      <c r="K101" s="155"/>
+      <c r="L101" s="154"/>
+      <c r="M101" s="155"/>
+    </row>
+    <row r="102" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E102" s="154"/>
+      <c r="F102" s="157"/>
+      <c r="G102" s="157"/>
+      <c r="H102" s="157"/>
+      <c r="I102" s="157"/>
+      <c r="J102" s="157"/>
+      <c r="K102" s="155"/>
+      <c r="L102" s="165"/>
+      <c r="M102" s="166"/>
+    </row>
+    <row r="103" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E103" s="198" t="s">
+        <v>119</v>
+      </c>
+      <c r="F103" s="199"/>
+      <c r="G103" s="199"/>
+      <c r="H103" s="199"/>
+      <c r="I103" s="199"/>
+      <c r="J103" s="200">
         <f>SUM(J93:J102)</f>
-        <v>145183.20164800002</v>
-      </c>
-      <c r="K103" s="191"/>
-      <c r="L103" s="168"/>
-      <c r="M103" s="169"/>
-    </row>
-    <row r="107" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="108" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E108" s="189" t="s">
+        <v>99863.89</v>
+      </c>
+      <c r="K103" s="190"/>
+      <c r="L103" s="167"/>
+      <c r="M103" s="168"/>
+    </row>
+    <row r="107" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="108" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E108" s="188" t="s">
+        <v>111</v>
+      </c>
+      <c r="F108" s="189"/>
+      <c r="G108" s="189"/>
+      <c r="H108" s="189"/>
+      <c r="I108" s="189"/>
+      <c r="J108" s="189"/>
+      <c r="K108" s="190"/>
+      <c r="L108" s="152"/>
+      <c r="M108" s="153"/>
+    </row>
+    <row r="109" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E109" s="191" t="s">
+        <v>112</v>
+      </c>
+      <c r="F109" s="189"/>
+      <c r="G109" s="189"/>
+      <c r="H109" s="189"/>
+      <c r="I109" s="189"/>
+      <c r="J109" s="189"/>
+      <c r="K109" s="190"/>
+      <c r="L109" s="154"/>
+      <c r="M109" s="155"/>
+    </row>
+    <row r="110" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E110" s="152"/>
+      <c r="F110" s="156"/>
+      <c r="G110" s="156"/>
+      <c r="H110" s="156"/>
+      <c r="I110" s="157"/>
+      <c r="J110" s="157">
+        <f>'detalle y gastos'!B7</f>
+        <v>0</v>
+      </c>
+      <c r="K110" s="155"/>
+      <c r="L110" s="154"/>
+      <c r="M110" s="155"/>
+    </row>
+    <row r="111" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E111" s="154" t="s">
         <v>113</v>
       </c>
-      <c r="F108" s="190"/>
-      <c r="G108" s="190"/>
-      <c r="H108" s="190"/>
-      <c r="I108" s="190"/>
-      <c r="J108" s="190"/>
-      <c r="K108" s="191"/>
-      <c r="L108" s="153"/>
-      <c r="M108" s="154"/>
-    </row>
-    <row r="109" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E109" s="192" t="s">
+      <c r="F111" s="157"/>
+      <c r="G111" s="157"/>
+      <c r="H111" s="157"/>
+      <c r="I111" s="157"/>
+      <c r="J111" s="157"/>
+      <c r="K111" s="155"/>
+      <c r="L111" s="154"/>
+      <c r="M111" s="155"/>
+    </row>
+    <row r="112" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E112" s="158"/>
+      <c r="F112" s="159"/>
+      <c r="G112" s="159"/>
+      <c r="H112" s="159"/>
+      <c r="I112" s="159"/>
+      <c r="J112" s="159"/>
+      <c r="K112" s="160"/>
+      <c r="L112" s="154"/>
+      <c r="M112" s="155"/>
+    </row>
+    <row r="113" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E113" s="192" t="s">
+        <v>49</v>
+      </c>
+      <c r="F113" s="193"/>
+      <c r="G113" s="193"/>
+      <c r="H113" s="193"/>
+      <c r="I113" s="193"/>
+      <c r="J113" s="193"/>
+      <c r="K113" s="194"/>
+      <c r="L113" s="154"/>
+      <c r="M113" s="155"/>
+    </row>
+    <row r="114" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E114" s="154"/>
+      <c r="F114" s="157"/>
+      <c r="G114" s="157"/>
+      <c r="H114" s="157"/>
+      <c r="I114" s="157"/>
+      <c r="J114" s="157"/>
+      <c r="K114" s="155"/>
+      <c r="L114" s="154"/>
+      <c r="M114" s="155"/>
+    </row>
+    <row r="115" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E115" s="154" t="s">
         <v>114</v>
       </c>
-      <c r="F109" s="190"/>
-      <c r="G109" s="190"/>
-      <c r="H109" s="190"/>
-      <c r="I109" s="190"/>
-      <c r="J109" s="190"/>
-      <c r="K109" s="191"/>
-      <c r="L109" s="155"/>
-      <c r="M109" s="156"/>
-    </row>
-    <row r="110" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E110" s="153"/>
-      <c r="F110" s="157"/>
-      <c r="G110" s="157"/>
-      <c r="H110" s="157"/>
-      <c r="I110" s="158"/>
-      <c r="J110" s="158">
-        <f>'detalle y gastos'!B7</f>
-        <v>0</v>
-      </c>
-      <c r="K110" s="156"/>
-      <c r="L110" s="155"/>
-      <c r="M110" s="156"/>
-    </row>
-    <row r="111" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E111" s="155" t="s">
-        <v>115</v>
-      </c>
-      <c r="F111" s="158"/>
-      <c r="G111" s="158"/>
-      <c r="H111" s="158"/>
-      <c r="I111" s="158"/>
-      <c r="J111" s="158"/>
-      <c r="K111" s="156"/>
-      <c r="L111" s="155"/>
-      <c r="M111" s="156"/>
-    </row>
-    <row r="112" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E112" s="159"/>
-      <c r="F112" s="160"/>
-      <c r="G112" s="160"/>
-      <c r="H112" s="160"/>
-      <c r="I112" s="160"/>
-      <c r="J112" s="160"/>
-      <c r="K112" s="161"/>
-      <c r="L112" s="155"/>
-      <c r="M112" s="156"/>
-    </row>
-    <row r="113" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E113" s="193" t="s">
-        <v>50</v>
-      </c>
-      <c r="F113" s="194"/>
-      <c r="G113" s="194"/>
-      <c r="H113" s="194"/>
-      <c r="I113" s="194"/>
-      <c r="J113" s="194"/>
-      <c r="K113" s="195"/>
-      <c r="L113" s="155"/>
-      <c r="M113" s="156"/>
-    </row>
-    <row r="114" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E114" s="155"/>
-      <c r="F114" s="158"/>
-      <c r="G114" s="158"/>
-      <c r="H114" s="158"/>
-      <c r="I114" s="158"/>
-      <c r="J114" s="158"/>
-      <c r="K114" s="156"/>
-      <c r="L114" s="155"/>
-      <c r="M114" s="156"/>
-    </row>
-    <row r="115" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E115" s="155" t="s">
-        <v>116</v>
-      </c>
-      <c r="F115" s="158"/>
-      <c r="G115" s="163" t="str">
+      <c r="F115" s="157"/>
+      <c r="G115" s="162" t="str">
         <f>C5</f>
         <v>Gomez Elizabeth</v>
       </c>
-      <c r="H115" s="158"/>
-      <c r="I115" s="158" t="s">
+      <c r="H115" s="157"/>
+      <c r="I115" s="157" t="s">
+        <v>115</v>
+      </c>
+      <c r="J115" s="161">
+        <v>45674</v>
+      </c>
+      <c r="K115" s="155"/>
+      <c r="L115" s="195" t="s">
+        <v>116</v>
+      </c>
+      <c r="M115" s="196"/>
+    </row>
+    <row r="116" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E116" s="154" t="s">
         <v>117</v>
       </c>
-      <c r="J115" s="162">
-        <v>45674</v>
-      </c>
-      <c r="K115" s="156"/>
-      <c r="L115" s="196" t="s">
+      <c r="F116" s="162">
+        <v>1</v>
+      </c>
+      <c r="G116" s="157"/>
+      <c r="H116" s="157"/>
+      <c r="I116" s="157"/>
+      <c r="J116" s="157"/>
+      <c r="K116" s="155"/>
+      <c r="L116" s="154"/>
+      <c r="M116" s="155"/>
+    </row>
+    <row r="117" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E117" s="154"/>
+      <c r="F117" s="157"/>
+      <c r="G117" s="157"/>
+      <c r="H117" s="157"/>
+      <c r="I117" s="157"/>
+      <c r="J117" s="157"/>
+      <c r="K117" s="155"/>
+      <c r="L117" s="197"/>
+      <c r="M117" s="196"/>
+    </row>
+    <row r="118" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E118" s="154" t="s">
+        <v>48</v>
+      </c>
+      <c r="F118" s="157"/>
+      <c r="G118" s="157"/>
+      <c r="H118" s="157"/>
+      <c r="I118" s="157"/>
+      <c r="J118" s="163">
+        <f>J5</f>
+        <v>0</v>
+      </c>
+      <c r="K118" s="155"/>
+      <c r="L118" s="154"/>
+      <c r="M118" s="155"/>
+    </row>
+    <row r="119" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E119" s="164" t="s">
         <v>118</v>
       </c>
-      <c r="M115" s="197"/>
-    </row>
-    <row r="116" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E116" s="155" t="s">
-        <v>119</v>
-      </c>
-      <c r="F116" s="163">
-        <v>1</v>
-      </c>
-      <c r="G116" s="158"/>
-      <c r="H116" s="158"/>
-      <c r="I116" s="158"/>
-      <c r="J116" s="158"/>
-      <c r="K116" s="156"/>
-      <c r="L116" s="155"/>
-      <c r="M116" s="156"/>
-    </row>
-    <row r="117" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E117" s="155"/>
-      <c r="F117" s="158"/>
-      <c r="G117" s="158"/>
-      <c r="H117" s="158"/>
-      <c r="I117" s="158"/>
-      <c r="J117" s="158"/>
-      <c r="K117" s="156"/>
-      <c r="L117" s="198"/>
-      <c r="M117" s="197"/>
-    </row>
-    <row r="118" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E118" s="155" t="s">
-        <v>49</v>
-      </c>
-      <c r="F118" s="158"/>
-      <c r="G118" s="158"/>
-      <c r="H118" s="158"/>
-      <c r="I118" s="158"/>
-      <c r="J118" s="164">
-        <f>J5</f>
-        <v>50112.700380000009</v>
-      </c>
-      <c r="K118" s="156"/>
-      <c r="L118" s="155"/>
-      <c r="M118" s="156"/>
-    </row>
-    <row r="119" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E119" s="165" t="s">
-        <v>120</v>
-      </c>
-      <c r="F119" s="158"/>
-      <c r="G119" s="158"/>
-      <c r="H119" s="158"/>
-      <c r="I119" s="158"/>
-      <c r="J119" s="164">
+      <c r="F119" s="157"/>
+      <c r="G119" s="157"/>
+      <c r="H119" s="157"/>
+      <c r="I119" s="157"/>
+      <c r="J119" s="163">
         <f>K5</f>
         <v>110400</v>
       </c>
-      <c r="K119" s="156"/>
-      <c r="L119" s="155"/>
-      <c r="M119" s="156"/>
-    </row>
-    <row r="120" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E120" s="165" t="s">
-        <v>124</v>
-      </c>
-      <c r="F120" s="158"/>
-      <c r="G120" s="158"/>
-      <c r="H120" s="158"/>
-      <c r="I120" s="158"/>
-      <c r="J120" s="164">
+      <c r="K119" s="155"/>
+      <c r="L119" s="154"/>
+      <c r="M119" s="155"/>
+    </row>
+    <row r="120" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E120" s="164" t="s">
+        <v>122</v>
+      </c>
+      <c r="F120" s="157"/>
+      <c r="G120" s="157"/>
+      <c r="H120" s="157"/>
+      <c r="I120" s="157"/>
+      <c r="J120" s="163">
         <f>-20862.34+20810</f>
         <v>-52.340000000000146</v>
       </c>
-      <c r="K120" s="156"/>
-      <c r="L120" s="155"/>
-      <c r="M120" s="156"/>
-    </row>
-    <row r="121" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E121" s="165"/>
-      <c r="F121" s="158"/>
-      <c r="G121" s="158"/>
-      <c r="H121" s="158"/>
-      <c r="I121" s="158"/>
-      <c r="J121" s="164"/>
-      <c r="K121" s="156"/>
-      <c r="L121" s="155"/>
-      <c r="M121" s="156"/>
-    </row>
-    <row r="122" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E122" s="165"/>
-      <c r="F122" s="158"/>
-      <c r="G122" s="158"/>
-      <c r="H122" s="158"/>
-      <c r="I122" s="158"/>
-      <c r="J122" s="164"/>
-      <c r="K122" s="156"/>
-      <c r="L122" s="155"/>
-      <c r="M122" s="156"/>
-    </row>
-    <row r="123" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="F123" s="158"/>
-      <c r="G123" s="158"/>
-      <c r="H123" s="158"/>
-      <c r="I123" s="158"/>
-      <c r="J123" s="164"/>
-      <c r="K123" s="156"/>
-      <c r="L123" s="155"/>
-      <c r="M123" s="156"/>
-    </row>
-    <row r="124" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E124" s="165"/>
-      <c r="F124" s="158"/>
-      <c r="G124" s="158"/>
-      <c r="H124" s="158"/>
-      <c r="I124" s="158"/>
-      <c r="J124" s="164"/>
-      <c r="K124" s="156"/>
-      <c r="L124" s="155"/>
-      <c r="M124" s="156"/>
-    </row>
-    <row r="125" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E125" s="155"/>
-      <c r="F125" s="158"/>
-      <c r="G125" s="158"/>
-      <c r="H125" s="158"/>
-      <c r="I125" s="158"/>
-      <c r="J125" s="158"/>
-      <c r="K125" s="156"/>
-      <c r="L125" s="155"/>
-      <c r="M125" s="156"/>
-    </row>
-    <row r="126" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E126" s="155"/>
-      <c r="F126" s="158"/>
-      <c r="G126" s="158"/>
-      <c r="H126" s="158"/>
-      <c r="I126" s="158"/>
-      <c r="J126" s="158"/>
-      <c r="K126" s="156"/>
-      <c r="L126" s="155"/>
-      <c r="M126" s="156"/>
-    </row>
-    <row r="127" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E127" s="155"/>
-      <c r="F127" s="158"/>
-      <c r="G127" s="158"/>
-      <c r="H127" s="158"/>
-      <c r="I127" s="158"/>
-      <c r="J127" s="158"/>
-      <c r="K127" s="156"/>
-      <c r="L127" s="166"/>
-      <c r="M127" s="167"/>
-    </row>
-    <row r="128" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E128" s="199" t="s">
-        <v>121</v>
-      </c>
-      <c r="F128" s="200"/>
-      <c r="G128" s="200"/>
-      <c r="H128" s="200"/>
-      <c r="I128" s="200"/>
-      <c r="J128" s="201">
+      <c r="K120" s="155"/>
+      <c r="L120" s="154"/>
+      <c r="M120" s="155"/>
+    </row>
+    <row r="121" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E121" s="164"/>
+      <c r="F121" s="157"/>
+      <c r="G121" s="157"/>
+      <c r="H121" s="157"/>
+      <c r="I121" s="157"/>
+      <c r="J121" s="163"/>
+      <c r="K121" s="155"/>
+      <c r="L121" s="154"/>
+      <c r="M121" s="155"/>
+    </row>
+    <row r="122" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E122" s="164"/>
+      <c r="F122" s="157"/>
+      <c r="G122" s="157"/>
+      <c r="H122" s="157"/>
+      <c r="I122" s="157"/>
+      <c r="J122" s="163"/>
+      <c r="K122" s="155"/>
+      <c r="L122" s="154"/>
+      <c r="M122" s="155"/>
+    </row>
+    <row r="123" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F123" s="157"/>
+      <c r="G123" s="157"/>
+      <c r="H123" s="157"/>
+      <c r="I123" s="157"/>
+      <c r="J123" s="163"/>
+      <c r="K123" s="155"/>
+      <c r="L123" s="154"/>
+      <c r="M123" s="155"/>
+    </row>
+    <row r="124" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E124" s="164"/>
+      <c r="F124" s="157"/>
+      <c r="G124" s="157"/>
+      <c r="H124" s="157"/>
+      <c r="I124" s="157"/>
+      <c r="J124" s="163"/>
+      <c r="K124" s="155"/>
+      <c r="L124" s="154"/>
+      <c r="M124" s="155"/>
+    </row>
+    <row r="125" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E125" s="154"/>
+      <c r="F125" s="157"/>
+      <c r="G125" s="157"/>
+      <c r="H125" s="157"/>
+      <c r="I125" s="157"/>
+      <c r="J125" s="157"/>
+      <c r="K125" s="155"/>
+      <c r="L125" s="154"/>
+      <c r="M125" s="155"/>
+    </row>
+    <row r="126" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E126" s="154"/>
+      <c r="F126" s="157"/>
+      <c r="G126" s="157"/>
+      <c r="H126" s="157"/>
+      <c r="I126" s="157"/>
+      <c r="J126" s="157"/>
+      <c r="K126" s="155"/>
+      <c r="L126" s="154"/>
+      <c r="M126" s="155"/>
+    </row>
+    <row r="127" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E127" s="154"/>
+      <c r="F127" s="157"/>
+      <c r="G127" s="157"/>
+      <c r="H127" s="157"/>
+      <c r="I127" s="157"/>
+      <c r="J127" s="157"/>
+      <c r="K127" s="155"/>
+      <c r="L127" s="165"/>
+      <c r="M127" s="166"/>
+    </row>
+    <row r="128" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E128" s="198" t="s">
+        <v>119</v>
+      </c>
+      <c r="F128" s="199"/>
+      <c r="G128" s="199"/>
+      <c r="H128" s="199"/>
+      <c r="I128" s="199"/>
+      <c r="J128" s="200">
         <f>SUM(J118:J127)</f>
-        <v>160460.36038</v>
-      </c>
-      <c r="K128" s="191"/>
-      <c r="L128" s="168"/>
-      <c r="M128" s="169"/>
+        <v>110347.66</v>
+      </c>
+      <c r="K128" s="190"/>
+      <c r="L128" s="167"/>
+      <c r="M128" s="168"/>
     </row>
   </sheetData>
   <mergeCells count="50">
@@ -7990,12 +8063,12 @@
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="I3:I4"/>
+    <mergeCell ref="I1:J1"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="E52:I52"/>
     <mergeCell ref="J52:K52"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A11:B11"/>
@@ -8014,7 +8087,6 @@
     <mergeCell ref="L92:M92"/>
     <mergeCell ref="E103:I103"/>
     <mergeCell ref="J103:K103"/>
-    <mergeCell ref="I1:J1"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="E108:K108"/>
     <mergeCell ref="E109:K109"/>
@@ -8030,6 +8102,7 @@
     <mergeCell ref="E37:K37"/>
     <mergeCell ref="L39:M39"/>
     <mergeCell ref="L41:M41"/>
+    <mergeCell ref="E52:I52"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/PATXOT 512/Agosto/PATXOT 521 Agosto.xlsx
+++ b/PATXOT 512/Agosto/PATXOT 521 Agosto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PATXOT 512\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56E022D1-3448-4832-81C8-A58423EF4291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87CB1EBA-F438-4539-AA0E-049260EAAC1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1749,6 +1749,47 @@
     </xf>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="22" fillId="11" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1759,12 +1800,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1785,35 +1820,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="22" fillId="11" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1829,12 +1835,6 @@
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1844,11 +1844,11 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2303,7 +2303,7 @@
       <c r="B17" s="87" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="211">
+      <c r="C17" s="174">
         <v>79724.34</v>
       </c>
       <c r="D17" s="48"/>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="B42" s="3"/>
       <c r="C42" s="145">
-        <v>8056.9037403397379</v>
+        <v>0</v>
       </c>
       <c r="D42" s="6"/>
       <c r="E42" s="6"/>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="C43" s="32">
         <f>'prorrateo '!F15</f>
-        <v>114809.90303832441</v>
+        <v>301017.59000000003</v>
       </c>
       <c r="D43" s="14"/>
       <c r="E43" s="14"/>
@@ -2570,7 +2570,7 @@
       <c r="B48" s="33"/>
       <c r="C48" s="40">
         <f>SUM(C42:C47)</f>
-        <v>-584910.38322133583</v>
+        <v>-406759.6</v>
       </c>
       <c r="D48" s="6"/>
     </row>
@@ -2690,14 +2690,11 @@
       <c r="E1" s="14">
         <v>438093.68</v>
       </c>
-      <c r="H1" s="212" t="s">
+      <c r="H1" s="175" t="s">
         <v>144</v>
       </c>
-      <c r="I1" s="212"/>
-      <c r="J1" s="14">
-        <f>-('detalle y gastos'!C44+'detalle y gastos'!C45+'detalle y gastos'!C46)</f>
-        <v>269683.51</v>
-      </c>
+      <c r="I1" s="175"/>
+      <c r="J1" s="14"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="97">
@@ -2717,14 +2714,14 @@
       <c r="L2" s="102"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="182" t="s">
+      <c r="A3" s="199" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="183"/>
-      <c r="C3" s="178" t="s">
+      <c r="B3" s="200"/>
+      <c r="C3" s="189" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="180" t="s">
+      <c r="D3" s="197" t="s">
         <v>55</v>
       </c>
       <c r="E3" s="7" t="s">
@@ -2733,19 +2730,19 @@
       <c r="F3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="178" t="s">
+      <c r="G3" s="189" t="s">
         <v>53</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="176" t="s">
+      <c r="I3" s="195" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="186" t="s">
+      <c r="J3" s="191" t="s">
         <v>110</v>
       </c>
-      <c r="K3" s="178" t="s">
+      <c r="K3" s="189" t="s">
         <v>42</v>
       </c>
       <c r="L3" s="45" t="s">
@@ -2753,32 +2750,32 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="184"/>
-      <c r="B4" s="185"/>
-      <c r="C4" s="179"/>
-      <c r="D4" s="181"/>
+      <c r="A4" s="201"/>
+      <c r="B4" s="202"/>
+      <c r="C4" s="190"/>
+      <c r="D4" s="198"/>
       <c r="E4" s="57" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="179"/>
+      <c r="G4" s="190"/>
       <c r="H4" s="37">
         <v>0.04</v>
       </c>
-      <c r="I4" s="177"/>
-      <c r="J4" s="187"/>
-      <c r="K4" s="179"/>
+      <c r="I4" s="196"/>
+      <c r="J4" s="192"/>
+      <c r="K4" s="190"/>
       <c r="L4" s="38" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="174">
+      <c r="A5" s="193">
         <v>1</v>
       </c>
-      <c r="B5" s="175"/>
+      <c r="B5" s="194"/>
       <c r="C5" s="110" t="s">
         <v>65</v>
       </c>
@@ -2787,7 +2784,7 @@
         <v>41531.40466575251</v>
       </c>
       <c r="F5" s="150">
-        <f t="shared" ref="F5:F9" si="0">E5</f>
+        <f t="shared" ref="F5:F14" si="0">E5</f>
         <v>41531.40466575251</v>
       </c>
       <c r="G5" s="151">
@@ -2807,18 +2804,18 @@
       </c>
       <c r="K5" s="142">
         <f>J$1*I5/100</f>
-        <v>37216.324380000005</v>
+        <v>0</v>
       </c>
       <c r="L5" s="103">
         <f>G5+H5+J5+K5</f>
-        <v>97673.252219999995</v>
+        <v>60456.927839999997</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A6" s="174">
+      <c r="A6" s="193">
         <v>2</v>
       </c>
-      <c r="B6" s="175"/>
+      <c r="B6" s="194"/>
       <c r="C6" s="110" t="s">
         <v>66</v>
       </c>
@@ -2849,18 +2846,18 @@
       </c>
       <c r="K6" s="142">
         <f t="shared" ref="K6:K14" si="4">J$1*I6/100</f>
-        <v>31984.464285999999</v>
+        <v>0</v>
       </c>
       <c r="L6" s="103">
         <f t="shared" ref="L6:L14" si="5">G6+H6+J6+K6</f>
-        <v>83942.374733999997</v>
+        <v>51957.910447999995</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A7" s="174">
+      <c r="A7" s="193">
         <v>3</v>
       </c>
-      <c r="B7" s="175"/>
+      <c r="B7" s="194"/>
       <c r="C7" s="110" t="s">
         <v>66</v>
       </c>
@@ -2870,14 +2867,17 @@
       <c r="E7" s="149">
         <v>37894.033173585289</v>
       </c>
-      <c r="F7" s="150"/>
+      <c r="F7" s="150">
+        <f t="shared" si="0"/>
+        <v>37894.033173585289</v>
+      </c>
       <c r="G7" s="151">
         <f t="shared" si="1"/>
-        <v>37894.033173585289</v>
+        <v>0</v>
       </c>
       <c r="H7" s="151">
         <f t="shared" si="2"/>
-        <v>1515.7613269434116</v>
+        <v>0</v>
       </c>
       <c r="I7" s="95">
         <v>12.46</v>
@@ -2888,18 +2888,18 @@
       </c>
       <c r="K7" s="142">
         <f t="shared" si="4"/>
-        <v>33602.565346000003</v>
+        <v>0</v>
       </c>
       <c r="L7" s="103">
         <f t="shared" si="5"/>
-        <v>127598.83237452871</v>
+        <v>54586.472527999998</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A8" s="174">
+      <c r="A8" s="193">
         <v>4</v>
       </c>
-      <c r="B8" s="175"/>
+      <c r="B8" s="194"/>
       <c r="C8" s="110" t="s">
         <v>67</v>
       </c>
@@ -2909,14 +2909,17 @@
       <c r="E8" s="149">
         <v>44723.725567140471</v>
       </c>
-      <c r="F8" s="150"/>
+      <c r="F8" s="150">
+        <f t="shared" si="0"/>
+        <v>44723.725567140471</v>
+      </c>
       <c r="G8" s="151">
         <f t="shared" si="1"/>
-        <v>44723.725567140471</v>
+        <v>0</v>
       </c>
       <c r="H8" s="151">
         <f t="shared" si="2"/>
-        <v>1788.949022685619</v>
+        <v>0</v>
       </c>
       <c r="I8" s="95">
         <v>14.75</v>
@@ -2927,18 +2930,18 @@
       </c>
       <c r="K8" s="142">
         <f t="shared" si="4"/>
-        <v>39778.317725000001</v>
+        <v>0</v>
       </c>
       <c r="L8" s="103">
         <f t="shared" si="5"/>
-        <v>150909.8101148261</v>
+        <v>64618.817800000004</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="174">
+      <c r="A9" s="193">
         <v>5</v>
       </c>
-      <c r="B9" s="175"/>
+      <c r="B9" s="194"/>
       <c r="C9" s="110" t="s">
         <v>68</v>
       </c>
@@ -2969,18 +2972,18 @@
       </c>
       <c r="K9" s="142">
         <f t="shared" si="4"/>
-        <v>33467.723591000002</v>
+        <v>0</v>
       </c>
       <c r="L9" s="103">
         <f>G9+H9+J9+K9</f>
-        <v>87835.149279000005</v>
+        <v>54367.425687999996</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="174">
+      <c r="A10" s="193">
         <v>6</v>
       </c>
-      <c r="B10" s="175"/>
+      <c r="B10" s="194"/>
       <c r="C10" s="110" t="s">
         <v>69</v>
       </c>
@@ -2988,14 +2991,17 @@
       <c r="E10" s="149">
         <v>37332.293419986621</v>
       </c>
-      <c r="F10" s="150"/>
+      <c r="F10" s="150">
+        <f t="shared" si="0"/>
+        <v>37332.293419986621</v>
+      </c>
       <c r="G10" s="151">
         <f t="shared" si="1"/>
-        <v>37332.293419986621</v>
+        <v>0</v>
       </c>
       <c r="H10" s="151">
         <f t="shared" si="2"/>
-        <v>1493.2917367994648</v>
+        <v>0</v>
       </c>
       <c r="I10" s="95">
         <v>12.48</v>
@@ -3006,18 +3012,18 @@
       </c>
       <c r="K10" s="142">
         <f t="shared" si="4"/>
-        <v>33656.502048000002</v>
+        <v>0</v>
       </c>
       <c r="L10" s="103">
         <f t="shared" si="5"/>
-        <v>127156.17846878609</v>
+        <v>54674.091264000002</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="174">
+      <c r="A11" s="193">
         <v>7</v>
       </c>
-      <c r="B11" s="175"/>
+      <c r="B11" s="194"/>
       <c r="C11" s="110" t="s">
         <v>70</v>
       </c>
@@ -3025,14 +3031,17 @@
       <c r="E11" s="149">
         <v>54686.953726963213</v>
       </c>
-      <c r="F11" s="150"/>
+      <c r="F11" s="150">
+        <f t="shared" si="0"/>
+        <v>54686.953726963213</v>
+      </c>
       <c r="G11" s="151">
         <f t="shared" si="1"/>
-        <v>54686.953726963213</v>
+        <v>0</v>
       </c>
       <c r="H11" s="151">
         <f t="shared" si="2"/>
-        <v>2187.4781490785285</v>
+        <v>0</v>
       </c>
       <c r="I11" s="95">
         <v>18.260000000000002</v>
@@ -3043,18 +3052,18 @@
       </c>
       <c r="K11" s="142">
         <f t="shared" si="4"/>
-        <v>49244.208926000007</v>
+        <v>0</v>
       </c>
       <c r="L11" s="103">
         <f t="shared" si="5"/>
-        <v>186114.54677004175</v>
+        <v>79995.905968000006</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="174" t="s">
+      <c r="A12" s="193" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="175"/>
+      <c r="B12" s="194"/>
       <c r="C12" s="110" t="str">
         <f>C9</f>
         <v>Grand Jorge</v>
@@ -3063,14 +3072,17 @@
       <c r="E12" s="149">
         <v>3895.6564420000004</v>
       </c>
-      <c r="F12" s="150"/>
+      <c r="F12" s="150">
+        <f t="shared" si="0"/>
+        <v>3895.6564420000004</v>
+      </c>
       <c r="G12" s="151">
         <f t="shared" si="1"/>
-        <v>3895.6564420000004</v>
+        <v>0</v>
       </c>
       <c r="H12" s="151">
         <f t="shared" si="2"/>
-        <v>155.82625768000003</v>
+        <v>0</v>
       </c>
       <c r="I12" s="95">
         <v>1.34</v>
@@ -3081,18 +3093,18 @@
       </c>
       <c r="K12" s="142">
         <f t="shared" si="4"/>
-        <v>3613.7590340000002</v>
+        <v>0</v>
       </c>
       <c r="L12" s="103">
         <f t="shared" si="5"/>
-        <v>13535.697045680001</v>
+        <v>5870.455312</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="174" t="s">
+      <c r="A13" s="193" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="175"/>
+      <c r="B13" s="194"/>
       <c r="C13" s="110" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
@@ -3101,14 +3113,17 @@
       <c r="E13" s="149">
         <v>3837.5123159999998</v>
       </c>
-      <c r="F13" s="150"/>
+      <c r="F13" s="150">
+        <f t="shared" si="0"/>
+        <v>3837.5123159999998</v>
+      </c>
       <c r="G13" s="151">
         <f t="shared" si="1"/>
-        <v>3837.5123159999998</v>
+        <v>0</v>
       </c>
       <c r="H13" s="151">
         <f t="shared" si="2"/>
-        <v>153.50049264</v>
+        <v>0</v>
       </c>
       <c r="I13" s="95">
         <v>1.32</v>
@@ -3119,18 +3134,18 @@
       </c>
       <c r="K13" s="142">
         <f t="shared" si="4"/>
-        <v>3559.8223320000002</v>
+        <v>0</v>
       </c>
       <c r="L13" s="103">
         <f t="shared" si="5"/>
-        <v>13333.671716640001</v>
+        <v>5782.8365760000006</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="174" t="s">
+      <c r="A14" s="193" t="s">
         <v>77</v>
       </c>
-      <c r="B14" s="175"/>
+      <c r="B14" s="194"/>
       <c r="C14" s="58" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
@@ -3139,14 +3154,17 @@
       <c r="E14" s="149">
         <v>3837.5123159999998</v>
       </c>
-      <c r="F14" s="150"/>
+      <c r="F14" s="150">
+        <f t="shared" si="0"/>
+        <v>3837.5123159999998</v>
+      </c>
       <c r="G14" s="151">
         <f t="shared" si="1"/>
-        <v>3837.5123159999998</v>
+        <v>0</v>
       </c>
       <c r="H14" s="151">
         <f t="shared" si="2"/>
-        <v>153.50049264</v>
+        <v>0</v>
       </c>
       <c r="I14" s="95">
         <v>1.32</v>
@@ -3157,11 +3175,11 @@
       </c>
       <c r="K14" s="142">
         <f t="shared" si="4"/>
-        <v>3559.8223320000002</v>
+        <v>0</v>
       </c>
       <c r="L14" s="103">
         <f t="shared" si="5"/>
-        <v>13333.671716640001</v>
+        <v>5782.8365760000006</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3177,12 +3195,12 @@
       </c>
       <c r="F15" s="107">
         <f>SUM(F5:F14)</f>
-        <v>114809.90303832441</v>
+        <v>301017.59000000003</v>
       </c>
       <c r="G15" s="107"/>
       <c r="H15" s="108">
         <f>SUM(H5:H14)</f>
-        <v>7448.3074784670234</v>
+        <v>0</v>
       </c>
       <c r="I15" s="109">
         <f t="shared" ref="I15" si="6">SUM(I5:I14)</f>
@@ -3194,11 +3212,11 @@
       </c>
       <c r="K15" s="42">
         <f>SUM(K5:K11)</f>
-        <v>258950.106302</v>
+        <v>0</v>
       </c>
       <c r="L15" s="42">
         <f>SUM(L5:L14)</f>
-        <v>901433.18444014259</v>
+        <v>438093.67999999993</v>
       </c>
     </row>
     <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
@@ -3590,15 +3608,15 @@
     <row r="32" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="188" t="s">
+      <c r="E32" s="180" t="s">
         <v>111</v>
       </c>
-      <c r="F32" s="189"/>
-      <c r="G32" s="189"/>
-      <c r="H32" s="189"/>
-      <c r="I32" s="189"/>
-      <c r="J32" s="189"/>
-      <c r="K32" s="190"/>
+      <c r="F32" s="181"/>
+      <c r="G32" s="181"/>
+      <c r="H32" s="181"/>
+      <c r="I32" s="181"/>
+      <c r="J32" s="181"/>
+      <c r="K32" s="179"/>
       <c r="L32" s="152"/>
       <c r="M32" s="153"/>
       <c r="N32"/>
@@ -3606,15 +3624,15 @@
     <row r="33" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
-      <c r="E33" s="191" t="s">
+      <c r="E33" s="182" t="s">
         <v>112</v>
       </c>
-      <c r="F33" s="189"/>
-      <c r="G33" s="189"/>
-      <c r="H33" s="189"/>
-      <c r="I33" s="189"/>
-      <c r="J33" s="189"/>
-      <c r="K33" s="190"/>
+      <c r="F33" s="181"/>
+      <c r="G33" s="181"/>
+      <c r="H33" s="181"/>
+      <c r="I33" s="181"/>
+      <c r="J33" s="181"/>
+      <c r="K33" s="179"/>
       <c r="L33" s="154"/>
       <c r="M33" s="155"/>
       <c r="N33"/>
@@ -3669,15 +3687,15 @@
     <row r="37" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="192" t="s">
+      <c r="E37" s="183" t="s">
         <v>49</v>
       </c>
-      <c r="F37" s="193"/>
-      <c r="G37" s="193"/>
-      <c r="H37" s="193"/>
-      <c r="I37" s="193"/>
-      <c r="J37" s="193"/>
-      <c r="K37" s="194"/>
+      <c r="F37" s="184"/>
+      <c r="G37" s="184"/>
+      <c r="H37" s="184"/>
+      <c r="I37" s="184"/>
+      <c r="J37" s="184"/>
+      <c r="K37" s="185"/>
       <c r="L37" s="154"/>
       <c r="M37" s="155"/>
       <c r="N37"/>
@@ -3715,10 +3733,10 @@
         <v>45674</v>
       </c>
       <c r="K39" s="155"/>
-      <c r="L39" s="195" t="s">
+      <c r="L39" s="186" t="s">
         <v>116</v>
       </c>
-      <c r="M39" s="196"/>
+      <c r="M39" s="187"/>
       <c r="N39"/>
     </row>
     <row r="40" spans="3:14" x14ac:dyDescent="0.25">
@@ -3749,8 +3767,8 @@
       <c r="I41" s="157"/>
       <c r="J41" s="157"/>
       <c r="K41" s="155"/>
-      <c r="L41" s="197"/>
-      <c r="M41" s="196"/>
+      <c r="L41" s="188"/>
+      <c r="M41" s="187"/>
       <c r="N41"/>
     </row>
     <row r="42" spans="3:14" x14ac:dyDescent="0.25">
@@ -3784,7 +3802,7 @@
       <c r="I43" s="157"/>
       <c r="J43" s="163">
         <f>K7</f>
-        <v>33602.565346000003</v>
+        <v>0</v>
       </c>
       <c r="K43" s="155"/>
       <c r="L43" s="154"/>
@@ -3803,7 +3821,7 @@
       <c r="I44" s="157"/>
       <c r="J44" s="163">
         <f>G7+H7</f>
-        <v>39409.794500528704</v>
+        <v>0</v>
       </c>
       <c r="K44" s="155"/>
       <c r="L44" s="154"/>
@@ -3915,18 +3933,18 @@
     <row r="52" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
-      <c r="E52" s="198" t="s">
+      <c r="E52" s="176" t="s">
         <v>119</v>
       </c>
-      <c r="F52" s="199"/>
-      <c r="G52" s="199"/>
-      <c r="H52" s="199"/>
-      <c r="I52" s="199"/>
-      <c r="J52" s="200">
+      <c r="F52" s="177"/>
+      <c r="G52" s="177"/>
+      <c r="H52" s="177"/>
+      <c r="I52" s="177"/>
+      <c r="J52" s="178">
         <f>SUM(J42:J51)</f>
-        <v>127674.63237452871</v>
-      </c>
-      <c r="K52" s="190"/>
+        <v>54662.272528000001</v>
+      </c>
+      <c r="K52" s="179"/>
       <c r="L52" s="167"/>
       <c r="M52" s="168"/>
       <c r="N52"/>
@@ -3938,28 +3956,28 @@
     </row>
     <row r="55" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="56" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E56" s="188" t="s">
+      <c r="E56" s="180" t="s">
         <v>111</v>
       </c>
-      <c r="F56" s="189"/>
-      <c r="G56" s="189"/>
-      <c r="H56" s="189"/>
-      <c r="I56" s="189"/>
-      <c r="J56" s="189"/>
-      <c r="K56" s="190"/>
+      <c r="F56" s="181"/>
+      <c r="G56" s="181"/>
+      <c r="H56" s="181"/>
+      <c r="I56" s="181"/>
+      <c r="J56" s="181"/>
+      <c r="K56" s="179"/>
       <c r="L56" s="152"/>
       <c r="M56" s="153"/>
     </row>
     <row r="57" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E57" s="191" t="s">
+      <c r="E57" s="182" t="s">
         <v>112</v>
       </c>
-      <c r="F57" s="189"/>
-      <c r="G57" s="189"/>
-      <c r="H57" s="189"/>
-      <c r="I57" s="189"/>
-      <c r="J57" s="189"/>
-      <c r="K57" s="190"/>
+      <c r="F57" s="181"/>
+      <c r="G57" s="181"/>
+      <c r="H57" s="181"/>
+      <c r="I57" s="181"/>
+      <c r="J57" s="181"/>
+      <c r="K57" s="179"/>
       <c r="L57" s="154"/>
       <c r="M57" s="155"/>
     </row>
@@ -4002,15 +4020,15 @@
       <c r="M60" s="155"/>
     </row>
     <row r="61" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="E61" s="192" t="s">
+      <c r="E61" s="183" t="s">
         <v>49</v>
       </c>
-      <c r="F61" s="193"/>
-      <c r="G61" s="193"/>
-      <c r="H61" s="193"/>
-      <c r="I61" s="193"/>
-      <c r="J61" s="193"/>
-      <c r="K61" s="194"/>
+      <c r="F61" s="184"/>
+      <c r="G61" s="184"/>
+      <c r="H61" s="184"/>
+      <c r="I61" s="184"/>
+      <c r="J61" s="184"/>
+      <c r="K61" s="185"/>
       <c r="L61" s="154"/>
       <c r="M61" s="155"/>
     </row>
@@ -4042,10 +4060,10 @@
         <v>45674</v>
       </c>
       <c r="K63" s="155"/>
-      <c r="L63" s="195" t="s">
+      <c r="L63" s="186" t="s">
         <v>116</v>
       </c>
-      <c r="M63" s="196"/>
+      <c r="M63" s="187"/>
     </row>
     <row r="64" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E64" s="154" t="s">
@@ -4070,8 +4088,8 @@
       <c r="I65" s="157"/>
       <c r="J65" s="157"/>
       <c r="K65" s="155"/>
-      <c r="L65" s="197"/>
-      <c r="M65" s="196"/>
+      <c r="L65" s="188"/>
+      <c r="M65" s="187"/>
     </row>
     <row r="66" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E66" s="154" t="s">
@@ -4099,7 +4117,7 @@
       <c r="I67" s="157"/>
       <c r="J67" s="163">
         <f>K8</f>
-        <v>39778.317725000001</v>
+        <v>0</v>
       </c>
       <c r="K67" s="155"/>
       <c r="L67" s="154"/>
@@ -4198,45 +4216,45 @@
       <c r="M75" s="166"/>
     </row>
     <row r="76" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E76" s="198" t="s">
+      <c r="E76" s="176" t="s">
         <v>119</v>
       </c>
-      <c r="F76" s="199"/>
-      <c r="G76" s="199"/>
-      <c r="H76" s="199"/>
-      <c r="I76" s="199"/>
-      <c r="J76" s="200">
+      <c r="F76" s="177"/>
+      <c r="G76" s="177"/>
+      <c r="H76" s="177"/>
+      <c r="I76" s="177"/>
+      <c r="J76" s="178">
         <f>SUM(J66:J75)</f>
-        <v>104397.13552500001</v>
-      </c>
-      <c r="K76" s="190"/>
+        <v>64618.817800000004</v>
+      </c>
+      <c r="K76" s="179"/>
       <c r="L76" s="167"/>
       <c r="M76" s="168"/>
     </row>
     <row r="82" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="83" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E83" s="188" t="s">
+      <c r="E83" s="180" t="s">
         <v>111</v>
       </c>
-      <c r="F83" s="189"/>
-      <c r="G83" s="189"/>
-      <c r="H83" s="189"/>
-      <c r="I83" s="189"/>
-      <c r="J83" s="189"/>
-      <c r="K83" s="190"/>
+      <c r="F83" s="181"/>
+      <c r="G83" s="181"/>
+      <c r="H83" s="181"/>
+      <c r="I83" s="181"/>
+      <c r="J83" s="181"/>
+      <c r="K83" s="179"/>
       <c r="L83" s="152"/>
       <c r="M83" s="153"/>
     </row>
     <row r="84" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E84" s="191" t="s">
+      <c r="E84" s="182" t="s">
         <v>112</v>
       </c>
-      <c r="F84" s="189"/>
-      <c r="G84" s="189"/>
-      <c r="H84" s="189"/>
-      <c r="I84" s="189"/>
-      <c r="J84" s="189"/>
-      <c r="K84" s="190"/>
+      <c r="F84" s="181"/>
+      <c r="G84" s="181"/>
+      <c r="H84" s="181"/>
+      <c r="I84" s="181"/>
+      <c r="J84" s="181"/>
+      <c r="K84" s="179"/>
       <c r="L84" s="154"/>
       <c r="M84" s="155"/>
     </row>
@@ -4279,15 +4297,15 @@
       <c r="M87" s="155"/>
     </row>
     <row r="88" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E88" s="192" t="s">
+      <c r="E88" s="183" t="s">
         <v>49</v>
       </c>
-      <c r="F88" s="193"/>
-      <c r="G88" s="193"/>
-      <c r="H88" s="193"/>
-      <c r="I88" s="193"/>
-      <c r="J88" s="193"/>
-      <c r="K88" s="194"/>
+      <c r="F88" s="184"/>
+      <c r="G88" s="184"/>
+      <c r="H88" s="184"/>
+      <c r="I88" s="184"/>
+      <c r="J88" s="184"/>
+      <c r="K88" s="185"/>
       <c r="L88" s="154"/>
       <c r="M88" s="155"/>
     </row>
@@ -4319,10 +4337,10 @@
         <v>45674</v>
       </c>
       <c r="K90" s="155"/>
-      <c r="L90" s="195" t="s">
+      <c r="L90" s="186" t="s">
         <v>116</v>
       </c>
-      <c r="M90" s="196"/>
+      <c r="M90" s="187"/>
     </row>
     <row r="91" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E91" s="154" t="s">
@@ -4347,8 +4365,8 @@
       <c r="I92" s="157"/>
       <c r="J92" s="157"/>
       <c r="K92" s="155"/>
-      <c r="L92" s="197"/>
-      <c r="M92" s="196"/>
+      <c r="L92" s="188"/>
+      <c r="M92" s="187"/>
     </row>
     <row r="93" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E93" s="154" t="s">
@@ -4376,7 +4394,7 @@
       <c r="I94" s="157"/>
       <c r="J94" s="163">
         <f>K10</f>
-        <v>33656.502048000002</v>
+        <v>0</v>
       </c>
       <c r="K94" s="155"/>
       <c r="L94" s="154"/>
@@ -4474,45 +4492,45 @@
       <c r="M102" s="166"/>
     </row>
     <row r="103" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E103" s="198" t="s">
+      <c r="E103" s="176" t="s">
         <v>119</v>
       </c>
-      <c r="F103" s="199"/>
-      <c r="G103" s="199"/>
-      <c r="H103" s="199"/>
-      <c r="I103" s="199"/>
-      <c r="J103" s="200">
+      <c r="F103" s="177"/>
+      <c r="G103" s="177"/>
+      <c r="H103" s="177"/>
+      <c r="I103" s="177"/>
+      <c r="J103" s="178">
         <f>SUM(J93:J102)</f>
-        <v>88354.483312000011</v>
-      </c>
-      <c r="K103" s="190"/>
+        <v>54697.981264000002</v>
+      </c>
+      <c r="K103" s="179"/>
       <c r="L103" s="167"/>
       <c r="M103" s="168"/>
     </row>
     <row r="107" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="108" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E108" s="188" t="s">
+      <c r="E108" s="180" t="s">
         <v>111</v>
       </c>
-      <c r="F108" s="189"/>
-      <c r="G108" s="189"/>
-      <c r="H108" s="189"/>
-      <c r="I108" s="189"/>
-      <c r="J108" s="189"/>
-      <c r="K108" s="190"/>
+      <c r="F108" s="181"/>
+      <c r="G108" s="181"/>
+      <c r="H108" s="181"/>
+      <c r="I108" s="181"/>
+      <c r="J108" s="181"/>
+      <c r="K108" s="179"/>
       <c r="L108" s="152"/>
       <c r="M108" s="153"/>
     </row>
     <row r="109" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E109" s="191" t="s">
+      <c r="E109" s="182" t="s">
         <v>112</v>
       </c>
-      <c r="F109" s="189"/>
-      <c r="G109" s="189"/>
-      <c r="H109" s="189"/>
-      <c r="I109" s="189"/>
-      <c r="J109" s="189"/>
-      <c r="K109" s="190"/>
+      <c r="F109" s="181"/>
+      <c r="G109" s="181"/>
+      <c r="H109" s="181"/>
+      <c r="I109" s="181"/>
+      <c r="J109" s="181"/>
+      <c r="K109" s="179"/>
       <c r="L109" s="154"/>
       <c r="M109" s="155"/>
     </row>
@@ -4555,15 +4573,15 @@
       <c r="M112" s="155"/>
     </row>
     <row r="113" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E113" s="192" t="s">
+      <c r="E113" s="183" t="s">
         <v>49</v>
       </c>
-      <c r="F113" s="193"/>
-      <c r="G113" s="193"/>
-      <c r="H113" s="193"/>
-      <c r="I113" s="193"/>
-      <c r="J113" s="193"/>
-      <c r="K113" s="194"/>
+      <c r="F113" s="184"/>
+      <c r="G113" s="184"/>
+      <c r="H113" s="184"/>
+      <c r="I113" s="184"/>
+      <c r="J113" s="184"/>
+      <c r="K113" s="185"/>
       <c r="L113" s="154"/>
       <c r="M113" s="155"/>
     </row>
@@ -4595,10 +4613,10 @@
         <v>45674</v>
       </c>
       <c r="K115" s="155"/>
-      <c r="L115" s="195" t="s">
+      <c r="L115" s="186" t="s">
         <v>116</v>
       </c>
-      <c r="M115" s="196"/>
+      <c r="M115" s="187"/>
     </row>
     <row r="116" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E116" s="154" t="s">
@@ -4623,8 +4641,8 @@
       <c r="I117" s="157"/>
       <c r="J117" s="157"/>
       <c r="K117" s="155"/>
-      <c r="L117" s="197"/>
-      <c r="M117" s="196"/>
+      <c r="L117" s="188"/>
+      <c r="M117" s="187"/>
     </row>
     <row r="118" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E118" s="154" t="s">
@@ -4652,7 +4670,7 @@
       <c r="I119" s="157"/>
       <c r="J119" s="163">
         <f>K5</f>
-        <v>37216.324380000005</v>
+        <v>0</v>
       </c>
       <c r="K119" s="155"/>
       <c r="L119" s="154"/>
@@ -4751,50 +4769,26 @@
       <c r="M127" s="166"/>
     </row>
     <row r="128" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E128" s="198" t="s">
+      <c r="E128" s="176" t="s">
         <v>119</v>
       </c>
-      <c r="F128" s="199"/>
-      <c r="G128" s="199"/>
-      <c r="H128" s="199"/>
-      <c r="I128" s="199"/>
-      <c r="J128" s="200">
+      <c r="F128" s="177"/>
+      <c r="G128" s="177"/>
+      <c r="H128" s="177"/>
+      <c r="I128" s="177"/>
+      <c r="J128" s="178">
         <f>SUM(J118:J127)</f>
-        <v>97620.912219999998</v>
-      </c>
-      <c r="K128" s="190"/>
+        <v>60404.587839999993</v>
+      </c>
+      <c r="K128" s="179"/>
       <c r="L128" s="167"/>
       <c r="M128" s="168"/>
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="E128:I128"/>
-    <mergeCell ref="J128:K128"/>
-    <mergeCell ref="E108:K108"/>
-    <mergeCell ref="E109:K109"/>
-    <mergeCell ref="E113:K113"/>
-    <mergeCell ref="L115:M115"/>
-    <mergeCell ref="L117:M117"/>
-    <mergeCell ref="E84:K84"/>
-    <mergeCell ref="E88:K88"/>
-    <mergeCell ref="L90:M90"/>
-    <mergeCell ref="L92:M92"/>
-    <mergeCell ref="E103:I103"/>
-    <mergeCell ref="J103:K103"/>
-    <mergeCell ref="L63:M63"/>
-    <mergeCell ref="L65:M65"/>
-    <mergeCell ref="E76:I76"/>
-    <mergeCell ref="J76:K76"/>
-    <mergeCell ref="E83:K83"/>
-    <mergeCell ref="E52:I52"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="E56:K56"/>
-    <mergeCell ref="E57:K57"/>
-    <mergeCell ref="E61:K61"/>
-    <mergeCell ref="E32:K32"/>
-    <mergeCell ref="E33:K33"/>
-    <mergeCell ref="E37:K37"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="A5:B5"/>
     <mergeCell ref="L39:M39"/>
     <mergeCell ref="L41:M41"/>
     <mergeCell ref="K3:K4"/>
@@ -4811,9 +4805,33 @@
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="L63:M63"/>
+    <mergeCell ref="L65:M65"/>
+    <mergeCell ref="E76:I76"/>
+    <mergeCell ref="J76:K76"/>
+    <mergeCell ref="E83:K83"/>
+    <mergeCell ref="L115:M115"/>
+    <mergeCell ref="L117:M117"/>
+    <mergeCell ref="E84:K84"/>
+    <mergeCell ref="E88:K88"/>
+    <mergeCell ref="L90:M90"/>
+    <mergeCell ref="L92:M92"/>
+    <mergeCell ref="E103:I103"/>
+    <mergeCell ref="J103:K103"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="E128:I128"/>
+    <mergeCell ref="J128:K128"/>
+    <mergeCell ref="E108:K108"/>
+    <mergeCell ref="E109:K109"/>
+    <mergeCell ref="E113:K113"/>
+    <mergeCell ref="E52:I52"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="E56:K56"/>
+    <mergeCell ref="E57:K57"/>
+    <mergeCell ref="E61:K61"/>
+    <mergeCell ref="E32:K32"/>
+    <mergeCell ref="E33:K33"/>
+    <mergeCell ref="E37:K37"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -5370,11 +5388,11 @@
       <c r="D1" s="55">
         <v>50000</v>
       </c>
-      <c r="H1" s="205">
+      <c r="H1" s="207">
         <v>250000</v>
       </c>
-      <c r="I1" s="205"/>
-      <c r="J1" s="205"/>
+      <c r="I1" s="207"/>
+      <c r="J1" s="207"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="52" t="s">
@@ -5438,13 +5456,13 @@
         <v>53</v>
       </c>
       <c r="K4" s="67"/>
-      <c r="L4" s="203" t="s">
+      <c r="L4" s="205" t="s">
         <v>60</v>
       </c>
       <c r="M4" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="N4" s="201" t="s">
+      <c r="N4" s="203" t="s">
         <v>54</v>
       </c>
       <c r="P4" s="21"/>
@@ -5473,11 +5491,11 @@
         <v>59</v>
       </c>
       <c r="K5" s="57"/>
-      <c r="L5" s="204"/>
+      <c r="L5" s="206"/>
       <c r="M5" s="81" t="s">
         <v>61</v>
       </c>
-      <c r="N5" s="202"/>
+      <c r="N5" s="204"/>
       <c r="P5" s="21"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -5980,14 +5998,14 @@
       <c r="L2" s="102"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="182" t="s">
+      <c r="A3" s="199" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="183"/>
-      <c r="C3" s="178" t="s">
+      <c r="B3" s="200"/>
+      <c r="C3" s="189" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="180" t="s">
+      <c r="D3" s="197" t="s">
         <v>55</v>
       </c>
       <c r="E3" s="7" t="s">
@@ -5996,50 +6014,50 @@
       <c r="F3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="178" t="s">
+      <c r="G3" s="189" t="s">
         <v>125</v>
       </c>
-      <c r="H3" s="178" t="s">
+      <c r="H3" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="176" t="s">
+      <c r="I3" s="195" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="180" t="s">
+      <c r="J3" s="197" t="s">
         <v>128</v>
       </c>
       <c r="K3" s="170" t="s">
         <v>127</v>
       </c>
-      <c r="L3" s="206" t="s">
+      <c r="L3" s="211" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="184"/>
-      <c r="B4" s="185"/>
-      <c r="C4" s="179"/>
-      <c r="D4" s="181"/>
+      <c r="A4" s="201"/>
+      <c r="B4" s="202"/>
+      <c r="C4" s="190"/>
+      <c r="D4" s="198"/>
       <c r="E4" s="57" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="179"/>
-      <c r="H4" s="179"/>
-      <c r="I4" s="177"/>
-      <c r="J4" s="181"/>
+      <c r="G4" s="190"/>
+      <c r="H4" s="190"/>
+      <c r="I4" s="196"/>
+      <c r="J4" s="198"/>
       <c r="K4" s="171" t="s">
         <v>129</v>
       </c>
-      <c r="L4" s="207"/>
+      <c r="L4" s="212"/>
     </row>
     <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="174">
+      <c r="A5" s="193">
         <v>1</v>
       </c>
-      <c r="B5" s="175"/>
+      <c r="B5" s="194"/>
       <c r="C5" s="110" t="s">
         <v>65</v>
       </c>
@@ -6076,10 +6094,10 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A6" s="174">
+      <c r="A6" s="193">
         <v>2</v>
       </c>
-      <c r="B6" s="175"/>
+      <c r="B6" s="194"/>
       <c r="C6" s="110" t="s">
         <v>66</v>
       </c>
@@ -6118,10 +6136,10 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A7" s="174">
+      <c r="A7" s="193">
         <v>3</v>
       </c>
-      <c r="B7" s="175"/>
+      <c r="B7" s="194"/>
       <c r="C7" s="110" t="s">
         <v>66</v>
       </c>
@@ -6160,10 +6178,10 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A8" s="174">
+      <c r="A8" s="193">
         <v>4</v>
       </c>
-      <c r="B8" s="175"/>
+      <c r="B8" s="194"/>
       <c r="C8" s="110" t="s">
         <v>67</v>
       </c>
@@ -6202,10 +6220,10 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="174">
+      <c r="A9" s="193">
         <v>5</v>
       </c>
-      <c r="B9" s="175"/>
+      <c r="B9" s="194"/>
       <c r="C9" s="110" t="s">
         <v>68</v>
       </c>
@@ -6244,10 +6262,10 @@
       </c>
     </row>
     <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="174">
+      <c r="A10" s="193">
         <v>6</v>
       </c>
-      <c r="B10" s="175"/>
+      <c r="B10" s="194"/>
       <c r="C10" s="110" t="s">
         <v>69</v>
       </c>
@@ -6284,10 +6302,10 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="174">
+      <c r="A11" s="193">
         <v>7</v>
       </c>
-      <c r="B11" s="175"/>
+      <c r="B11" s="194"/>
       <c r="C11" s="110" t="s">
         <v>70</v>
       </c>
@@ -6324,10 +6342,10 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="174" t="s">
+      <c r="A12" s="193" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="175"/>
+      <c r="B12" s="194"/>
       <c r="C12" s="110" t="str">
         <f>C9</f>
         <v>Grand Jorge</v>
@@ -6365,10 +6383,10 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="174" t="s">
+      <c r="A13" s="193" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="175"/>
+      <c r="B13" s="194"/>
       <c r="C13" s="110" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
@@ -6406,10 +6424,10 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="174" t="s">
+      <c r="A14" s="193" t="s">
         <v>77</v>
       </c>
-      <c r="B14" s="175"/>
+      <c r="B14" s="194"/>
       <c r="C14" s="58" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
@@ -6875,15 +6893,15 @@
     <row r="32" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="188" t="s">
+      <c r="E32" s="180" t="s">
         <v>111</v>
       </c>
-      <c r="F32" s="189"/>
-      <c r="G32" s="189"/>
-      <c r="H32" s="189"/>
-      <c r="I32" s="189"/>
-      <c r="J32" s="189"/>
-      <c r="K32" s="190"/>
+      <c r="F32" s="181"/>
+      <c r="G32" s="181"/>
+      <c r="H32" s="181"/>
+      <c r="I32" s="181"/>
+      <c r="J32" s="181"/>
+      <c r="K32" s="179"/>
       <c r="L32" s="152"/>
       <c r="M32" s="153"/>
       <c r="N32"/>
@@ -6891,15 +6909,15 @@
     <row r="33" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
-      <c r="E33" s="191" t="s">
+      <c r="E33" s="182" t="s">
         <v>112</v>
       </c>
-      <c r="F33" s="189"/>
-      <c r="G33" s="189"/>
-      <c r="H33" s="189"/>
-      <c r="I33" s="189"/>
-      <c r="J33" s="189"/>
-      <c r="K33" s="190"/>
+      <c r="F33" s="181"/>
+      <c r="G33" s="181"/>
+      <c r="H33" s="181"/>
+      <c r="I33" s="181"/>
+      <c r="J33" s="181"/>
+      <c r="K33" s="179"/>
       <c r="L33" s="154"/>
       <c r="M33" s="155"/>
       <c r="N33"/>
@@ -6954,15 +6972,15 @@
     <row r="37" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="192" t="s">
+      <c r="E37" s="183" t="s">
         <v>49</v>
       </c>
-      <c r="F37" s="193"/>
-      <c r="G37" s="193"/>
-      <c r="H37" s="193"/>
-      <c r="I37" s="193"/>
-      <c r="J37" s="193"/>
-      <c r="K37" s="194"/>
+      <c r="F37" s="184"/>
+      <c r="G37" s="184"/>
+      <c r="H37" s="184"/>
+      <c r="I37" s="184"/>
+      <c r="J37" s="184"/>
+      <c r="K37" s="185"/>
       <c r="L37" s="154"/>
       <c r="M37" s="155"/>
       <c r="N37"/>
@@ -7000,10 +7018,10 @@
         <v>45674</v>
       </c>
       <c r="K39" s="155"/>
-      <c r="L39" s="195" t="s">
+      <c r="L39" s="186" t="s">
         <v>116</v>
       </c>
-      <c r="M39" s="196"/>
+      <c r="M39" s="187"/>
       <c r="N39"/>
     </row>
     <row r="40" spans="3:14" x14ac:dyDescent="0.25">
@@ -7034,8 +7052,8 @@
       <c r="I41" s="157"/>
       <c r="J41" s="157"/>
       <c r="K41" s="155"/>
-      <c r="L41" s="197"/>
-      <c r="M41" s="196"/>
+      <c r="L41" s="188"/>
+      <c r="M41" s="187"/>
       <c r="N41"/>
     </row>
     <row r="42" spans="3:14" x14ac:dyDescent="0.25">
@@ -7200,18 +7218,18 @@
     <row r="52" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
-      <c r="E52" s="198" t="s">
+      <c r="E52" s="176" t="s">
         <v>119</v>
       </c>
-      <c r="F52" s="199"/>
-      <c r="G52" s="199"/>
-      <c r="H52" s="199"/>
-      <c r="I52" s="199"/>
-      <c r="J52" s="200">
+      <c r="F52" s="177"/>
+      <c r="G52" s="177"/>
+      <c r="H52" s="177"/>
+      <c r="I52" s="177"/>
+      <c r="J52" s="178">
         <f>SUM(J42:J51)</f>
         <v>99755.8</v>
       </c>
-      <c r="K52" s="190"/>
+      <c r="K52" s="179"/>
       <c r="L52" s="167"/>
       <c r="M52" s="168"/>
       <c r="N52"/>
@@ -7223,28 +7241,28 @@
     </row>
     <row r="55" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="56" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E56" s="188" t="s">
+      <c r="E56" s="180" t="s">
         <v>111</v>
       </c>
-      <c r="F56" s="189"/>
-      <c r="G56" s="189"/>
-      <c r="H56" s="189"/>
-      <c r="I56" s="189"/>
-      <c r="J56" s="189"/>
-      <c r="K56" s="190"/>
+      <c r="F56" s="181"/>
+      <c r="G56" s="181"/>
+      <c r="H56" s="181"/>
+      <c r="I56" s="181"/>
+      <c r="J56" s="181"/>
+      <c r="K56" s="179"/>
       <c r="L56" s="152"/>
       <c r="M56" s="153"/>
     </row>
     <row r="57" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E57" s="191" t="s">
+      <c r="E57" s="182" t="s">
         <v>112</v>
       </c>
-      <c r="F57" s="189"/>
-      <c r="G57" s="189"/>
-      <c r="H57" s="189"/>
-      <c r="I57" s="189"/>
-      <c r="J57" s="189"/>
-      <c r="K57" s="190"/>
+      <c r="F57" s="181"/>
+      <c r="G57" s="181"/>
+      <c r="H57" s="181"/>
+      <c r="I57" s="181"/>
+      <c r="J57" s="181"/>
+      <c r="K57" s="179"/>
       <c r="L57" s="154"/>
       <c r="M57" s="155"/>
     </row>
@@ -7287,15 +7305,15 @@
       <c r="M60" s="155"/>
     </row>
     <row r="61" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="E61" s="192" t="s">
+      <c r="E61" s="183" t="s">
         <v>49</v>
       </c>
-      <c r="F61" s="193"/>
-      <c r="G61" s="193"/>
-      <c r="H61" s="193"/>
-      <c r="I61" s="193"/>
-      <c r="J61" s="193"/>
-      <c r="K61" s="194"/>
+      <c r="F61" s="184"/>
+      <c r="G61" s="184"/>
+      <c r="H61" s="184"/>
+      <c r="I61" s="184"/>
+      <c r="J61" s="184"/>
+      <c r="K61" s="185"/>
       <c r="L61" s="154"/>
       <c r="M61" s="155"/>
     </row>
@@ -7327,10 +7345,10 @@
         <v>45674</v>
       </c>
       <c r="K63" s="155"/>
-      <c r="L63" s="195" t="s">
+      <c r="L63" s="186" t="s">
         <v>116</v>
       </c>
-      <c r="M63" s="196"/>
+      <c r="M63" s="187"/>
     </row>
     <row r="64" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E64" s="154" t="s">
@@ -7355,8 +7373,8 @@
       <c r="I65" s="157"/>
       <c r="J65" s="157"/>
       <c r="K65" s="155"/>
-      <c r="L65" s="197"/>
-      <c r="M65" s="196"/>
+      <c r="L65" s="188"/>
+      <c r="M65" s="187"/>
     </row>
     <row r="66" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E66" s="154" t="s">
@@ -7483,45 +7501,45 @@
       <c r="M75" s="166"/>
     </row>
     <row r="76" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E76" s="198" t="s">
+      <c r="E76" s="176" t="s">
         <v>119</v>
       </c>
-      <c r="F76" s="199"/>
-      <c r="G76" s="199"/>
-      <c r="H76" s="199"/>
-      <c r="I76" s="199"/>
-      <c r="J76" s="200">
+      <c r="F76" s="177"/>
+      <c r="G76" s="177"/>
+      <c r="H76" s="177"/>
+      <c r="I76" s="177"/>
+      <c r="J76" s="178">
         <f>SUM(J66:J75)</f>
         <v>118000</v>
       </c>
-      <c r="K76" s="190"/>
+      <c r="K76" s="179"/>
       <c r="L76" s="167"/>
       <c r="M76" s="168"/>
     </row>
     <row r="82" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="83" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E83" s="188" t="s">
+      <c r="E83" s="180" t="s">
         <v>111</v>
       </c>
-      <c r="F83" s="189"/>
-      <c r="G83" s="189"/>
-      <c r="H83" s="189"/>
-      <c r="I83" s="189"/>
-      <c r="J83" s="189"/>
-      <c r="K83" s="190"/>
+      <c r="F83" s="181"/>
+      <c r="G83" s="181"/>
+      <c r="H83" s="181"/>
+      <c r="I83" s="181"/>
+      <c r="J83" s="181"/>
+      <c r="K83" s="179"/>
       <c r="L83" s="152"/>
       <c r="M83" s="153"/>
     </row>
     <row r="84" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E84" s="191" t="s">
+      <c r="E84" s="182" t="s">
         <v>112</v>
       </c>
-      <c r="F84" s="189"/>
-      <c r="G84" s="189"/>
-      <c r="H84" s="189"/>
-      <c r="I84" s="189"/>
-      <c r="J84" s="189"/>
-      <c r="K84" s="190"/>
+      <c r="F84" s="181"/>
+      <c r="G84" s="181"/>
+      <c r="H84" s="181"/>
+      <c r="I84" s="181"/>
+      <c r="J84" s="181"/>
+      <c r="K84" s="179"/>
       <c r="L84" s="154"/>
       <c r="M84" s="155"/>
     </row>
@@ -7564,15 +7582,15 @@
       <c r="M87" s="155"/>
     </row>
     <row r="88" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E88" s="192" t="s">
+      <c r="E88" s="183" t="s">
         <v>49</v>
       </c>
-      <c r="F88" s="193"/>
-      <c r="G88" s="193"/>
-      <c r="H88" s="193"/>
-      <c r="I88" s="193"/>
-      <c r="J88" s="193"/>
-      <c r="K88" s="194"/>
+      <c r="F88" s="184"/>
+      <c r="G88" s="184"/>
+      <c r="H88" s="184"/>
+      <c r="I88" s="184"/>
+      <c r="J88" s="184"/>
+      <c r="K88" s="185"/>
       <c r="L88" s="154"/>
       <c r="M88" s="155"/>
     </row>
@@ -7604,10 +7622,10 @@
         <v>45674</v>
       </c>
       <c r="K90" s="155"/>
-      <c r="L90" s="195" t="s">
+      <c r="L90" s="186" t="s">
         <v>116</v>
       </c>
-      <c r="M90" s="196"/>
+      <c r="M90" s="187"/>
     </row>
     <row r="91" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E91" s="154" t="s">
@@ -7632,8 +7650,8 @@
       <c r="I92" s="157"/>
       <c r="J92" s="157"/>
       <c r="K92" s="155"/>
-      <c r="L92" s="197"/>
-      <c r="M92" s="196"/>
+      <c r="L92" s="188"/>
+      <c r="M92" s="187"/>
     </row>
     <row r="93" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E93" s="154" t="s">
@@ -7759,45 +7777,45 @@
       <c r="M102" s="166"/>
     </row>
     <row r="103" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E103" s="198" t="s">
+      <c r="E103" s="176" t="s">
         <v>119</v>
       </c>
-      <c r="F103" s="199"/>
-      <c r="G103" s="199"/>
-      <c r="H103" s="199"/>
-      <c r="I103" s="199"/>
-      <c r="J103" s="200">
+      <c r="F103" s="177"/>
+      <c r="G103" s="177"/>
+      <c r="H103" s="177"/>
+      <c r="I103" s="177"/>
+      <c r="J103" s="178">
         <f>SUM(J93:J102)</f>
         <v>99863.89</v>
       </c>
-      <c r="K103" s="190"/>
+      <c r="K103" s="179"/>
       <c r="L103" s="167"/>
       <c r="M103" s="168"/>
     </row>
     <row r="107" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="108" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E108" s="188" t="s">
+      <c r="E108" s="180" t="s">
         <v>111</v>
       </c>
-      <c r="F108" s="189"/>
-      <c r="G108" s="189"/>
-      <c r="H108" s="189"/>
-      <c r="I108" s="189"/>
-      <c r="J108" s="189"/>
-      <c r="K108" s="190"/>
+      <c r="F108" s="181"/>
+      <c r="G108" s="181"/>
+      <c r="H108" s="181"/>
+      <c r="I108" s="181"/>
+      <c r="J108" s="181"/>
+      <c r="K108" s="179"/>
       <c r="L108" s="152"/>
       <c r="M108" s="153"/>
     </row>
     <row r="109" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E109" s="191" t="s">
+      <c r="E109" s="182" t="s">
         <v>112</v>
       </c>
-      <c r="F109" s="189"/>
-      <c r="G109" s="189"/>
-      <c r="H109" s="189"/>
-      <c r="I109" s="189"/>
-      <c r="J109" s="189"/>
-      <c r="K109" s="190"/>
+      <c r="F109" s="181"/>
+      <c r="G109" s="181"/>
+      <c r="H109" s="181"/>
+      <c r="I109" s="181"/>
+      <c r="J109" s="181"/>
+      <c r="K109" s="179"/>
       <c r="L109" s="154"/>
       <c r="M109" s="155"/>
     </row>
@@ -7840,15 +7858,15 @@
       <c r="M112" s="155"/>
     </row>
     <row r="113" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E113" s="192" t="s">
+      <c r="E113" s="183" t="s">
         <v>49</v>
       </c>
-      <c r="F113" s="193"/>
-      <c r="G113" s="193"/>
-      <c r="H113" s="193"/>
-      <c r="I113" s="193"/>
-      <c r="J113" s="193"/>
-      <c r="K113" s="194"/>
+      <c r="F113" s="184"/>
+      <c r="G113" s="184"/>
+      <c r="H113" s="184"/>
+      <c r="I113" s="184"/>
+      <c r="J113" s="184"/>
+      <c r="K113" s="185"/>
       <c r="L113" s="154"/>
       <c r="M113" s="155"/>
     </row>
@@ -7880,10 +7898,10 @@
         <v>45674</v>
       </c>
       <c r="K115" s="155"/>
-      <c r="L115" s="195" t="s">
+      <c r="L115" s="186" t="s">
         <v>116</v>
       </c>
-      <c r="M115" s="196"/>
+      <c r="M115" s="187"/>
     </row>
     <row r="116" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E116" s="154" t="s">
@@ -7908,8 +7926,8 @@
       <c r="I117" s="157"/>
       <c r="J117" s="157"/>
       <c r="K117" s="155"/>
-      <c r="L117" s="197"/>
-      <c r="M117" s="196"/>
+      <c r="L117" s="188"/>
+      <c r="M117" s="187"/>
     </row>
     <row r="118" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E118" s="154" t="s">
@@ -8036,57 +8054,23 @@
       <c r="M127" s="166"/>
     </row>
     <row r="128" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E128" s="198" t="s">
+      <c r="E128" s="176" t="s">
         <v>119</v>
       </c>
-      <c r="F128" s="199"/>
-      <c r="G128" s="199"/>
-      <c r="H128" s="199"/>
-      <c r="I128" s="199"/>
-      <c r="J128" s="200">
+      <c r="F128" s="177"/>
+      <c r="G128" s="177"/>
+      <c r="H128" s="177"/>
+      <c r="I128" s="177"/>
+      <c r="J128" s="178">
         <f>SUM(J118:J127)</f>
         <v>110347.66</v>
       </c>
-      <c r="K128" s="190"/>
+      <c r="K128" s="179"/>
       <c r="L128" s="167"/>
       <c r="M128" s="168"/>
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="E32:K32"/>
-    <mergeCell ref="L115:M115"/>
-    <mergeCell ref="L117:M117"/>
-    <mergeCell ref="E128:I128"/>
-    <mergeCell ref="J128:K128"/>
-    <mergeCell ref="E83:K83"/>
-    <mergeCell ref="E84:K84"/>
-    <mergeCell ref="E88:K88"/>
-    <mergeCell ref="L90:M90"/>
-    <mergeCell ref="L92:M92"/>
-    <mergeCell ref="E103:I103"/>
-    <mergeCell ref="J103:K103"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="E108:K108"/>
     <mergeCell ref="E109:K109"/>
@@ -8103,6 +8087,40 @@
     <mergeCell ref="L39:M39"/>
     <mergeCell ref="L41:M41"/>
     <mergeCell ref="E52:I52"/>
+    <mergeCell ref="L115:M115"/>
+    <mergeCell ref="L117:M117"/>
+    <mergeCell ref="E128:I128"/>
+    <mergeCell ref="J128:K128"/>
+    <mergeCell ref="E83:K83"/>
+    <mergeCell ref="E84:K84"/>
+    <mergeCell ref="E88:K88"/>
+    <mergeCell ref="L90:M90"/>
+    <mergeCell ref="L92:M92"/>
+    <mergeCell ref="E103:I103"/>
+    <mergeCell ref="J103:K103"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="E32:K32"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="I1:J1"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
